--- a/data/staticsheet.xlsx
+++ b/data/staticsheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ronan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ronan\Desktop\Game Related\Lost Ark\discord-raid-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E92D05-52D4-47C6-8E91-D8198AF82CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FF0238-EB03-4E89-BA15-E32533C8F049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="5175" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2073,7 +2073,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2246,12 +2246,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF85200C"/>
         <bgColor rgb="FF85200C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7CB4D"/>
-        <bgColor rgb="FFF7CB4D"/>
       </patternFill>
     </fill>
     <fill>
@@ -2887,7 +2881,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="258">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3053,9 +3047,7 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="29" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3068,24 +3060,23 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3099,12 +3090,12 @@
     <xf numFmtId="0" fontId="5" fillId="26" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3117,16 +3108,16 @@
     <xf numFmtId="0" fontId="4" fillId="25" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="34" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3147,13 +3138,13 @@
     <xf numFmtId="0" fontId="1" fillId="17" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -3182,10 +3173,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="39" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="38" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="39" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3740,22 +3731,6 @@
       </fill>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
@@ -3779,13 +3754,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="14">
     <tableStyle name="LATE TRACKER-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="61"/>
-      <tableStyleElement type="headerRow" dxfId="64"/>
-      <tableStyleElement type="firstRowStripe" dxfId="63"/>
-      <tableStyleElement type="secondRowStripe" dxfId="62"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="64"/>
+      <tableStyleElement type="headerRow" dxfId="63"/>
+      <tableStyleElement type="firstRowStripe" dxfId="62"/>
+      <tableStyleElement type="secondRowStripe" dxfId="61"/>
     </tableStyle>
     <tableStyle name="Marcel-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="60"/>
@@ -4902,7 +4893,7 @@
     <col min="7" max="23" width="12.5703125" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" ht="12.75">
       <c r="A1" s="21"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4913,8 +4904,8 @@
       <c r="M1" s="1"/>
       <c r="N1" s="22"/>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="248" t="s">
+    <row r="2" spans="1:14" ht="12.75">
+      <c r="A2" s="245" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="23" t="s">
@@ -4932,7 +4923,7 @@
       <c r="F2" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="248"/>
+      <c r="H2" s="245"/>
       <c r="I2" s="3" t="s">
         <v>49</v>
       </c>
@@ -4949,8 +4940,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="249"/>
+    <row r="3" spans="1:14" ht="12.75">
+      <c r="A3" s="246"/>
       <c r="B3" s="28"/>
       <c r="C3" s="29" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C2),"""",HLOOKUP(REGEXEXTRACT(C2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C2,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"#REF!")</f>
@@ -4968,7 +4959,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F2),"""",HLOOKUP(REGEXEXTRACT(F2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F2,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Bard")</f>
         <v>Bard</v>
       </c>
-      <c r="H3" s="249"/>
+      <c r="H3" s="246"/>
       <c r="I3" s="30"/>
       <c r="J3" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J2),"""",HLOOKUP(REGEXEXTRACT(J2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J2,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Slayer")</f>
@@ -4987,8 +4978,8 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="249"/>
+    <row r="4" spans="1:14" ht="12.75">
+      <c r="A4" s="246"/>
       <c r="B4" s="31"/>
       <c r="C4" s="32" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C2),"""",HLOOKUP(REGEXEXTRACT(C2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C2,""(.*)-.*""),""!C3:V"")),3,FALSE))"),"#REF!")</f>
@@ -5006,7 +4997,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F2),"""",HLOOKUP(REGEXEXTRACT(F2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F2,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1670)</f>
         <v>1670</v>
       </c>
-      <c r="H4" s="249"/>
+      <c r="H4" s="246"/>
       <c r="I4" s="33"/>
       <c r="J4" s="10">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J2),"""",HLOOKUP(REGEXEXTRACT(J2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J2,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1610)</f>
@@ -5025,15 +5016,15 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" ht="12.75">
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="248" t="s">
+    <row r="6" spans="1:14" ht="12.75">
+      <c r="A6" s="245" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="23" t="s">
@@ -5051,7 +5042,7 @@
       <c r="F6" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="248"/>
+      <c r="H6" s="245"/>
       <c r="I6" s="3" t="s">
         <v>49</v>
       </c>
@@ -5068,8 +5059,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="249"/>
+    <row r="7" spans="1:14" ht="12.75">
+      <c r="A7" s="246"/>
       <c r="B7" s="28"/>
       <c r="C7" s="29" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C6),"""",HLOOKUP(REGEXEXTRACT(C6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C6,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"#REF!")</f>
@@ -5087,7 +5078,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F6),"""",HLOOKUP(REGEXEXTRACT(F6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F6,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Bard")</f>
         <v>Bard</v>
       </c>
-      <c r="H7" s="249"/>
+      <c r="H7" s="246"/>
       <c r="I7" s="30"/>
       <c r="J7" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J6),"""",HLOOKUP(REGEXEXTRACT(J6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J6,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"GL")</f>
@@ -5106,8 +5097,8 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="249"/>
+    <row r="8" spans="1:14" ht="12.75">
+      <c r="A8" s="246"/>
       <c r="B8" s="31"/>
       <c r="C8" s="32" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C6),"""",HLOOKUP(REGEXEXTRACT(C6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),"#REF!")</f>
@@ -5125,7 +5116,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F6),"""",HLOOKUP(REGEXEXTRACT(F6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F6,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1700)</f>
         <v>1700</v>
       </c>
-      <c r="H8" s="249"/>
+      <c r="H8" s="246"/>
       <c r="I8" s="33"/>
       <c r="J8" s="10">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J6),"""",HLOOKUP(REGEXEXTRACT(J6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J6,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
@@ -5144,13 +5135,13 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" ht="12.75">
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="248" t="s">
+    <row r="10" spans="1:14" ht="12.75">
+      <c r="A10" s="245" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -5168,7 +5159,7 @@
       <c r="F10" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="248"/>
+      <c r="H10" s="245"/>
       <c r="I10" s="3" t="s">
         <v>49</v>
       </c>
@@ -5185,8 +5176,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="249"/>
+    <row r="11" spans="1:14" ht="12.75">
+      <c r="A11" s="246"/>
       <c r="B11" s="28"/>
       <c r="C11" s="29" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C10),"""",HLOOKUP(REGEXEXTRACT(C10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C10,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"#REF!")</f>
@@ -5204,7 +5195,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F10),"""",HLOOKUP(REGEXEXTRACT(F10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F10,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Summoner")</f>
         <v>Summoner</v>
       </c>
-      <c r="H11" s="249"/>
+      <c r="H11" s="246"/>
       <c r="I11" s="30"/>
       <c r="J11" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J10),"""",HLOOKUP(REGEXEXTRACT(J10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J10,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Scouter")</f>
@@ -5223,8 +5214,8 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="249"/>
+    <row r="12" spans="1:14" ht="12.75">
+      <c r="A12" s="246"/>
       <c r="B12" s="31"/>
       <c r="C12" s="32" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C10),"""",HLOOKUP(REGEXEXTRACT(C10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C10,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
@@ -5242,7 +5233,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F10),"""",HLOOKUP(REGEXEXTRACT(F10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F10,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1680)</f>
         <v>1680</v>
       </c>
-      <c r="H12" s="249"/>
+      <c r="H12" s="246"/>
       <c r="I12" s="33"/>
       <c r="J12" s="10">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J10),"""",HLOOKUP(REGEXEXTRACT(J10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J10,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1600)</f>
@@ -5261,13 +5252,13 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" ht="12.75">
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="248" t="s">
+    <row r="14" spans="1:14" ht="12.75">
+      <c r="A14" s="245" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="23" t="s">
@@ -5285,7 +5276,7 @@
       <c r="F14" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="H14" s="248"/>
+      <c r="H14" s="245"/>
       <c r="I14" s="3" t="s">
         <v>49</v>
       </c>
@@ -5302,8 +5293,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="249"/>
+    <row r="15" spans="1:14" ht="12.75">
+      <c r="A15" s="246"/>
       <c r="B15" s="15"/>
       <c r="C15" s="29" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C14),"""",HLOOKUP(REGEXEXTRACT(C14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C14,""(.*)-.*""),""!C3:Z"")),2,FALSE))"),"#REF!")</f>
@@ -5321,7 +5312,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F14),"""",HLOOKUP(REGEXEXTRACT(F14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F14,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"BREAKER")</f>
         <v>BREAKER</v>
       </c>
-      <c r="H15" s="249"/>
+      <c r="H15" s="246"/>
       <c r="I15" s="36"/>
       <c r="J15" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J14),"""",HLOOKUP(REGEXEXTRACT(J14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J14,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Slayer")</f>
@@ -5340,8 +5331,8 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="249"/>
+    <row r="16" spans="1:14" ht="12.75">
+      <c r="A16" s="246"/>
       <c r="B16" s="16"/>
       <c r="C16" s="32" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C14),"""",HLOOKUP(REGEXEXTRACT(C14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C14,""(.*)-.*""),""!C3:Z"")),3,FALSE))"),"#REF!")</f>
@@ -5359,7 +5350,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F14),"""",HLOOKUP(REGEXEXTRACT(F14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F14,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H16" s="249"/>
+      <c r="H16" s="246"/>
       <c r="I16" s="37"/>
       <c r="J16" s="10">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J14),"""",HLOOKUP(REGEXEXTRACT(J14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J14,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
@@ -5378,8 +5369,8 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="248" t="s">
+    <row r="18" spans="1:13" ht="12.75">
+      <c r="A18" s="245" t="s">
         <v>0</v>
       </c>
       <c r="B18" s="23" t="s">
@@ -5397,7 +5388,7 @@
       <c r="F18" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="H18" s="248"/>
+      <c r="H18" s="245"/>
       <c r="I18" s="3" t="s">
         <v>49</v>
       </c>
@@ -5414,8 +5405,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="249"/>
+    <row r="19" spans="1:13" ht="12.75">
+      <c r="A19" s="246"/>
       <c r="B19" s="15"/>
       <c r="C19" s="29" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C18),"""",HLOOKUP(REGEXEXTRACT(C18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C18,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"#REF!")</f>
@@ -5433,7 +5424,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F18),"""",HLOOKUP(REGEXEXTRACT(F18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F18,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"GL")</f>
         <v>GL</v>
       </c>
-      <c r="H19" s="249"/>
+      <c r="H19" s="246"/>
       <c r="I19" s="30"/>
       <c r="J19" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J18),"""",HLOOKUP(REGEXEXTRACT(J18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J18,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"#REF!")</f>
@@ -5452,8 +5443,8 @@
         <v>Aeromancer</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="249"/>
+    <row r="20" spans="1:13" ht="12.75">
+      <c r="A20" s="246"/>
       <c r="B20" s="16"/>
       <c r="C20" s="32" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C18),"""",HLOOKUP(REGEXEXTRACT(C18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C18,""(.*)-.*""),""!C3:V"")),3,FALSE))"),"#REF!")</f>
@@ -5471,7 +5462,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F18),"""",HLOOKUP(REGEXEXTRACT(F18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F18,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H20" s="249"/>
+      <c r="H20" s="246"/>
       <c r="I20" s="33"/>
       <c r="J20" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J18),"""",HLOOKUP(REGEXEXTRACT(J18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J18,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
@@ -5490,8 +5481,8 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="248" t="s">
+    <row r="22" spans="1:13" ht="12.75">
+      <c r="A22" s="245" t="s">
         <v>0</v>
       </c>
       <c r="B22" s="23" t="s">
@@ -5509,7 +5500,7 @@
       <c r="F22" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="H22" s="248"/>
+      <c r="H22" s="245"/>
       <c r="I22" s="3" t="s">
         <v>49</v>
       </c>
@@ -5526,8 +5517,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="249"/>
+    <row r="23" spans="1:13" ht="12.75">
+      <c r="A23" s="246"/>
       <c r="B23" s="15"/>
       <c r="C23" s="29" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C22),"""",HLOOKUP(REGEXEXTRACT(C22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C22,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"#REF!")</f>
@@ -5545,7 +5536,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F22),"""",HLOOKUP(REGEXEXTRACT(F22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F22,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Paladin")</f>
         <v>Paladin</v>
       </c>
-      <c r="H23" s="249"/>
+      <c r="H23" s="246"/>
       <c r="I23" s="30"/>
       <c r="J23" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J22),"""",HLOOKUP(REGEXEXTRACT(J22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J22,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Summoner")</f>
@@ -5564,8 +5555,8 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="249"/>
+    <row r="24" spans="1:13" ht="12.75">
+      <c r="A24" s="246"/>
       <c r="B24" s="16"/>
       <c r="C24" s="32" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C22),"""",HLOOKUP(REGEXEXTRACT(C22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C22,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
@@ -5583,7 +5574,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F22),"""",HLOOKUP(REGEXEXTRACT(F22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F22,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H24" s="249"/>
+      <c r="H24" s="246"/>
       <c r="I24" s="33"/>
       <c r="J24" s="10">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J22),"""",HLOOKUP(REGEXEXTRACT(J22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J22,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
@@ -5602,8 +5593,8 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="250" t="s">
+    <row r="26" spans="1:13" ht="12.75">
+      <c r="A26" s="247" t="s">
         <v>0</v>
       </c>
       <c r="B26" s="23" t="s">
@@ -5621,7 +5612,7 @@
       <c r="F26" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="248"/>
+      <c r="H26" s="245"/>
       <c r="I26" s="3" t="s">
         <v>71</v>
       </c>
@@ -5634,8 +5625,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="249"/>
+    <row r="27" spans="1:13" ht="12.75">
+      <c r="A27" s="246"/>
       <c r="B27" s="38"/>
       <c r="C27" s="29" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C26),"""",HLOOKUP(REGEXEXTRACT(C26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C26,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"#REF!")</f>
@@ -5653,7 +5644,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F26),"""",HLOOKUP(REGEXEXTRACT(F26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F26,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Artill")</f>
         <v>Artill</v>
       </c>
-      <c r="H27" s="249"/>
+      <c r="H27" s="246"/>
       <c r="I27" s="39"/>
       <c r="J27" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J26),"""",HLOOKUP(REGEXEXTRACT(J26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J26,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"")</f>
@@ -5672,8 +5663,8 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="249"/>
+    <row r="28" spans="1:13" ht="12.75">
+      <c r="A28" s="246"/>
       <c r="B28" s="40"/>
       <c r="C28" s="32" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C26),"""",HLOOKUP(REGEXEXTRACT(C26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C26,""(.*)-.*""),""!C3:V"")),3,FALSE))"),"#REF!")</f>
@@ -5691,7 +5682,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F26),"""",HLOOKUP(REGEXEXTRACT(F26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F26,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H28" s="249"/>
+      <c r="H28" s="246"/>
       <c r="I28" s="41"/>
       <c r="J28" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J26),"""",HLOOKUP(REGEXEXTRACT(J26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J26,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
@@ -5710,15 +5701,15 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" ht="12.75">
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
       <c r="M29" s="10"/>
     </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="248" t="s">
+    <row r="30" spans="1:13" ht="12.75">
+      <c r="A30" s="245" t="s">
         <v>0</v>
       </c>
       <c r="B30" s="23" t="s">
@@ -5732,7 +5723,7 @@
       <c r="F30" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="H30" s="248"/>
+      <c r="H30" s="245"/>
       <c r="I30" s="42" t="s">
         <v>71</v>
       </c>
@@ -5747,8 +5738,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="249"/>
+    <row r="31" spans="1:13" ht="12.75">
+      <c r="A31" s="246"/>
       <c r="B31" s="39"/>
       <c r="C31" s="29" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C30),"""",HLOOKUP(REGEXEXTRACT(C30,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C30,""(.*)-.*""),""!C3:Z"")),2,FALSE))"),"#REF!")</f>
@@ -5766,7 +5757,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F30),"""",HLOOKUP(REGEXEXTRACT(F30,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F30,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Bonk")</f>
         <v>Bonk</v>
       </c>
-      <c r="H31" s="249"/>
+      <c r="H31" s="246"/>
       <c r="I31" s="39"/>
       <c r="J31" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J30),"""",HLOOKUP(REGEXEXTRACT(J30,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J30,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"")</f>
@@ -5785,8 +5776,8 @@
         <v>Deathblade</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="249"/>
+    <row r="32" spans="1:13" ht="12.75">
+      <c r="A32" s="246"/>
       <c r="B32" s="41"/>
       <c r="C32" s="32" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C30),"""",HLOOKUP(REGEXEXTRACT(C30,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C30,""(.*)-.*""),""!C3:Z"")),3,FALSE))"),"#REF!")</f>
@@ -5804,7 +5795,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F30),"""",HLOOKUP(REGEXEXTRACT(F30,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F30,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H32" s="249"/>
+      <c r="H32" s="246"/>
       <c r="I32" s="41"/>
       <c r="J32" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J30),"""",HLOOKUP(REGEXEXTRACT(J30,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J30,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
@@ -5823,7 +5814,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" ht="12.75">
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
       <c r="D33" s="45"/>
@@ -5835,8 +5826,8 @@
       <c r="L33" s="22"/>
       <c r="M33" s="22"/>
     </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="248" t="s">
+    <row r="34" spans="1:13" ht="12.75">
+      <c r="A34" s="245" t="s">
         <v>0</v>
       </c>
       <c r="B34" s="23" t="s">
@@ -5852,7 +5843,7 @@
         <v>75</v>
       </c>
       <c r="F34" s="26"/>
-      <c r="H34" s="248"/>
+      <c r="H34" s="245"/>
       <c r="I34" s="3" t="s">
         <v>71</v>
       </c>
@@ -5861,8 +5852,8 @@
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
     </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="249"/>
+    <row r="35" spans="1:13" ht="12.75">
+      <c r="A35" s="246"/>
       <c r="B35" s="13"/>
       <c r="C35" s="29" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C34),"""",HLOOKUP(REGEXEXTRACT(C34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C34,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"#REF!")</f>
@@ -5880,7 +5871,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F34),"""",HLOOKUP(REGEXEXTRACT(F34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F34,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="H35" s="249"/>
+      <c r="H35" s="246"/>
       <c r="I35" s="39"/>
       <c r="J35" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J34),"""",HLOOKUP(REGEXEXTRACT(J34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J34,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"")</f>
@@ -5899,8 +5890,8 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="249"/>
+    <row r="36" spans="1:13" ht="12.75">
+      <c r="A36" s="246"/>
       <c r="B36" s="14"/>
       <c r="C36" s="32" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C34),"""",HLOOKUP(REGEXEXTRACT(C34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C34,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
@@ -5918,7 +5909,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F34),"""",HLOOKUP(REGEXEXTRACT(F34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F34,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="H36" s="249"/>
+      <c r="H36" s="246"/>
       <c r="I36" s="41"/>
       <c r="J36" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J34),"""",HLOOKUP(REGEXEXTRACT(J34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J34,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
@@ -5937,8 +5928,8 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="248" t="s">
+    <row r="38" spans="1:13" ht="12.75">
+      <c r="A38" s="245" t="s">
         <v>0</v>
       </c>
       <c r="B38" s="23" t="s">
@@ -5956,7 +5947,7 @@
       <c r="F38" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="H38" s="248"/>
+      <c r="H38" s="245"/>
       <c r="I38" s="3" t="s">
         <v>71</v>
       </c>
@@ -5965,8 +5956,8 @@
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
     </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="249"/>
+    <row r="39" spans="1:13" ht="12.75">
+      <c r="A39" s="246"/>
       <c r="B39" s="46"/>
       <c r="C39" s="29" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C38),"""",HLOOKUP(REGEXEXTRACT(C38,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C38,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Gunlancer")</f>
@@ -5984,7 +5975,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F38),"""",HLOOKUP(REGEXEXTRACT(F38,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F38,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Slayer")</f>
         <v>Slayer</v>
       </c>
-      <c r="H39" s="249"/>
+      <c r="H39" s="246"/>
       <c r="I39" s="39"/>
       <c r="J39" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J38),"""",HLOOKUP(REGEXEXTRACT(J38,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J38,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"")</f>
@@ -6003,8 +5994,8 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:13">
-      <c r="A40" s="249"/>
+    <row r="40" spans="1:13" ht="12.75">
+      <c r="A40" s="246"/>
       <c r="B40" s="47"/>
       <c r="C40" s="32">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C38),"""",HLOOKUP(REGEXEXTRACT(C38,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C38,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1600.83)</f>
@@ -6022,7 +6013,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F38),"""",HLOOKUP(REGEXEXTRACT(F38,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F38,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1610)</f>
         <v>1610</v>
       </c>
-      <c r="H40" s="249"/>
+      <c r="H40" s="246"/>
       <c r="I40" s="41"/>
       <c r="J40" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J38),"""",HLOOKUP(REGEXEXTRACT(J38,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J38,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
@@ -6041,35 +6032,26 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="246"/>
+    <row r="42" spans="1:13" ht="12.75">
+      <c r="A42" s="243"/>
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A43" s="247"/>
+      <c r="A43" s="244"/>
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A44" s="247"/>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="246"/>
+      <c r="A44" s="244"/>
+    </row>
+    <row r="46" spans="1:13" ht="12.75">
+      <c r="A46" s="243"/>
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A47" s="247"/>
+      <c r="A47" s="244"/>
     </row>
     <row r="48" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A48" s="247"/>
+      <c r="A48" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A38:A40"/>
     <mergeCell ref="H38:H40"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="H2:H4"/>
@@ -6083,6 +6065,15 @@
     <mergeCell ref="H26:H28"/>
     <mergeCell ref="H30:H32"/>
     <mergeCell ref="H34:H36"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="A38:A40"/>
   </mergeCells>
   <conditionalFormatting sqref="H2:H12 A2:A48 H14:H16 H18:H20 H22:H24 H26:H45 B33 B37 B41 B45">
     <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
@@ -6123,33 +6114,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13">
-      <c r="A2" s="246"/>
-      <c r="B2" s="206" t="s">
+      <c r="A2" s="243"/>
+      <c r="B2" s="203" t="s">
         <v>302</v>
       </c>
-      <c r="C2" s="217" t="s">
+      <c r="C2" s="214" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="217" t="s">
+      <c r="D2" s="214" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="217" t="s">
+      <c r="E2" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="217"/>
-      <c r="H2" s="246" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="206" t="s">
+      <c r="F2" s="214"/>
+      <c r="H2" s="243" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="203" t="s">
         <v>303</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="217"/>
-      <c r="L2" s="217"/>
-      <c r="M2" s="217"/>
+      <c r="J2" s="214"/>
+      <c r="K2" s="214"/>
+      <c r="L2" s="214"/>
+      <c r="M2" s="214"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="247"/>
+      <c r="A3" s="244"/>
       <c r="B3" s="98"/>
       <c r="C3" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C2),"""",HLOOKUP(REGEXEXTRACT(C2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C2,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Bard")</f>
@@ -6163,7 +6154,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E2),"""",HLOOKUP(REGEXEXTRACT(E2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E2,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Gunslinger")</f>
         <v>Gunslinger</v>
       </c>
-      <c r="H3" s="247"/>
+      <c r="H3" s="244"/>
       <c r="I3" s="98"/>
       <c r="J3" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J2),"""",HLOOKUP(REGEXEXTRACT(J2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J2,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
@@ -6183,8 +6174,8 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="247"/>
-      <c r="B4" s="218"/>
+      <c r="A4" s="244"/>
+      <c r="B4" s="215"/>
       <c r="C4" s="7">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C2),"""",HLOOKUP(REGEXEXTRACT(C2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C2,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1560)</f>
         <v>1560</v>
@@ -6197,8 +6188,8 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E2),"""",HLOOKUP(REGEXEXTRACT(E2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E2,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H4" s="247"/>
-      <c r="I4" s="218"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="215"/>
       <c r="J4" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J2),"""",HLOOKUP(REGEXEXTRACT(J2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J2,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
@@ -6217,23 +6208,23 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="L5" s="246"/>
+      <c r="L5" s="243"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="246"/>
-      <c r="B6" s="206" t="s">
+      <c r="A6" s="243"/>
+      <c r="B6" s="203" t="s">
         <v>302</v>
       </c>
-      <c r="C6" s="217" t="s">
+      <c r="C6" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="217" t="s">
+      <c r="D6" s="214" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="217" t="s">
+      <c r="E6" s="214" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="217"/>
+      <c r="F6" s="214"/>
       <c r="I6" s="7" t="s">
         <v>41</v>
       </c>
@@ -6243,10 +6234,10 @@
       <c r="K6" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="L6" s="247"/>
+      <c r="L6" s="244"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="247"/>
+      <c r="A7" s="244"/>
       <c r="B7" s="98"/>
       <c r="C7" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C6),"""",HLOOKUP(REGEXEXTRACT(C6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C6,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Wardancer")</f>
@@ -6275,11 +6266,11 @@
         <f t="shared" si="0"/>
         <v>19362</v>
       </c>
-      <c r="L7" s="247"/>
+      <c r="L7" s="244"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="247"/>
-      <c r="B8" s="218"/>
+      <c r="A8" s="244"/>
+      <c r="B8" s="215"/>
       <c r="C8" s="7">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C6),"""",HLOOKUP(REGEXEXTRACT(C6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C6,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1620)</f>
         <v>1620</v>
@@ -6320,20 +6311,20 @@
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="246"/>
-      <c r="B10" s="206" t="s">
+      <c r="A10" s="243"/>
+      <c r="B10" s="203" t="s">
         <v>302</v>
       </c>
-      <c r="C10" s="217" t="s">
+      <c r="C10" s="214" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="217" t="s">
+      <c r="D10" s="214" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="217" t="s">
+      <c r="E10" s="214" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="217"/>
+      <c r="F10" s="214"/>
       <c r="H10" s="7" t="s">
         <v>306</v>
       </c>
@@ -6348,7 +6339,7 @@
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="247"/>
+      <c r="A11" s="244"/>
       <c r="B11" s="98"/>
       <c r="C11" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C10),"""",HLOOKUP(REGEXEXTRACT(C10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C10,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Gunslinger")</f>
@@ -6381,8 +6372,8 @@
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="247"/>
-      <c r="B12" s="218"/>
+      <c r="A12" s="244"/>
+      <c r="B12" s="215"/>
       <c r="C12" s="7">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C10),"""",HLOOKUP(REGEXEXTRACT(C10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C10,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1600)</f>
         <v>1600</v>
@@ -6427,14 +6418,14 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="246"/>
-      <c r="B14" s="206" t="s">
+      <c r="A14" s="243"/>
+      <c r="B14" s="203" t="s">
         <v>302</v>
       </c>
-      <c r="C14" s="217"/>
-      <c r="D14" s="217"/>
-      <c r="E14" s="217"/>
-      <c r="F14" s="217"/>
+      <c r="C14" s="214"/>
+      <c r="D14" s="214"/>
+      <c r="E14" s="214"/>
+      <c r="F14" s="214"/>
       <c r="H14" s="7" t="s">
         <v>306</v>
       </c>
@@ -6449,7 +6440,7 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="247"/>
+      <c r="A15" s="244"/>
       <c r="B15" s="98"/>
       <c r="C15" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C14),"""",HLOOKUP(REGEXEXTRACT(C14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C14,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
@@ -6477,8 +6468,8 @@
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="247"/>
-      <c r="B16" s="218"/>
+      <c r="A16" s="244"/>
+      <c r="B16" s="215"/>
       <c r="C16" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C14),"""",HLOOKUP(REGEXEXTRACT(C14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C14,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
@@ -6561,14 +6552,14 @@
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="246"/>
-      <c r="B21" s="206" t="s">
+      <c r="A21" s="243"/>
+      <c r="B21" s="203" t="s">
         <v>305</v>
       </c>
-      <c r="C21" s="217"/>
-      <c r="D21" s="217"/>
-      <c r="E21" s="217"/>
-      <c r="F21" s="217"/>
+      <c r="C21" s="214"/>
+      <c r="D21" s="214"/>
+      <c r="E21" s="214"/>
+      <c r="F21" s="214"/>
       <c r="H21" s="7" t="s">
         <v>306</v>
       </c>
@@ -6583,7 +6574,7 @@
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="247"/>
+      <c r="A22" s="244"/>
       <c r="B22" s="98"/>
       <c r="C22" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C21),"""",HLOOKUP(REGEXEXTRACT(C21,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C21,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
@@ -6615,8 +6606,8 @@
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="247"/>
-      <c r="B23" s="218"/>
+      <c r="A23" s="244"/>
+      <c r="B23" s="215"/>
       <c r="C23" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C21),"""",HLOOKUP(REGEXEXTRACT(C21,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C21,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
@@ -6635,17 +6626,17 @@
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="246"/>
-      <c r="B25" s="206" t="s">
+      <c r="A25" s="243"/>
+      <c r="B25" s="203" t="s">
         <v>305</v>
       </c>
-      <c r="C25" s="217"/>
-      <c r="D25" s="217"/>
-      <c r="E25" s="217"/>
-      <c r="F25" s="217"/>
+      <c r="C25" s="214"/>
+      <c r="D25" s="214"/>
+      <c r="E25" s="214"/>
+      <c r="F25" s="214"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="247"/>
+      <c r="A26" s="244"/>
       <c r="B26" s="98"/>
       <c r="C26" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C25),"""",HLOOKUP(REGEXEXTRACT(C25,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C25,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
@@ -6665,8 +6656,8 @@
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="247"/>
-      <c r="B27" s="218"/>
+      <c r="A27" s="244"/>
+      <c r="B27" s="215"/>
       <c r="C27" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C25),"""",HLOOKUP(REGEXEXTRACT(C25,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C25,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
@@ -6685,17 +6676,17 @@
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="246"/>
-      <c r="B29" s="206" t="s">
+      <c r="A29" s="243"/>
+      <c r="B29" s="203" t="s">
         <v>305</v>
       </c>
-      <c r="C29" s="217"/>
-      <c r="D29" s="217"/>
-      <c r="E29" s="217"/>
-      <c r="F29" s="217"/>
+      <c r="C29" s="214"/>
+      <c r="D29" s="214"/>
+      <c r="E29" s="214"/>
+      <c r="F29" s="214"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="247"/>
+      <c r="A30" s="244"/>
       <c r="B30" s="98"/>
       <c r="C30" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C29),"""",HLOOKUP(REGEXEXTRACT(C29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C29,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
@@ -6715,8 +6706,8 @@
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="247"/>
-      <c r="B31" s="218"/>
+      <c r="A31" s="244"/>
+      <c r="B31" s="215"/>
       <c r="C31" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C29),"""",HLOOKUP(REGEXEXTRACT(C29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C29,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
@@ -6735,21 +6726,21 @@
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="246"/>
-      <c r="B36" s="206" t="s">
+      <c r="A36" s="243"/>
+      <c r="B36" s="203" t="s">
         <v>311</v>
       </c>
-      <c r="C36" s="217" t="s">
+      <c r="C36" s="214" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="217" t="s">
+      <c r="D36" s="214" t="s">
         <v>312</v>
       </c>
-      <c r="E36" s="217"/>
-      <c r="F36" s="217"/>
+      <c r="E36" s="214"/>
+      <c r="F36" s="214"/>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="247"/>
+      <c r="A37" s="244"/>
       <c r="B37" s="98"/>
       <c r="C37" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C36),"""",HLOOKUP(REGEXEXTRACT(C36,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C36,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Gunslinger")</f>
@@ -6769,8 +6760,8 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="247"/>
-      <c r="B38" s="218"/>
+      <c r="A38" s="244"/>
+      <c r="B38" s="215"/>
       <c r="C38" s="7">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C36),"""",HLOOKUP(REGEXEXTRACT(C36,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C36,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1600)</f>
         <v>1600</v>
@@ -6789,21 +6780,21 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="246"/>
-      <c r="B40" s="206" t="s">
+      <c r="A40" s="243"/>
+      <c r="B40" s="203" t="s">
         <v>311</v>
       </c>
-      <c r="C40" s="217" t="s">
+      <c r="C40" s="214" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="217" t="s">
+      <c r="D40" s="214" t="s">
         <v>313</v>
       </c>
-      <c r="E40" s="217"/>
-      <c r="F40" s="217"/>
+      <c r="E40" s="214"/>
+      <c r="F40" s="214"/>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="247"/>
+      <c r="A41" s="244"/>
       <c r="B41" s="98"/>
       <c r="C41" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C40),"""",HLOOKUP(REGEXEXTRACT(C40,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C40,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Guardianknight")</f>
@@ -6823,8 +6814,8 @@
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="247"/>
-      <c r="B42" s="218"/>
+      <c r="A42" s="244"/>
+      <c r="B42" s="215"/>
       <c r="C42" s="7">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C40),"""",HLOOKUP(REGEXEXTRACT(C40,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C40,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1750)</f>
         <v>1750</v>
@@ -6843,21 +6834,21 @@
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="246"/>
-      <c r="B44" s="206" t="s">
+      <c r="A44" s="243"/>
+      <c r="B44" s="203" t="s">
         <v>311</v>
       </c>
-      <c r="C44" s="217" t="s">
+      <c r="C44" s="214" t="s">
         <v>3</v>
       </c>
-      <c r="D44" s="217" t="s">
+      <c r="D44" s="214" t="s">
         <v>270</v>
       </c>
-      <c r="E44" s="217"/>
-      <c r="F44" s="217"/>
+      <c r="E44" s="214"/>
+      <c r="F44" s="214"/>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="247"/>
+      <c r="A45" s="244"/>
       <c r="B45" s="98"/>
       <c r="C45" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C44),"""",HLOOKUP(REGEXEXTRACT(C44,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C44,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Sorceress")</f>
@@ -6877,8 +6868,8 @@
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="247"/>
-      <c r="B46" s="218"/>
+      <c r="A46" s="244"/>
+      <c r="B46" s="215"/>
       <c r="C46" s="7">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C44),"""",HLOOKUP(REGEXEXTRACT(C44,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C44,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1600)</f>
         <v>1600</v>
@@ -6897,25 +6888,25 @@
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="246" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" s="206" t="s">
+      <c r="A48" s="243" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="203" t="s">
         <v>311</v>
       </c>
-      <c r="C48" s="217" t="s">
+      <c r="C48" s="214" t="s">
         <v>30</v>
       </c>
-      <c r="D48" s="217" t="s">
+      <c r="D48" s="214" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="217" t="s">
+      <c r="E48" s="214" t="s">
         <v>8</v>
       </c>
-      <c r="F48" s="217"/>
+      <c r="F48" s="214"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="247"/>
+      <c r="A49" s="244"/>
       <c r="B49" s="98"/>
       <c r="C49" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C48),"""",HLOOKUP(REGEXEXTRACT(C48,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C48,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Soulfist")</f>
@@ -6935,8 +6926,8 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="247"/>
-      <c r="B50" s="218"/>
+      <c r="A50" s="244"/>
+      <c r="B50" s="215"/>
       <c r="C50" s="7">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C48),"""",HLOOKUP(REGEXEXTRACT(C48,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C48,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1750)</f>
         <v>1750</v>
@@ -6958,26 +6949,26 @@
       <c r="A51" s="49"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="246" t="s">
-        <v>0</v>
-      </c>
-      <c r="B52" s="219" t="s">
+      <c r="A52" s="243" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="216" t="s">
         <v>311</v>
       </c>
-      <c r="C52" s="217" t="s">
+      <c r="C52" s="214" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="217" t="s">
+      <c r="D52" s="214" t="s">
         <v>35</v>
       </c>
-      <c r="E52" s="217" t="s">
+      <c r="E52" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="F52" s="217"/>
+      <c r="F52" s="214"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="247"/>
-      <c r="B53" s="220"/>
+      <c r="A53" s="244"/>
+      <c r="B53" s="217"/>
       <c r="C53" s="48" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C52),"""",HLOOKUP(REGEXEXTRACT(C52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C52,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Deathblade")</f>
         <v>Deathblade</v>
@@ -6993,8 +6984,8 @@
       <c r="F53" s="48"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="247"/>
-      <c r="B54" s="221"/>
+      <c r="A54" s="244"/>
+      <c r="B54" s="218"/>
       <c r="C54" s="48">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C52),"""",HLOOKUP(REGEXEXTRACT(C52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C52,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1540)</f>
         <v>1540</v>
@@ -7010,22 +7001,22 @@
       <c r="F54" s="48"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="246"/>
-      <c r="B56" s="219" t="s">
+      <c r="A56" s="243"/>
+      <c r="B56" s="216" t="s">
         <v>311</v>
       </c>
-      <c r="C56" s="217" t="s">
+      <c r="C56" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="D56" s="217" t="s">
+      <c r="D56" s="214" t="s">
         <v>12</v>
       </c>
-      <c r="E56" s="217"/>
-      <c r="F56" s="217"/>
+      <c r="E56" s="214"/>
+      <c r="F56" s="214"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="247"/>
-      <c r="B57" s="220"/>
+      <c r="A57" s="244"/>
+      <c r="B57" s="217"/>
       <c r="C57" s="48" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C56),"""",HLOOKUP(REGEXEXTRACT(C56,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C56,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Wardancer")</f>
         <v>Wardancer</v>
@@ -7041,8 +7032,8 @@
       <c r="F57" s="48"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="247"/>
-      <c r="B58" s="221"/>
+      <c r="A58" s="244"/>
+      <c r="B58" s="218"/>
       <c r="C58" s="48">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C56),"""",HLOOKUP(REGEXEXTRACT(C56,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C56,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1620)</f>
         <v>1620</v>
@@ -7058,25 +7049,25 @@
       <c r="F58" s="48"/>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="246" t="s">
-        <v>0</v>
-      </c>
-      <c r="B63" s="206" t="s">
+      <c r="A63" s="243" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C63" s="217" t="s">
+      <c r="C63" s="214" t="s">
         <v>14</v>
       </c>
-      <c r="D63" s="217" t="s">
+      <c r="D63" s="214" t="s">
         <v>63</v>
       </c>
-      <c r="E63" s="217" t="s">
+      <c r="E63" s="214" t="s">
         <v>24</v>
       </c>
-      <c r="F63" s="217"/>
+      <c r="F63" s="214"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="247"/>
+      <c r="A64" s="244"/>
       <c r="B64" s="98"/>
       <c r="C64" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C63),"""",HLOOKUP(REGEXEXTRACT(C63,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C63,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Deathblade")</f>
@@ -7092,8 +7083,8 @@
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="247"/>
-      <c r="B65" s="218"/>
+      <c r="A65" s="244"/>
+      <c r="B65" s="215"/>
       <c r="C65" s="7">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C63),"""",HLOOKUP(REGEXEXTRACT(C63,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C63,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1540)</f>
         <v>1540</v>
@@ -7112,23 +7103,23 @@
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="246"/>
-      <c r="B67" s="206" t="s">
+      <c r="A67" s="243"/>
+      <c r="B67" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C67" s="217" t="s">
+      <c r="C67" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="D67" s="217" t="s">
+      <c r="D67" s="214" t="s">
         <v>27</v>
       </c>
-      <c r="E67" s="217" t="s">
+      <c r="E67" s="214" t="s">
         <v>40</v>
       </c>
-      <c r="F67" s="217"/>
+      <c r="F67" s="214"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="247"/>
+      <c r="A68" s="244"/>
       <c r="B68" s="98"/>
       <c r="C68" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C67),"""",HLOOKUP(REGEXEXTRACT(C67,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C67,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Wardancer")</f>
@@ -7144,8 +7135,8 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="247"/>
-      <c r="B69" s="218"/>
+      <c r="A69" s="244"/>
+      <c r="B69" s="215"/>
       <c r="C69" s="7">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C67),"""",HLOOKUP(REGEXEXTRACT(C67,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C67,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1620)</f>
         <v>1620</v>
@@ -7164,23 +7155,23 @@
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="246"/>
-      <c r="B71" s="206" t="s">
+      <c r="A71" s="243"/>
+      <c r="B71" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C71" s="217" t="s">
+      <c r="C71" s="214" t="s">
         <v>10</v>
       </c>
-      <c r="D71" s="217" t="s">
+      <c r="D71" s="214" t="s">
         <v>3</v>
       </c>
-      <c r="E71" s="217" t="s">
+      <c r="E71" s="214" t="s">
         <v>12</v>
       </c>
-      <c r="F71" s="217"/>
+      <c r="F71" s="214"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="247"/>
+      <c r="A72" s="244"/>
       <c r="B72" s="98"/>
       <c r="C72" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C71),"""",HLOOKUP(REGEXEXTRACT(C71,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C71,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Bard")</f>
@@ -7196,8 +7187,8 @@
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="247"/>
-      <c r="B73" s="218"/>
+      <c r="A73" s="244"/>
+      <c r="B73" s="215"/>
       <c r="C73" s="7">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C71),"""",HLOOKUP(REGEXEXTRACT(C71,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C71,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1560)</f>
         <v>1560</v>
@@ -7217,6 +7208,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="L5:L7"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A67:A69"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A29:A31"/>
@@ -7225,16 +7226,6 @@
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="A52:A54"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A10:A12"/>
   </mergeCells>
   <conditionalFormatting sqref="H2:H4 A2:A58 L5:L7 A63:A65 A67:A69 A71:A73">
     <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
@@ -7272,17 +7263,17 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="246"/>
-      <c r="B2" s="222" t="s">
+      <c r="A2" s="243"/>
+      <c r="B2" s="219" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="223" t="s">
+      <c r="C2" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="223" t="s">
+      <c r="D2" s="220" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="223" t="s">
+      <c r="E2" s="220" t="s">
         <v>315</v>
       </c>
       <c r="F2" s="53" t="s">
@@ -7290,8 +7281,8 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="247"/>
-      <c r="B3" s="224"/>
+      <c r="A3" s="244"/>
+      <c r="B3" s="221"/>
       <c r="C3" s="48" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C2),"""",HLOOKUP(REGEXEXTRACT(C2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C2,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Wardancer")</f>
         <v>Wardancer</v>
@@ -7303,52 +7294,52 @@
       <c r="E3" s="48" t="s">
         <v>317</v>
       </c>
-      <c r="F3" s="194" t="s">
+      <c r="F3" s="191" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="247"/>
-      <c r="B4" s="225"/>
-      <c r="C4" s="226">
+      <c r="A4" s="244"/>
+      <c r="B4" s="222"/>
+      <c r="C4" s="223">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C2),"""",HLOOKUP(REGEXEXTRACT(C2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C2,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1620)</f>
         <v>1620</v>
       </c>
-      <c r="D4" s="226">
+      <c r="D4" s="223">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D2),"""",HLOOKUP(REGEXEXTRACT(D2,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D2,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1600)</f>
         <v>1600</v>
       </c>
-      <c r="E4" s="195"/>
-      <c r="F4" s="196"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="193"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="B5" s="195"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="195"/>
-      <c r="E5" s="195"/>
-      <c r="F5" s="195"/>
+      <c r="B5" s="192"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="192"/>
+      <c r="F5" s="192"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="246"/>
-      <c r="B6" s="227" t="s">
+      <c r="A6" s="243"/>
+      <c r="B6" s="224" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="228" t="s">
+      <c r="C6" s="225" t="s">
         <v>319</v>
       </c>
-      <c r="D6" s="228" t="s">
+      <c r="D6" s="225" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="228" t="s">
+      <c r="E6" s="225" t="s">
         <v>315</v>
       </c>
-      <c r="F6" s="229" t="s">
+      <c r="F6" s="226" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="247"/>
-      <c r="B7" s="224"/>
+      <c r="A7" s="244"/>
+      <c r="B7" s="221"/>
       <c r="C7" s="48" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C6),"""",HLOOKUP(REGEXEXTRACT(C6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C6,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Reaper")</f>
         <v>Reaper</v>
@@ -7360,52 +7351,52 @@
       <c r="E7" s="48" t="s">
         <v>320</v>
       </c>
-      <c r="F7" s="194" t="s">
+      <c r="F7" s="191" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="247"/>
-      <c r="B8" s="225"/>
-      <c r="C8" s="226">
+      <c r="A8" s="244"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="223">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C6),"""",HLOOKUP(REGEXEXTRACT(C6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C6,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1520)</f>
         <v>1520</v>
       </c>
-      <c r="D8" s="226">
+      <c r="D8" s="223">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D6),"""",HLOOKUP(REGEXEXTRACT(D6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D6,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="E8" s="195"/>
-      <c r="F8" s="196"/>
+      <c r="E8" s="192"/>
+      <c r="F8" s="193"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="B9" s="195"/>
-      <c r="C9" s="195"/>
-      <c r="D9" s="195"/>
-      <c r="E9" s="195"/>
-      <c r="F9" s="195"/>
+      <c r="B9" s="192"/>
+      <c r="C9" s="192"/>
+      <c r="D9" s="192"/>
+      <c r="E9" s="192"/>
+      <c r="F9" s="192"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="246"/>
-      <c r="B10" s="227" t="s">
+      <c r="A10" s="243"/>
+      <c r="B10" s="224" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="228" t="s">
+      <c r="C10" s="225" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="228" t="s">
+      <c r="D10" s="225" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="228" t="s">
+      <c r="E10" s="225" t="s">
         <v>315</v>
       </c>
-      <c r="F10" s="229" t="s">
+      <c r="F10" s="226" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="247"/>
-      <c r="B11" s="230"/>
+      <c r="A11" s="244"/>
+      <c r="B11" s="227"/>
       <c r="C11" s="48" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C10),"""",HLOOKUP(REGEXEXTRACT(C10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C10,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
@@ -7417,52 +7408,52 @@
       <c r="E11" s="48" t="s">
         <v>322</v>
       </c>
-      <c r="F11" s="194" t="s">
+      <c r="F11" s="191" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="247"/>
-      <c r="B12" s="231"/>
-      <c r="C12" s="226" t="str">
+      <c r="A12" s="244"/>
+      <c r="B12" s="228"/>
+      <c r="C12" s="223" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C10),"""",HLOOKUP(REGEXEXTRACT(C10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C10,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="D12" s="226" t="str">
+      <c r="D12" s="223" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D10),"""",HLOOKUP(REGEXEXTRACT(D10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D10,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="E12" s="195"/>
-      <c r="F12" s="196"/>
+      <c r="E12" s="192"/>
+      <c r="F12" s="193"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="B13" s="195"/>
+      <c r="B13" s="192"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="246"/>
-      <c r="B14" s="232" t="s">
+      <c r="A14" s="243"/>
+      <c r="B14" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="228" t="s">
+      <c r="C14" s="225" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="228" t="s">
+      <c r="D14" s="225" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="228" t="s">
+      <c r="E14" s="225" t="s">
         <v>315</v>
       </c>
-      <c r="F14" s="229" t="s">
+      <c r="F14" s="226" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="247"/>
-      <c r="B15" s="230"/>
+      <c r="A15" s="244"/>
+      <c r="B15" s="227"/>
       <c r="C15" s="48" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C14),"""",HLOOKUP(REGEXEXTRACT(C14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C14,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
@@ -7474,52 +7465,52 @@
       <c r="E15" s="48" t="s">
         <v>324</v>
       </c>
-      <c r="F15" s="194" t="s">
+      <c r="F15" s="191" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="247"/>
-      <c r="B16" s="231"/>
-      <c r="C16" s="195" t="str">
+      <c r="A16" s="244"/>
+      <c r="B16" s="228"/>
+      <c r="C16" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C14),"""",HLOOKUP(REGEXEXTRACT(C14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C14,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="D16" s="226" t="str">
+      <c r="D16" s="223" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D14),"""",HLOOKUP(REGEXEXTRACT(D14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D14,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="E16" s="195"/>
-      <c r="F16" s="196"/>
+      <c r="E16" s="192"/>
+      <c r="F16" s="193"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="B17" s="195"/>
+      <c r="B17" s="192"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="246"/>
-      <c r="B18" s="227" t="s">
+      <c r="A18" s="243"/>
+      <c r="B18" s="224" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="228" t="s">
+      <c r="C18" s="225" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="228" t="s">
+      <c r="D18" s="225" t="s">
         <v>3</v>
       </c>
-      <c r="E18" s="228" t="s">
+      <c r="E18" s="225" t="s">
         <v>315</v>
       </c>
-      <c r="F18" s="229" t="s">
+      <c r="F18" s="226" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="247"/>
-      <c r="B19" s="233"/>
+      <c r="A19" s="244"/>
+      <c r="B19" s="230"/>
       <c r="C19" s="48" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C18),"""",HLOOKUP(REGEXEXTRACT(C18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C18,""(.*)-.*""),""!C3:L"")),2,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
@@ -7531,52 +7522,52 @@
       <c r="E19" s="48" t="s">
         <v>326</v>
       </c>
-      <c r="F19" s="194" t="s">
+      <c r="F19" s="191" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="247"/>
-      <c r="B20" s="234"/>
-      <c r="C20" s="195" t="str">
+      <c r="A20" s="244"/>
+      <c r="B20" s="231"/>
+      <c r="C20" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C18),"""",HLOOKUP(REGEXEXTRACT(C18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C18,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="D20" s="226">
+      <c r="D20" s="223">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D18),"""",HLOOKUP(REGEXEXTRACT(D18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D18,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1600)</f>
         <v>1600</v>
       </c>
-      <c r="E20" s="195"/>
-      <c r="F20" s="196"/>
+      <c r="E20" s="192"/>
+      <c r="F20" s="193"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="B21" s="195"/>
-      <c r="C21" s="195"/>
-      <c r="D21" s="195"/>
-      <c r="E21" s="195"/>
-      <c r="F21" s="195"/>
+      <c r="B21" s="192"/>
+      <c r="C21" s="192"/>
+      <c r="D21" s="192"/>
+      <c r="E21" s="192"/>
+      <c r="F21" s="192"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="246"/>
-      <c r="B22" s="227" t="s">
+      <c r="A22" s="243"/>
+      <c r="B22" s="224" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="228" t="s">
+      <c r="C22" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="228" t="s">
+      <c r="D22" s="225" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="228" t="s">
+      <c r="E22" s="225" t="s">
         <v>315</v>
       </c>
-      <c r="F22" s="229" t="s">
+      <c r="F22" s="226" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="247"/>
-      <c r="B23" s="233"/>
+      <c r="A23" s="244"/>
+      <c r="B23" s="230"/>
       <c r="C23" s="48" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C22),"""",HLOOKUP(REGEXEXTRACT(C22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C22,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
@@ -7588,33 +7579,33 @@
       <c r="E23" s="48" t="s">
         <v>321</v>
       </c>
-      <c r="F23" s="194" t="s">
+      <c r="F23" s="191" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="247"/>
-      <c r="B24" s="234"/>
-      <c r="C24" s="195" t="str">
+      <c r="A24" s="244"/>
+      <c r="B24" s="231"/>
+      <c r="C24" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C22),"""",HLOOKUP(REGEXEXTRACT(C22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C22,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="D24" s="226">
+      <c r="D24" s="223">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D22),"""",HLOOKUP(REGEXEXTRACT(D22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D22,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="E24" s="195"/>
-      <c r="F24" s="196"/>
+      <c r="E24" s="192"/>
+      <c r="F24" s="193"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="B25" s="195"/>
-      <c r="C25" s="195"/>
-      <c r="D25" s="195"/>
-      <c r="E25" s="195"/>
-      <c r="F25" s="195"/>
+      <c r="B25" s="192"/>
+      <c r="C25" s="192"/>
+      <c r="D25" s="192"/>
+      <c r="E25" s="192"/>
+      <c r="F25" s="192"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="246"/>
+      <c r="A26" s="243"/>
       <c r="B26" s="12" t="s">
         <v>1</v>
       </c>
@@ -7627,12 +7618,12 @@
       <c r="E26" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="229" t="s">
+      <c r="F26" s="226" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="247"/>
+      <c r="A27" s="244"/>
       <c r="B27" s="13"/>
       <c r="C27" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C26),"""",HLOOKUP(REGEXEXTRACT(C26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C26,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#REF!")</f>
@@ -7652,7 +7643,7 @@
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="247"/>
+      <c r="A28" s="244"/>
       <c r="B28" s="14"/>
       <c r="C28" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C26),"""",HLOOKUP(REGEXEXTRACT(C26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C26,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
@@ -7672,18 +7663,18 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="195"/>
-      <c r="C29" s="195"/>
-      <c r="D29" s="195"/>
-      <c r="E29" s="195"/>
-      <c r="F29" s="195"/>
+      <c r="B29" s="192"/>
+      <c r="C29" s="192"/>
+      <c r="D29" s="192"/>
+      <c r="E29" s="192"/>
+      <c r="F29" s="192"/>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="246"/>
+      <c r="A30" s="243"/>
       <c r="B30" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="228" t="s">
+      <c r="C30" s="225" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="5" t="s">
@@ -7697,7 +7688,7 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="247"/>
+      <c r="A31" s="244"/>
       <c r="B31" s="13"/>
       <c r="C31" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C30),"""",HLOOKUP(REGEXEXTRACT(C30,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C30,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#N/A")</f>
@@ -7717,7 +7708,7 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="247"/>
+      <c r="A32" s="244"/>
       <c r="B32" s="14"/>
       <c r="C32" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C30),"""",HLOOKUP(REGEXEXTRACT(C30,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C30,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#N/A")</f>
@@ -7737,33 +7728,33 @@
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="B33" s="195"/>
-      <c r="C33" s="195"/>
-      <c r="D33" s="195"/>
-      <c r="E33" s="195"/>
-      <c r="F33" s="195"/>
+      <c r="B33" s="192"/>
+      <c r="C33" s="192"/>
+      <c r="D33" s="192"/>
+      <c r="E33" s="192"/>
+      <c r="F33" s="192"/>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="246"/>
-      <c r="B34" s="232" t="s">
+      <c r="A34" s="243"/>
+      <c r="B34" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="228" t="s">
+      <c r="C34" s="225" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="228" t="s">
+      <c r="D34" s="225" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="228" t="s">
+      <c r="E34" s="225" t="s">
         <v>14</v>
       </c>
-      <c r="F34" s="228" t="s">
+      <c r="F34" s="225" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="247"/>
-      <c r="B35" s="235"/>
+      <c r="A35" s="244"/>
+      <c r="B35" s="232"/>
       <c r="C35" s="48" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C34),"""",HLOOKUP(REGEXEXTRACT(C34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C34,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
@@ -7776,33 +7767,33 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E34),"""",HLOOKUP(REGEXEXTRACT(E34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E34,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Deathblade")</f>
         <v>Deathblade</v>
       </c>
-      <c r="F35" s="194" t="str">
+      <c r="F35" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F34),"""",HLOOKUP(REGEXEXTRACT(F34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F34,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"Arcana")</f>
         <v>Arcana</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="247"/>
-      <c r="B36" s="236"/>
-      <c r="C36" s="195" t="str">
+      <c r="A36" s="244"/>
+      <c r="B36" s="233"/>
+      <c r="C36" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C34),"""",HLOOKUP(REGEXEXTRACT(C34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C34,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="D36" s="226">
+      <c r="D36" s="223">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D34),"""",HLOOKUP(REGEXEXTRACT(D34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D34,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
-      <c r="E36" s="226">
+      <c r="E36" s="223">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E34),"""",HLOOKUP(REGEXEXTRACT(E34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E34,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1540)</f>
         <v>1540</v>
       </c>
-      <c r="F36" s="237">
+      <c r="F36" s="234">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F34),"""",HLOOKUP(REGEXEXTRACT(F34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F34,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1560)</f>
         <v>1560</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="246"/>
+      <c r="A38" s="243"/>
       <c r="B38" s="12" t="s">
         <v>1</v>
       </c>
@@ -7820,7 +7811,7 @@
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="247"/>
+      <c r="A39" s="244"/>
       <c r="B39" s="15"/>
       <c r="C39" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C38),"""",HLOOKUP(REGEXEXTRACT(C38,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C38,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#N/A")</f>
@@ -7840,7 +7831,7 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="247"/>
+      <c r="A40" s="244"/>
       <c r="B40" s="16"/>
       <c r="C40" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C38),"""",HLOOKUP(REGEXEXTRACT(C38,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C38,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#N/A")</f>
@@ -7866,13 +7857,13 @@
       <c r="C42" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D42" s="228" t="s">
+      <c r="D42" s="225" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F42" s="228" t="s">
+      <c r="F42" s="225" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8070,7 +8061,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="207" t="s">
         <v>279</v>
       </c>
     </row>
@@ -8089,7 +8080,7 @@
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="210" t="s">
+      <c r="A4" s="207" t="s">
         <v>282</v>
       </c>
       <c r="G4" s="7"/>
@@ -8133,7 +8124,7 @@
       <c r="J8" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="K8" s="211" t="e">
+      <c r="K8" s="208" t="e">
         <f ca="1">IF(G8=H19,I20,H20)</f>
         <v>#NAME?</v>
       </c>
@@ -8162,13 +8153,13 @@
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="B11" s="212" t="s">
+      <c r="B11" s="209" t="s">
         <v>254</v>
       </c>
-      <c r="C11" s="212" t="s">
+      <c r="C11" s="209" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="212" t="s">
+      <c r="D11" s="209" t="s">
         <v>79</v>
       </c>
       <c r="G11" s="7" t="s">
@@ -8205,9 +8196,9 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="B13" s="213"/>
-      <c r="C13" s="213"/>
-      <c r="D13" s="213"/>
+      <c r="B13" s="210"/>
+      <c r="C13" s="210"/>
+      <c r="D13" s="210"/>
       <c r="G13" s="7" t="e">
         <f ca="1">_xludf.IFS(I12=H19,J19,I12=I19,J19,I12=J19,I19)</f>
         <v>#NAME?</v>
@@ -8228,144 +8219,144 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="B14" s="213"/>
-      <c r="C14" s="213"/>
-      <c r="D14" s="213"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="210"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="B15" s="213"/>
-      <c r="C15" s="213"/>
-      <c r="D15" s="213"/>
+      <c r="B15" s="210"/>
+      <c r="C15" s="210"/>
+      <c r="D15" s="210"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="B16" s="213"/>
-      <c r="C16" s="213"/>
-      <c r="D16" s="213"/>
-      <c r="F16" s="210"/>
+      <c r="B16" s="210"/>
+      <c r="C16" s="210"/>
+      <c r="D16" s="210"/>
+      <c r="F16" s="207"/>
       <c r="G16" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="H16" s="211">
+      <c r="H16" s="208">
         <f>SUM(B40:D40)</f>
         <v>22419.199999999997</v>
       </c>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="213"/>
-      <c r="C17" s="213"/>
-      <c r="D17" s="213"/>
+      <c r="B17" s="210"/>
+      <c r="C17" s="210"/>
+      <c r="D17" s="210"/>
       <c r="G17" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="H17" s="211">
+      <c r="H17" s="208">
         <f>H16/3</f>
         <v>7473.0666666666657</v>
       </c>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="213"/>
-      <c r="C18" s="213"/>
-      <c r="D18" s="213"/>
+      <c r="B18" s="210"/>
+      <c r="C18" s="210"/>
+      <c r="D18" s="210"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="213"/>
-      <c r="C19" s="213"/>
-      <c r="D19" s="213"/>
-      <c r="H19" s="212" t="e">
+      <c r="B19" s="210"/>
+      <c r="C19" s="210"/>
+      <c r="D19" s="210"/>
+      <c r="H19" s="209" t="e">
         <f t="shared" ref="H19:J19" ca="1" si="1">_xludf.CONCAT(B12,B11)</f>
         <v>#NAME?</v>
       </c>
-      <c r="I19" s="212" t="e">
+      <c r="I19" s="209" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#NAME?</v>
       </c>
-      <c r="J19" s="212" t="e">
+      <c r="J19" s="209" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#NAME?</v>
       </c>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="213"/>
-      <c r="C20" s="213"/>
-      <c r="D20" s="213"/>
+      <c r="B20" s="210"/>
+      <c r="C20" s="210"/>
+      <c r="D20" s="210"/>
       <c r="G20" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="H20" s="211">
+      <c r="H20" s="208">
         <f t="shared" ref="H20:J20" si="2">$H$17-B40</f>
         <v>461.61666666666588</v>
       </c>
-      <c r="I20" s="211">
+      <c r="I20" s="208">
         <f t="shared" si="2"/>
         <v>152.86666666666588</v>
       </c>
-      <c r="J20" s="211">
+      <c r="J20" s="208">
         <f t="shared" si="2"/>
         <v>-614.48333333333358</v>
       </c>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="213"/>
-      <c r="C21" s="213"/>
-      <c r="D21" s="213"/>
+      <c r="B21" s="210"/>
+      <c r="C21" s="210"/>
+      <c r="D21" s="210"/>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="213"/>
-      <c r="C22" s="213"/>
-      <c r="D22" s="213"/>
+      <c r="B22" s="210"/>
+      <c r="C22" s="210"/>
+      <c r="D22" s="210"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="213"/>
-      <c r="C23" s="213"/>
-      <c r="D23" s="213"/>
+      <c r="B23" s="210"/>
+      <c r="C23" s="210"/>
+      <c r="D23" s="210"/>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="213"/>
-      <c r="C24" s="213"/>
-      <c r="D24" s="213"/>
+      <c r="B24" s="210"/>
+      <c r="C24" s="210"/>
+      <c r="D24" s="210"/>
       <c r="J24" s="7"/>
     </row>
     <row r="25" spans="2:10">
-      <c r="B25" s="213"/>
-      <c r="C25" s="213"/>
-      <c r="D25" s="213"/>
+      <c r="B25" s="210"/>
+      <c r="C25" s="210"/>
+      <c r="D25" s="210"/>
       <c r="J25" s="7"/>
     </row>
     <row r="26" spans="2:10">
-      <c r="B26" s="213"/>
-      <c r="C26" s="213"/>
-      <c r="D26" s="213"/>
+      <c r="B26" s="210"/>
+      <c r="C26" s="210"/>
+      <c r="D26" s="210"/>
       <c r="J26" s="7"/>
     </row>
     <row r="27" spans="2:10">
-      <c r="B27" s="213"/>
-      <c r="C27" s="213"/>
-      <c r="D27" s="213"/>
+      <c r="B27" s="210"/>
+      <c r="C27" s="210"/>
+      <c r="D27" s="210"/>
       <c r="J27" s="7"/>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="213"/>
-      <c r="C28" s="213"/>
-      <c r="D28" s="213"/>
+      <c r="B28" s="210"/>
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
       <c r="F28" s="7"/>
       <c r="J28" s="7"/>
     </row>
     <row r="29" spans="2:10">
-      <c r="B29" s="213"/>
-      <c r="C29" s="213"/>
-      <c r="D29" s="213"/>
+      <c r="B29" s="210"/>
+      <c r="C29" s="210"/>
+      <c r="D29" s="210"/>
       <c r="J29" s="7"/>
     </row>
     <row r="30" spans="2:10">
-      <c r="B30" s="213"/>
-      <c r="C30" s="213"/>
-      <c r="D30" s="213"/>
+      <c r="B30" s="210"/>
+      <c r="C30" s="210"/>
+      <c r="D30" s="210"/>
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="2:10">
-      <c r="B31" s="213"/>
-      <c r="C31" s="213"/>
-      <c r="D31" s="213"/>
+      <c r="B31" s="210"/>
+      <c r="C31" s="210"/>
+      <c r="D31" s="210"/>
       <c r="J31" s="7"/>
     </row>
     <row r="32" spans="2:10">
@@ -8381,13 +8372,13 @@
       <c r="J32" s="7"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="B33" s="214">
+      <c r="B33" s="211">
         <v>50</v>
       </c>
-      <c r="C33" s="214">
+      <c r="C33" s="211">
         <v>50</v>
       </c>
-      <c r="D33" s="214">
+      <c r="D33" s="211">
         <v>150</v>
       </c>
       <c r="J33" s="7"/>
@@ -8405,13 +8396,13 @@
       <c r="J34" s="7"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="B35" s="214">
+      <c r="B35" s="211">
         <v>50</v>
       </c>
-      <c r="C35" s="214">
+      <c r="C35" s="211">
         <v>100</v>
       </c>
-      <c r="D35" s="214">
+      <c r="D35" s="211">
         <v>100</v>
       </c>
       <c r="J35" s="7"/>
@@ -8428,13 +8419,13 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="B37" s="215">
+      <c r="B37" s="212">
         <v>100</v>
       </c>
-      <c r="C37" s="215">
+      <c r="C37" s="212">
         <v>50</v>
       </c>
-      <c r="D37" s="215">
+      <c r="D37" s="212">
         <v>50</v>
       </c>
     </row>
@@ -8459,15 +8450,15 @@
       <c r="A39" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="B39" s="216">
+      <c r="B39" s="213">
         <f t="shared" ref="B39:D39" si="4">SUM(IF(ISNUMBER(B32),B32,0),IF(ISNUMBER(B34),B34,0),IF(ISNUMBER(B36),B36,0)) *0.95 - SUM(IF(ISNUMBER(B33),B33,0),IF(ISNUMBER(B35),B35,0),IF(ISNUMBER(B37),B37,0))</f>
         <v>7011.45</v>
       </c>
-      <c r="C39" s="216">
+      <c r="C39" s="213">
         <f t="shared" si="4"/>
         <v>7320.2</v>
       </c>
-      <c r="D39" s="216">
+      <c r="D39" s="213">
         <f t="shared" si="4"/>
         <v>8087.5499999999993</v>
       </c>
@@ -8476,15 +8467,15 @@
       <c r="A40" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B40" s="211">
+      <c r="B40" s="208">
         <f t="shared" ref="B40:D40" si="5">B38*0.95+B39</f>
         <v>7011.45</v>
       </c>
-      <c r="C40" s="211">
+      <c r="C40" s="208">
         <f t="shared" si="5"/>
         <v>7320.2</v>
       </c>
-      <c r="D40" s="211">
+      <c r="D40" s="208">
         <f t="shared" si="5"/>
         <v>8087.5499999999993</v>
       </c>
@@ -8494,7 +8485,7 @@
         <f t="shared" ref="A42:D42" ca="1" si="6">IF($H$3=1,G8,G12)</f>
         <v>#NAME?</v>
       </c>
-      <c r="B42" s="210" t="str">
+      <c r="B42" s="207" t="str">
         <f t="shared" si="6"/>
         <v>lists gem for</v>
       </c>
@@ -8502,11 +8493,11 @@
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
       </c>
-      <c r="D42" s="210" t="str">
+      <c r="D42" s="207" t="str">
         <f t="shared" si="6"/>
         <v>at price</v>
       </c>
-      <c r="E42" s="211" t="e">
+      <c r="E42" s="208" t="e">
         <f t="shared" ref="E42:E43" ca="1" si="7">ABS(IF($H$3=1,K8,K12))</f>
         <v>#NAME?</v>
       </c>
@@ -8516,7 +8507,7 @@
         <f t="shared" ref="A43:D43" ca="1" si="8">IF($H$3=1,G9,G13)</f>
         <v>#NAME?</v>
       </c>
-      <c r="B43" s="210" t="str">
+      <c r="B43" s="207" t="str">
         <f t="shared" si="8"/>
         <v>lists gem for</v>
       </c>
@@ -8524,11 +8515,11 @@
         <f t="shared" ca="1" si="8"/>
         <v>#NAME?</v>
       </c>
-      <c r="D43" s="210" t="str">
+      <c r="D43" s="207" t="str">
         <f t="shared" si="8"/>
         <v>at price</v>
       </c>
-      <c r="E43" s="211" t="e">
+      <c r="E43" s="208" t="e">
         <f t="shared" ca="1" si="7"/>
         <v>#NAME?</v>
       </c>
@@ -11769,7 +11760,7 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14">
-      <c r="A4" s="251" t="s">
+      <c r="A4" s="248" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="64" t="s">
@@ -11787,7 +11778,7 @@
       <c r="F4" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="H4" s="251" t="s">
+      <c r="H4" s="248" t="s">
         <v>0</v>
       </c>
       <c r="I4" s="65" t="s">
@@ -11807,7 +11798,7 @@
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="247"/>
+      <c r="A5" s="244"/>
       <c r="B5" s="66" t="s">
         <v>135</v>
       </c>
@@ -11827,7 +11818,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F4),"""",HLOOKUP(REGEXEXTRACT(F4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F4,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H5" s="247"/>
+      <c r="H5" s="244"/>
       <c r="I5" s="67" t="s">
         <v>136</v>
       </c>
@@ -11849,7 +11840,7 @@
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="247"/>
+      <c r="A6" s="244"/>
       <c r="B6" s="68"/>
       <c r="C6" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C4),"""",HLOOKUP(REGEXEXTRACT(C4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -11867,7 +11858,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F4),"""",HLOOKUP(REGEXEXTRACT(F4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H6" s="247"/>
+      <c r="H6" s="244"/>
       <c r="I6" s="69"/>
       <c r="J6" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J4),"""",HLOOKUP(REGEXEXTRACT(J4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -11887,7 +11878,7 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="251" t="s">
+      <c r="A8" s="248" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="70" t="s">
@@ -11905,10 +11896,10 @@
       <c r="F8" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="H8" s="252"/>
+      <c r="H8" s="249"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="247"/>
+      <c r="A9" s="244"/>
       <c r="B9" s="71" t="s">
         <v>137</v>
       </c>
@@ -11928,10 +11919,10 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F8),"""",HLOOKUP(REGEXEXTRACT(F8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F8,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Valk")</f>
         <v>Valk</v>
       </c>
-      <c r="H9" s="247"/>
+      <c r="H9" s="244"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="247"/>
+      <c r="A10" s="244"/>
       <c r="B10" s="72"/>
       <c r="C10" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C8),"""",HLOOKUP(REGEXEXTRACT(C8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C8,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -11949,7 +11940,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F8),"""",HLOOKUP(REGEXEXTRACT(F8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F8,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H10" s="247"/>
+      <c r="H10" s="244"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="73"/>
@@ -11968,7 +11959,7 @@
       <c r="N11" s="73"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="251" t="s">
+      <c r="A12" s="248" t="s">
         <v>0</v>
       </c>
       <c r="B12" s="64" t="s">
@@ -11986,7 +11977,7 @@
       <c r="F12" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="H12" s="251"/>
+      <c r="H12" s="248"/>
       <c r="I12" s="74" t="s">
         <v>138</v>
       </c>
@@ -12004,7 +11995,7 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="247"/>
+      <c r="A13" s="244"/>
       <c r="B13" s="66" t="s">
         <v>137</v>
       </c>
@@ -12024,7 +12015,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F12),"""",HLOOKUP(REGEXEXTRACT(F12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F12,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H13" s="247"/>
+      <c r="H13" s="244"/>
       <c r="I13" s="75" t="s">
         <v>137</v>
       </c>
@@ -12045,7 +12036,7 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="247"/>
+      <c r="A14" s="244"/>
       <c r="B14" s="68"/>
       <c r="C14" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C12),"""",HLOOKUP(REGEXEXTRACT(C12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -12063,7 +12054,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F12),"""",HLOOKUP(REGEXEXTRACT(F12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H14" s="247"/>
+      <c r="H14" s="244"/>
       <c r="I14" s="76"/>
       <c r="J14" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J12),"""",HLOOKUP(REGEXEXTRACT(J12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -12080,7 +12071,7 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="251" t="s">
+      <c r="A16" s="248" t="s">
         <v>0</v>
       </c>
       <c r="B16" s="64" t="s">
@@ -12098,7 +12089,7 @@
       <c r="F16" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="H16" s="251"/>
+      <c r="H16" s="248"/>
       <c r="I16" s="77" t="s">
         <v>138</v>
       </c>
@@ -12116,7 +12107,7 @@
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="247"/>
+      <c r="A17" s="244"/>
       <c r="B17" s="66" t="s">
         <v>137</v>
       </c>
@@ -12136,7 +12127,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F16),"""",HLOOKUP(REGEXEXTRACT(F16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F16,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H17" s="247"/>
+      <c r="H17" s="244"/>
       <c r="I17" s="78" t="s">
         <v>137</v>
       </c>
@@ -12157,7 +12148,7 @@
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="247"/>
+      <c r="A18" s="244"/>
       <c r="B18" s="68"/>
       <c r="C18" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C16),"""",HLOOKUP(REGEXEXTRACT(C16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C16,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -12175,7 +12166,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F16),"""",HLOOKUP(REGEXEXTRACT(F16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F16,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
-      <c r="H18" s="247"/>
+      <c r="H18" s="244"/>
       <c r="I18" s="79"/>
       <c r="J18" s="59"/>
       <c r="K18" s="59">
@@ -12192,7 +12183,7 @@
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="251"/>
+      <c r="A20" s="248"/>
       <c r="B20" s="70" t="s">
         <v>138</v>
       </c>
@@ -12208,7 +12199,7 @@
       <c r="F20" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="H20" s="251"/>
+      <c r="H20" s="248"/>
       <c r="I20" s="77" t="s">
         <v>138</v>
       </c>
@@ -12226,7 +12217,7 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="247"/>
+      <c r="A21" s="244"/>
       <c r="B21" s="71" t="s">
         <v>137</v>
       </c>
@@ -12246,7 +12237,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F20),"""",HLOOKUP(REGEXEXTRACT(F20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F20,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Paladin")</f>
         <v>Paladin</v>
       </c>
-      <c r="H21" s="247"/>
+      <c r="H21" s="244"/>
       <c r="I21" s="78" t="s">
         <v>137</v>
       </c>
@@ -12267,7 +12258,7 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="247"/>
+      <c r="A22" s="244"/>
       <c r="B22" s="72"/>
       <c r="C22" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C20),"""",HLOOKUP(REGEXEXTRACT(C20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C20,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -12285,7 +12276,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F20),"""",HLOOKUP(REGEXEXTRACT(F20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F20,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H22" s="247"/>
+      <c r="H22" s="244"/>
       <c r="I22" s="79"/>
       <c r="J22" s="59"/>
       <c r="K22" s="59">
@@ -12302,7 +12293,7 @@
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="252"/>
+      <c r="A24" s="249"/>
       <c r="B24" s="80" t="s">
         <v>138</v>
       </c>
@@ -12318,7 +12309,7 @@
       <c r="F24" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="H24" s="251" t="s">
+      <c r="H24" s="248" t="s">
         <v>0</v>
       </c>
       <c r="I24" s="65" t="s">
@@ -12338,7 +12329,7 @@
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="247"/>
+      <c r="A25" s="244"/>
       <c r="B25" s="81" t="s">
         <v>137</v>
       </c>
@@ -12358,7 +12349,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F24),"""",HLOOKUP(REGEXEXTRACT(F24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F24,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Bard")</f>
         <v>Bard</v>
       </c>
-      <c r="H25" s="247"/>
+      <c r="H25" s="244"/>
       <c r="I25" s="67" t="s">
         <v>137</v>
       </c>
@@ -12380,7 +12371,7 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="247"/>
+      <c r="A26" s="244"/>
       <c r="B26" s="82"/>
       <c r="C26" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C24),"""",HLOOKUP(REGEXEXTRACT(C24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C24,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -12398,7 +12389,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F24),"""",HLOOKUP(REGEXEXTRACT(F24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F24,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H26" s="247"/>
+      <c r="H26" s="244"/>
       <c r="I26" s="69"/>
       <c r="J26" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J24),"""",HLOOKUP(REGEXEXTRACT(J24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J24,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -12434,7 +12425,7 @@
       <c r="N27" s="73"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="251" t="s">
+      <c r="A28" s="248" t="s">
         <v>0</v>
       </c>
       <c r="B28" s="83" t="s">
@@ -12452,10 +12443,10 @@
       <c r="F28" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="H28" s="252"/>
+      <c r="H28" s="249"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="247"/>
+      <c r="A29" s="244"/>
       <c r="B29" s="84" t="s">
         <v>137</v>
       </c>
@@ -12475,10 +12466,10 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F28),"""",HLOOKUP(REGEXEXTRACT(F28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F28,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Valk")</f>
         <v>Valk</v>
       </c>
-      <c r="H29" s="247"/>
+      <c r="H29" s="244"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="247"/>
+      <c r="A30" s="244"/>
       <c r="B30" s="85"/>
       <c r="C30" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C28),"""",HLOOKUP(REGEXEXTRACT(C28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C28,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
@@ -12496,16 +12487,10 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F28),"""",HLOOKUP(REGEXEXTRACT(F28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F28,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
-      <c r="H30" s="247"/>
+      <c r="H30" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A24:A26"/>
@@ -12514,6 +12499,12 @@
     <mergeCell ref="H24:H26"/>
     <mergeCell ref="H28:H30"/>
     <mergeCell ref="H16:H18"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="H12:H14"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:A6 H4:H6 A8:A10 H8:H10 A12:A14 H12:H14 A16:A18 H16:H18 A20:A22 H20:H22 A24:A26 H24:H26 A28:A30 H28:H30">
     <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
@@ -17090,66 +17081,66 @@
       <c r="J2" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="P2" s="256" t="s">
+      <c r="P2" s="253" t="s">
         <v>538</v>
       </c>
-      <c r="Q2" s="247"/>
-      <c r="R2" s="247"/>
-      <c r="S2" s="247"/>
-      <c r="T2" s="247"/>
-      <c r="U2" s="247"/>
-      <c r="V2" s="247"/>
-      <c r="W2" s="247"/>
+      <c r="Q2" s="244"/>
+      <c r="R2" s="244"/>
+      <c r="S2" s="244"/>
+      <c r="T2" s="244"/>
+      <c r="U2" s="244"/>
+      <c r="V2" s="244"/>
+      <c r="W2" s="244"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
     </row>
     <row r="3" spans="1:26">
-      <c r="B3" s="206" t="s">
+      <c r="B3" s="203" t="s">
         <v>302</v>
       </c>
-      <c r="C3" s="191" t="s">
+      <c r="C3" s="188" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="192" t="s">
+      <c r="D3" s="189" t="s">
         <v>312</v>
       </c>
-      <c r="E3" s="192"/>
-      <c r="F3" s="192"/>
-      <c r="G3" s="192" t="s">
+      <c r="E3" s="189"/>
+      <c r="F3" s="189"/>
+      <c r="G3" s="189" t="s">
         <v>270</v>
       </c>
-      <c r="H3" s="192" t="s">
+      <c r="H3" s="189" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="192" t="s">
+      <c r="I3" s="189" t="s">
         <v>539</v>
       </c>
-      <c r="J3" s="193" t="s">
+      <c r="J3" s="190" t="s">
         <v>540</v>
       </c>
-      <c r="P3" s="238" t="s">
+      <c r="P3" s="235" t="s">
         <v>349</v>
       </c>
-      <c r="Q3" s="238" t="s">
+      <c r="Q3" s="235" t="s">
         <v>541</v>
       </c>
-      <c r="R3" s="238" t="s">
+      <c r="R3" s="235" t="s">
         <v>41</v>
       </c>
-      <c r="S3" s="238" t="s">
+      <c r="S3" s="235" t="s">
         <v>79</v>
       </c>
-      <c r="T3" s="238" t="s">
+      <c r="T3" s="235" t="s">
         <v>256</v>
       </c>
-      <c r="U3" s="238" t="s">
+      <c r="U3" s="235" t="s">
         <v>255</v>
       </c>
-      <c r="V3" s="238" t="s">
+      <c r="V3" s="235" t="s">
         <v>80</v>
       </c>
-      <c r="W3" s="238" t="s">
+      <c r="W3" s="235" t="s">
         <v>82</v>
       </c>
     </row>
@@ -17157,7 +17148,7 @@
       <c r="B4" s="98" t="s">
         <v>542</v>
       </c>
-      <c r="C4" s="232" t="str">
+      <c r="C4" s="229" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C3),"""",HLOOKUP(REGEXEXTRACT(C3,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C3,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Arcana")</f>
         <v>Arcana</v>
       </c>
@@ -17179,139 +17170,139 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I3),"""",HLOOKUP(REGEXEXTRACT(I3,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I3,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Reaper")</f>
         <v>Reaper</v>
       </c>
-      <c r="J4" s="194" t="str">
+      <c r="J4" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J3),"""",HLOOKUP(REGEXEXTRACT(J3,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J3,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="P4" s="239" t="s">
+      <c r="P4" s="236" t="s">
         <v>104</v>
       </c>
-      <c r="Q4" s="239">
+      <c r="Q4" s="236">
         <f t="shared" ref="Q4:Q26" si="0">SUM(R4:W4)</f>
         <v>6</v>
       </c>
-      <c r="R4" s="239">
+      <c r="R4" s="236">
         <v>3</v>
       </c>
-      <c r="S4" s="239">
+      <c r="S4" s="236">
         <v>1</v>
       </c>
-      <c r="T4" s="239">
+      <c r="T4" s="236">
         <v>1</v>
       </c>
-      <c r="U4" s="239">
+      <c r="U4" s="236">
         <v>1</v>
       </c>
-      <c r="V4" s="239">
-        <v>0</v>
-      </c>
-      <c r="W4" s="239">
+      <c r="V4" s="236">
+        <v>0</v>
+      </c>
+      <c r="W4" s="236">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:26">
-      <c r="B5" s="218"/>
-      <c r="C5" s="240">
+      <c r="B5" s="215"/>
+      <c r="C5" s="237">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C3),"""",HLOOKUP(REGEXEXTRACT(C3,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C3,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1570)</f>
         <v>1570</v>
       </c>
-      <c r="D5" s="195" t="str">
+      <c r="D5" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D3),"""",HLOOKUP(REGEXEXTRACT(D3,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D3,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="E5" s="195"/>
-      <c r="F5" s="195"/>
-      <c r="G5" s="195">
+      <c r="E5" s="192"/>
+      <c r="F5" s="192"/>
+      <c r="G5" s="192">
         <v>1477.5</v>
       </c>
-      <c r="H5" s="195">
+      <c r="H5" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H3),"""",HLOOKUP(REGEXEXTRACT(H3,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H3,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1540)</f>
         <v>1540</v>
       </c>
-      <c r="I5" s="195">
+      <c r="I5" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I3),"""",HLOOKUP(REGEXEXTRACT(I3,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I3,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1490)</f>
         <v>1490</v>
       </c>
-      <c r="J5" s="196" t="str">
+      <c r="J5" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J3),"""",HLOOKUP(REGEXEXTRACT(J3,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J3,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="P5" s="241" t="s">
+      <c r="P5" s="238" t="s">
         <v>395</v>
       </c>
-      <c r="Q5" s="241">
+      <c r="Q5" s="238">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="R5" s="241">
+      <c r="R5" s="238">
         <v>1</v>
       </c>
-      <c r="S5" s="241">
+      <c r="S5" s="238">
         <v>1</v>
       </c>
-      <c r="T5" s="241">
+      <c r="T5" s="238">
         <v>1</v>
       </c>
-      <c r="U5" s="241">
+      <c r="U5" s="238">
         <v>1</v>
       </c>
-      <c r="V5" s="241">
-        <v>0</v>
-      </c>
-      <c r="W5" s="241">
+      <c r="V5" s="238">
+        <v>0</v>
+      </c>
+      <c r="W5" s="238">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:26">
-      <c r="B6" s="206" t="s">
+      <c r="B6" s="203" t="s">
         <v>302</v>
       </c>
-      <c r="C6" s="191" t="s">
+      <c r="C6" s="188" t="s">
         <v>319</v>
       </c>
-      <c r="D6" s="192" t="s">
+      <c r="D6" s="189" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="192"/>
-      <c r="F6" s="192"/>
-      <c r="G6" s="192" t="s">
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="189" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="192" t="s">
+      <c r="H6" s="189" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="192" t="s">
+      <c r="I6" s="189" t="s">
         <v>543</v>
       </c>
-      <c r="J6" s="193" t="s">
+      <c r="J6" s="190" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="257" t="s">
+      <c r="N6" s="254" t="s">
         <v>544</v>
       </c>
-      <c r="P6" s="239" t="s">
+      <c r="P6" s="236" t="s">
         <v>351</v>
       </c>
-      <c r="Q6" s="239">
+      <c r="Q6" s="236">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="R6" s="239">
-        <v>0</v>
-      </c>
-      <c r="S6" s="239">
+      <c r="R6" s="236">
+        <v>0</v>
+      </c>
+      <c r="S6" s="236">
         <v>1</v>
       </c>
-      <c r="T6" s="239">
+      <c r="T6" s="236">
         <v>2</v>
       </c>
-      <c r="U6" s="239">
+      <c r="U6" s="236">
         <v>1</v>
       </c>
-      <c r="V6" s="239">
+      <c r="V6" s="236">
         <v>1</v>
       </c>
-      <c r="W6" s="239">
+      <c r="W6" s="236">
         <v>0</v>
       </c>
     </row>
@@ -17319,7 +17310,7 @@
       <c r="B7" s="98" t="s">
         <v>545</v>
       </c>
-      <c r="C7" s="232" t="str">
+      <c r="C7" s="229" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C6),"""",HLOOKUP(REGEXEXTRACT(C6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C6,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Reaper")</f>
         <v>Reaper</v>
       </c>
@@ -17341,143 +17332,143 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I6),"""",HLOOKUP(REGEXEXTRACT(I6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I6,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Sole(fish)")</f>
         <v>Sole(fish)</v>
       </c>
-      <c r="J7" s="242" t="str">
+      <c r="J7" s="239" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J6),"""",HLOOKUP(REGEXEXTRACT(J6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J6,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="N7" s="247"/>
-      <c r="P7" s="241" t="s">
+      <c r="N7" s="244"/>
+      <c r="P7" s="238" t="s">
         <v>96</v>
       </c>
-      <c r="Q7" s="241">
+      <c r="Q7" s="238">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R7" s="241">
-        <v>0</v>
-      </c>
-      <c r="S7" s="241">
-        <v>0</v>
-      </c>
-      <c r="T7" s="241">
+      <c r="R7" s="238">
+        <v>0</v>
+      </c>
+      <c r="S7" s="238">
+        <v>0</v>
+      </c>
+      <c r="T7" s="238">
         <v>1</v>
       </c>
-      <c r="U7" s="241">
-        <v>0</v>
-      </c>
-      <c r="V7" s="241">
+      <c r="U7" s="238">
+        <v>0</v>
+      </c>
+      <c r="V7" s="238">
         <v>1</v>
       </c>
-      <c r="W7" s="241">
+      <c r="W7" s="238">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:26">
-      <c r="B8" s="218"/>
-      <c r="C8" s="240">
+      <c r="B8" s="215"/>
+      <c r="C8" s="237">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C6),"""",HLOOKUP(REGEXEXTRACT(C6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C6,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1520)</f>
         <v>1520</v>
       </c>
-      <c r="D8" s="195">
+      <c r="D8" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D6),"""",HLOOKUP(REGEXEXTRACT(D6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D6,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
-      <c r="E8" s="195" t="str">
+      <c r="E8" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E6),"""",HLOOKUP(REGEXEXTRACT(E6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E6,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="F8" s="195"/>
-      <c r="G8" s="195" t="str">
+      <c r="F8" s="192"/>
+      <c r="G8" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G6),"""",HLOOKUP(REGEXEXTRACT(G6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G6,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="H8" s="195">
+      <c r="H8" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H6),"""",HLOOKUP(REGEXEXTRACT(H6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H6,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="I8" s="195">
+      <c r="I8" s="192">
         <v>1475</v>
       </c>
       <c r="J8" s="11" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J6),"""",HLOOKUP(REGEXEXTRACT(J6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J6,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="P8" s="239" t="s">
+      <c r="P8" s="236" t="s">
         <v>355</v>
       </c>
-      <c r="Q8" s="239">
+      <c r="Q8" s="236">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R8" s="239">
+      <c r="R8" s="236">
         <v>1</v>
       </c>
-      <c r="S8" s="239">
+      <c r="S8" s="236">
         <v>1</v>
       </c>
-      <c r="T8" s="239">
-        <v>0</v>
-      </c>
-      <c r="U8" s="239">
-        <v>0</v>
-      </c>
-      <c r="V8" s="239">
+      <c r="T8" s="236">
+        <v>0</v>
+      </c>
+      <c r="U8" s="236">
+        <v>0</v>
+      </c>
+      <c r="V8" s="236">
         <v>1</v>
       </c>
-      <c r="W8" s="239">
+      <c r="W8" s="236">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:26">
-      <c r="B9" s="206" t="s">
+      <c r="B9" s="203" t="s">
         <v>302</v>
       </c>
-      <c r="C9" s="217" t="s">
+      <c r="C9" s="214" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="217" t="s">
+      <c r="D9" s="214" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="217"/>
-      <c r="F9" s="217"/>
-      <c r="G9" s="217" t="s">
+      <c r="E9" s="214"/>
+      <c r="F9" s="214"/>
+      <c r="G9" s="214" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="217" t="s">
+      <c r="H9" s="214" t="s">
         <v>546</v>
       </c>
-      <c r="I9" s="217" t="s">
+      <c r="I9" s="214" t="s">
         <v>547</v>
       </c>
-      <c r="J9" s="243" t="s">
+      <c r="J9" s="240" t="s">
         <v>548</v>
       </c>
       <c r="N9" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="P9" s="241" t="s">
+      <c r="P9" s="238" t="s">
         <v>359</v>
       </c>
-      <c r="Q9" s="241">
+      <c r="Q9" s="238">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R9" s="241">
+      <c r="R9" s="238">
         <v>1</v>
       </c>
-      <c r="S9" s="241">
-        <v>0</v>
-      </c>
-      <c r="T9" s="241">
-        <v>0</v>
-      </c>
-      <c r="U9" s="241">
-        <v>0</v>
-      </c>
-      <c r="V9" s="241">
+      <c r="S9" s="238">
+        <v>0</v>
+      </c>
+      <c r="T9" s="238">
+        <v>0</v>
+      </c>
+      <c r="U9" s="238">
+        <v>0</v>
+      </c>
+      <c r="V9" s="238">
         <v>1</v>
       </c>
-      <c r="W9" s="241">
+      <c r="W9" s="238">
         <v>0</v>
       </c>
     </row>
@@ -17508,41 +17499,41 @@
       <c r="I10" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="J10" s="242" t="str">
+      <c r="J10" s="239" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J9),"""",HLOOKUP(REGEXEXTRACT(J9,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J9,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="P10" s="239" t="s">
+      <c r="P10" s="236" t="s">
         <v>408</v>
       </c>
-      <c r="Q10" s="239">
+      <c r="Q10" s="236">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R10" s="239">
-        <v>0</v>
-      </c>
-      <c r="S10" s="239">
+      <c r="R10" s="236">
+        <v>0</v>
+      </c>
+      <c r="S10" s="236">
         <v>1</v>
       </c>
-      <c r="T10" s="239">
+      <c r="T10" s="236">
         <v>1</v>
       </c>
-      <c r="U10" s="239">
-        <v>0</v>
-      </c>
-      <c r="V10" s="239">
-        <v>0</v>
-      </c>
-      <c r="W10" s="239">
+      <c r="U10" s="236">
+        <v>0</v>
+      </c>
+      <c r="V10" s="236">
+        <v>0</v>
+      </c>
+      <c r="W10" s="236">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:26">
-      <c r="B11" s="218"/>
+      <c r="B11" s="215"/>
       <c r="C11" s="10">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C9),"""",HLOOKUP(REGEXEXTRACT(C9,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C9,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1540)</f>
         <v>1540</v>
@@ -17555,7 +17546,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E9),"""",HLOOKUP(REGEXEXTRACT(E9,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E9,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="F11" s="244"/>
+      <c r="F11" s="241"/>
       <c r="G11" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G9),"""",HLOOKUP(REGEXEXTRACT(G9,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G9,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
@@ -17574,106 +17565,106 @@
       <c r="N11" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="P11" s="241" t="s">
+      <c r="P11" s="238" t="s">
         <v>553</v>
       </c>
-      <c r="Q11" s="241">
+      <c r="Q11" s="238">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R11" s="241">
-        <v>0</v>
-      </c>
-      <c r="S11" s="241">
-        <v>0</v>
-      </c>
-      <c r="T11" s="241">
-        <v>0</v>
-      </c>
-      <c r="U11" s="241">
+      <c r="R11" s="238">
+        <v>0</v>
+      </c>
+      <c r="S11" s="238">
+        <v>0</v>
+      </c>
+      <c r="T11" s="238">
+        <v>0</v>
+      </c>
+      <c r="U11" s="238">
         <v>1</v>
       </c>
-      <c r="V11" s="241">
+      <c r="V11" s="238">
         <v>1</v>
       </c>
-      <c r="W11" s="241">
+      <c r="W11" s="238">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:26">
-      <c r="P12" s="239" t="s">
+      <c r="P12" s="236" t="s">
         <v>357</v>
       </c>
-      <c r="Q12" s="239">
+      <c r="Q12" s="236">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R12" s="239">
+      <c r="R12" s="236">
         <v>1</v>
       </c>
-      <c r="S12" s="239">
-        <v>0</v>
-      </c>
-      <c r="T12" s="239">
+      <c r="S12" s="236">
+        <v>0</v>
+      </c>
+      <c r="T12" s="236">
         <v>1</v>
       </c>
-      <c r="U12" s="239">
-        <v>0</v>
-      </c>
-      <c r="V12" s="239">
-        <v>0</v>
-      </c>
-      <c r="W12" s="239">
+      <c r="U12" s="236">
+        <v>0</v>
+      </c>
+      <c r="V12" s="236">
+        <v>0</v>
+      </c>
+      <c r="W12" s="236">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:26">
-      <c r="B13" s="206" t="s">
+      <c r="B13" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="191" t="s">
+      <c r="C13" s="188" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="192" t="s">
+      <c r="D13" s="189" t="s">
         <v>312</v>
       </c>
-      <c r="E13" s="192"/>
-      <c r="F13" s="192"/>
-      <c r="G13" s="192" t="s">
+      <c r="E13" s="189"/>
+      <c r="F13" s="189"/>
+      <c r="G13" s="189" t="s">
         <v>270</v>
       </c>
-      <c r="H13" s="192" t="s">
+      <c r="H13" s="189" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="192" t="s">
+      <c r="I13" s="189" t="s">
         <v>554</v>
       </c>
-      <c r="J13" s="193" t="s">
+      <c r="J13" s="190" t="s">
         <v>540</v>
       </c>
-      <c r="P13" s="241" t="s">
+      <c r="P13" s="238" t="s">
         <v>352</v>
       </c>
-      <c r="Q13" s="241">
+      <c r="Q13" s="238">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R13" s="241">
-        <v>0</v>
-      </c>
-      <c r="S13" s="241">
-        <v>0</v>
-      </c>
-      <c r="T13" s="241">
-        <v>0</v>
-      </c>
-      <c r="U13" s="241">
-        <v>0</v>
-      </c>
-      <c r="V13" s="241">
+      <c r="R13" s="238">
+        <v>0</v>
+      </c>
+      <c r="S13" s="238">
+        <v>0</v>
+      </c>
+      <c r="T13" s="238">
+        <v>0</v>
+      </c>
+      <c r="U13" s="238">
+        <v>0</v>
+      </c>
+      <c r="V13" s="238">
         <v>1</v>
       </c>
-      <c r="W13" s="241">
+      <c r="W13" s="238">
         <v>1</v>
       </c>
     </row>
@@ -17681,7 +17672,7 @@
       <c r="B14" s="98" t="s">
         <v>550</v>
       </c>
-      <c r="C14" s="232" t="str">
+      <c r="C14" s="229" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C13),"""",HLOOKUP(REGEXEXTRACT(C13,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C13,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Wardancer")</f>
         <v>Wardancer</v>
       </c>
@@ -17706,96 +17697,96 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I13),"""",HLOOKUP(REGEXEXTRACT(I13,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I13,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Wardancer")</f>
         <v>Wardancer</v>
       </c>
-      <c r="J14" s="194" t="str">
+      <c r="J14" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J13),"""",HLOOKUP(REGEXEXTRACT(J13,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J13,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="P14" s="239" t="s">
+      <c r="P14" s="236" t="s">
         <v>354</v>
       </c>
-      <c r="Q14" s="239">
+      <c r="Q14" s="236">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R14" s="239">
+      <c r="R14" s="236">
         <v>1</v>
       </c>
-      <c r="S14" s="239">
-        <v>0</v>
-      </c>
-      <c r="T14" s="239">
-        <v>0</v>
-      </c>
-      <c r="U14" s="239">
-        <v>0</v>
-      </c>
-      <c r="V14" s="239">
+      <c r="S14" s="236">
+        <v>0</v>
+      </c>
+      <c r="T14" s="236">
+        <v>0</v>
+      </c>
+      <c r="U14" s="236">
+        <v>0</v>
+      </c>
+      <c r="V14" s="236">
         <v>1</v>
       </c>
-      <c r="W14" s="239">
+      <c r="W14" s="236">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:26">
-      <c r="B15" s="218"/>
-      <c r="C15" s="240">
+      <c r="B15" s="215"/>
+      <c r="C15" s="237">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C13),"""",HLOOKUP(REGEXEXTRACT(C13,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C13,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1620)</f>
         <v>1620</v>
       </c>
-      <c r="D15" s="195" t="str">
+      <c r="D15" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D13),"""",HLOOKUP(REGEXEXTRACT(D13,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D13,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="E15" s="195" t="str">
+      <c r="E15" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E13),"""",HLOOKUP(REGEXEXTRACT(E13,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E13,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="F15" s="245"/>
-      <c r="G15" s="195" t="str">
+      <c r="F15" s="242"/>
+      <c r="G15" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G13),"""",HLOOKUP(REGEXEXTRACT(G13,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G13,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="H15" s="195">
+      <c r="H15" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H13),"""",HLOOKUP(REGEXEXTRACT(H13,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H13,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1540)</f>
         <v>1540</v>
       </c>
-      <c r="I15" s="195">
+      <c r="I15" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I13),"""",HLOOKUP(REGEXEXTRACT(I13,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I13,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1460)</f>
         <v>1460</v>
       </c>
-      <c r="J15" s="196" t="str">
+      <c r="J15" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J13),"""",HLOOKUP(REGEXEXTRACT(J13,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J13,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>556</v>
       </c>
-      <c r="P15" s="241" t="s">
+      <c r="P15" s="238" t="s">
         <v>322</v>
       </c>
-      <c r="Q15" s="241">
+      <c r="Q15" s="238">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R15" s="241">
+      <c r="R15" s="238">
         <v>1</v>
       </c>
-      <c r="S15" s="241">
-        <v>0</v>
-      </c>
-      <c r="T15" s="241">
-        <v>0</v>
-      </c>
-      <c r="U15" s="241">
+      <c r="S15" s="238">
+        <v>0</v>
+      </c>
+      <c r="T15" s="238">
+        <v>0</v>
+      </c>
+      <c r="U15" s="238">
         <v>1</v>
       </c>
-      <c r="V15" s="241">
-        <v>0</v>
-      </c>
-      <c r="W15" s="241">
+      <c r="V15" s="238">
+        <v>0</v>
+      </c>
+      <c r="W15" s="238">
         <v>1</v>
       </c>
     </row>
@@ -17803,24 +17794,24 @@
       <c r="B16" s="98" t="s">
         <v>314</v>
       </c>
-      <c r="C16" s="191" t="s">
+      <c r="C16" s="188" t="s">
         <v>313</v>
       </c>
-      <c r="D16" s="192" t="s">
+      <c r="D16" s="189" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="192"/>
-      <c r="F16" s="192"/>
-      <c r="G16" s="192" t="s">
+      <c r="E16" s="189"/>
+      <c r="F16" s="189"/>
+      <c r="G16" s="189" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="192" t="s">
+      <c r="H16" s="189" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="192" t="s">
+      <c r="I16" s="189" t="s">
         <v>543</v>
       </c>
-      <c r="J16" s="193" t="s">
+      <c r="J16" s="190" t="s">
         <v>26</v>
       </c>
       <c r="M16" s="7" t="s">
@@ -17829,29 +17820,29 @@
       <c r="N16" s="7" t="s">
         <v>558</v>
       </c>
-      <c r="P16" s="239" t="s">
+      <c r="P16" s="236" t="s">
         <v>559</v>
       </c>
-      <c r="Q16" s="239">
+      <c r="Q16" s="236">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="R16" s="239">
-        <v>0</v>
-      </c>
-      <c r="S16" s="239">
-        <v>0</v>
-      </c>
-      <c r="T16" s="239">
+      <c r="R16" s="236">
+        <v>0</v>
+      </c>
+      <c r="S16" s="236">
+        <v>0</v>
+      </c>
+      <c r="T16" s="236">
         <v>1</v>
       </c>
-      <c r="U16" s="239">
-        <v>0</v>
-      </c>
-      <c r="V16" s="239">
-        <v>0</v>
-      </c>
-      <c r="W16" s="239">
+      <c r="U16" s="236">
+        <v>0</v>
+      </c>
+      <c r="V16" s="236">
+        <v>0</v>
+      </c>
+      <c r="W16" s="236">
         <v>1</v>
       </c>
     </row>
@@ -17859,7 +17850,7 @@
       <c r="B17" s="98" t="s">
         <v>550</v>
       </c>
-      <c r="C17" s="232" t="str">
+      <c r="C17" s="229" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C16),"""",HLOOKUP(REGEXEXTRACT(C16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C16,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
@@ -17884,95 +17875,95 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I16),"""",HLOOKUP(REGEXEXTRACT(I16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I16,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"Sole(fish)")</f>
         <v>Sole(fish)</v>
       </c>
-      <c r="J17" s="194" t="str">
+      <c r="J17" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J16),"""",HLOOKUP(REGEXEXTRACT(J16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J16,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="P17" s="241" t="s">
+      <c r="P17" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="Q17" s="241">
+      <c r="Q17" s="238">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R17" s="241">
-        <v>0</v>
-      </c>
-      <c r="S17" s="241">
-        <v>0</v>
-      </c>
-      <c r="T17" s="241">
-        <v>0</v>
-      </c>
-      <c r="U17" s="241">
-        <v>0</v>
-      </c>
-      <c r="V17" s="241">
-        <v>0</v>
-      </c>
-      <c r="W17" s="241">
+      <c r="R17" s="238">
+        <v>0</v>
+      </c>
+      <c r="S17" s="238">
+        <v>0</v>
+      </c>
+      <c r="T17" s="238">
+        <v>0</v>
+      </c>
+      <c r="U17" s="238">
+        <v>0</v>
+      </c>
+      <c r="V17" s="238">
+        <v>0</v>
+      </c>
+      <c r="W17" s="238">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:23">
-      <c r="B18" s="218"/>
-      <c r="C18" s="240" t="str">
+      <c r="B18" s="215"/>
+      <c r="C18" s="237" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C16),"""",HLOOKUP(REGEXEXTRACT(C16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C16,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="D18" s="195">
+      <c r="D18" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D16),"""",HLOOKUP(REGEXEXTRACT(D16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D16,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
-      <c r="E18" s="195" t="str">
+      <c r="E18" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E16),"""",HLOOKUP(REGEXEXTRACT(E16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E16,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="F18" s="195"/>
-      <c r="G18" s="195">
+      <c r="F18" s="192"/>
+      <c r="G18" s="192">
         <v>1460</v>
       </c>
-      <c r="H18" s="195">
+      <c r="H18" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H16),"""",HLOOKUP(REGEXEXTRACT(H16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H16,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="I18" s="195">
+      <c r="I18" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I16),"""",HLOOKUP(REGEXEXTRACT(I16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I16,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1487.5)</f>
         <v>1487.5</v>
       </c>
-      <c r="J18" s="196" t="str">
+      <c r="J18" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J16),"""",HLOOKUP(REGEXEXTRACT(J16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J16,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="P18" s="239" t="s">
+      <c r="P18" s="236" t="s">
         <v>397</v>
       </c>
-      <c r="Q18" s="239">
+      <c r="Q18" s="236">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R18" s="239">
-        <v>0</v>
-      </c>
-      <c r="S18" s="239">
+      <c r="R18" s="236">
+        <v>0</v>
+      </c>
+      <c r="S18" s="236">
         <v>1</v>
       </c>
-      <c r="T18" s="239">
-        <v>0</v>
-      </c>
-      <c r="U18" s="239">
-        <v>0</v>
-      </c>
-      <c r="V18" s="239">
-        <v>0</v>
-      </c>
-      <c r="W18" s="239">
+      <c r="T18" s="236">
+        <v>0</v>
+      </c>
+      <c r="U18" s="236">
+        <v>0</v>
+      </c>
+      <c r="V18" s="236">
+        <v>0</v>
+      </c>
+      <c r="W18" s="236">
         <v>0</v>
       </c>
     </row>
@@ -17980,52 +17971,52 @@
       <c r="B19" s="98" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="217" t="s">
+      <c r="C19" s="214" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="217" t="s">
+      <c r="D19" s="214" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="217"/>
-      <c r="F19" s="217"/>
-      <c r="G19" s="217" t="s">
+      <c r="E19" s="214"/>
+      <c r="F19" s="214"/>
+      <c r="G19" s="214" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="217" t="s">
+      <c r="H19" s="214" t="s">
         <v>546</v>
       </c>
-      <c r="I19" s="217" t="s">
+      <c r="I19" s="214" t="s">
         <v>547</v>
       </c>
-      <c r="J19" s="243" t="s">
+      <c r="J19" s="240" t="s">
         <v>548</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="P19" s="241" t="s">
+      <c r="P19" s="238" t="s">
         <v>508</v>
       </c>
-      <c r="Q19" s="241">
+      <c r="Q19" s="238">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R19" s="241">
-        <v>0</v>
-      </c>
-      <c r="S19" s="241">
-        <v>0</v>
-      </c>
-      <c r="T19" s="241">
-        <v>0</v>
-      </c>
-      <c r="U19" s="241">
+      <c r="R19" s="238">
+        <v>0</v>
+      </c>
+      <c r="S19" s="238">
+        <v>0</v>
+      </c>
+      <c r="T19" s="238">
+        <v>0</v>
+      </c>
+      <c r="U19" s="238">
         <v>1</v>
       </c>
-      <c r="V19" s="241">
-        <v>0</v>
-      </c>
-      <c r="W19" s="241">
+      <c r="V19" s="238">
+        <v>0</v>
+      </c>
+      <c r="W19" s="238">
         <v>0</v>
       </c>
     </row>
@@ -18056,41 +18047,41 @@
       <c r="I20" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="J20" s="242" t="str">
+      <c r="J20" s="239" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J19),"""",HLOOKUP(REGEXEXTRACT(J19,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J19,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="P20" s="239" t="s">
+      <c r="P20" s="236" t="s">
         <v>506</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="236">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R20" s="239">
-        <v>0</v>
-      </c>
-      <c r="S20" s="239">
-        <v>0</v>
-      </c>
-      <c r="T20" s="239">
-        <v>0</v>
-      </c>
-      <c r="U20" s="239">
-        <v>0</v>
-      </c>
-      <c r="V20" s="239">
-        <v>0</v>
-      </c>
-      <c r="W20" s="239">
+      <c r="R20" s="236">
+        <v>0</v>
+      </c>
+      <c r="S20" s="236">
+        <v>0</v>
+      </c>
+      <c r="T20" s="236">
+        <v>0</v>
+      </c>
+      <c r="U20" s="236">
+        <v>0</v>
+      </c>
+      <c r="V20" s="236">
+        <v>0</v>
+      </c>
+      <c r="W20" s="236">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:23">
-      <c r="B21" s="218"/>
+      <c r="B21" s="215"/>
       <c r="C21" s="10">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C19),"""",HLOOKUP(REGEXEXTRACT(C19,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C19,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1540)</f>
         <v>1540</v>
@@ -18122,73 +18113,73 @@
       <c r="M21" s="7" t="s">
         <v>564</v>
       </c>
-      <c r="P21" s="241" t="s">
+      <c r="P21" s="238" t="s">
         <v>377</v>
       </c>
-      <c r="Q21" s="241">
+      <c r="Q21" s="238">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R21" s="241">
-        <v>0</v>
-      </c>
-      <c r="S21" s="241">
-        <v>0</v>
-      </c>
-      <c r="T21" s="241">
-        <v>0</v>
-      </c>
-      <c r="U21" s="241">
-        <v>0</v>
-      </c>
-      <c r="V21" s="241">
-        <v>0</v>
-      </c>
-      <c r="W21" s="241">
+      <c r="R21" s="238">
+        <v>0</v>
+      </c>
+      <c r="S21" s="238">
+        <v>0</v>
+      </c>
+      <c r="T21" s="238">
+        <v>0</v>
+      </c>
+      <c r="U21" s="238">
+        <v>0</v>
+      </c>
+      <c r="V21" s="238">
+        <v>0</v>
+      </c>
+      <c r="W21" s="238">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:23">
-      <c r="B22" s="206" t="s">
+      <c r="B22" s="203" t="s">
         <v>314</v>
       </c>
-      <c r="C22" s="217"/>
-      <c r="D22" s="217"/>
-      <c r="E22" s="217"/>
-      <c r="F22" s="217"/>
-      <c r="G22" s="217"/>
-      <c r="H22" s="217"/>
-      <c r="I22" s="217"/>
-      <c r="J22" s="243"/>
+      <c r="C22" s="214"/>
+      <c r="D22" s="214"/>
+      <c r="E22" s="214"/>
+      <c r="F22" s="214"/>
+      <c r="G22" s="214"/>
+      <c r="H22" s="214"/>
+      <c r="I22" s="214"/>
+      <c r="J22" s="240"/>
       <c r="M22" s="7" t="s">
         <v>565</v>
       </c>
       <c r="N22" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="P22" s="239" t="s">
+      <c r="P22" s="236" t="s">
         <v>396</v>
       </c>
-      <c r="Q22" s="239">
+      <c r="Q22" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R22" s="239">
-        <v>0</v>
-      </c>
-      <c r="S22" s="239">
-        <v>0</v>
-      </c>
-      <c r="T22" s="239">
-        <v>0</v>
-      </c>
-      <c r="U22" s="239">
-        <v>0</v>
-      </c>
-      <c r="V22" s="239">
-        <v>0</v>
-      </c>
-      <c r="W22" s="239">
+      <c r="R22" s="236">
+        <v>0</v>
+      </c>
+      <c r="S22" s="236">
+        <v>0</v>
+      </c>
+      <c r="T22" s="236">
+        <v>0</v>
+      </c>
+      <c r="U22" s="236">
+        <v>0</v>
+      </c>
+      <c r="V22" s="236">
+        <v>0</v>
+      </c>
+      <c r="W22" s="236">
         <v>0</v>
       </c>
     </row>
@@ -18224,41 +18215,41 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I22),"""",HLOOKUP(REGEXEXTRACT(I22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I22,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J23" s="242" t="str">
+      <c r="J23" s="239" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J22),"""",HLOOKUP(REGEXEXTRACT(J22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J22,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
       <c r="M23" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="P23" s="241" t="s">
+      <c r="P23" s="238" t="s">
         <v>507</v>
       </c>
-      <c r="Q23" s="241">
+      <c r="Q23" s="238">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R23" s="241">
-        <v>0</v>
-      </c>
-      <c r="S23" s="241">
-        <v>0</v>
-      </c>
-      <c r="T23" s="241">
-        <v>0</v>
-      </c>
-      <c r="U23" s="241">
-        <v>0</v>
-      </c>
-      <c r="V23" s="241">
-        <v>0</v>
-      </c>
-      <c r="W23" s="241">
+      <c r="R23" s="238">
+        <v>0</v>
+      </c>
+      <c r="S23" s="238">
+        <v>0</v>
+      </c>
+      <c r="T23" s="238">
+        <v>0</v>
+      </c>
+      <c r="U23" s="238">
+        <v>0</v>
+      </c>
+      <c r="V23" s="238">
+        <v>0</v>
+      </c>
+      <c r="W23" s="238">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:23">
-      <c r="B24" s="218"/>
+      <c r="B24" s="215"/>
       <c r="C24" s="7" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C22),"""",HLOOKUP(REGEXEXTRACT(C22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C22,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
@@ -18287,36 +18278,36 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I22),"""",HLOOKUP(REGEXEXTRACT(I22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I22,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J24" s="242" t="str">
+      <c r="J24" s="239" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J22),"""",HLOOKUP(REGEXEXTRACT(J22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J22,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
       <c r="M24" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="P24" s="239" t="s">
+      <c r="P24" s="236" t="s">
         <v>567</v>
       </c>
-      <c r="Q24" s="239">
+      <c r="Q24" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R24" s="239">
-        <v>0</v>
-      </c>
-      <c r="S24" s="239">
-        <v>0</v>
-      </c>
-      <c r="T24" s="239">
-        <v>0</v>
-      </c>
-      <c r="U24" s="239">
-        <v>0</v>
-      </c>
-      <c r="V24" s="239">
-        <v>0</v>
-      </c>
-      <c r="W24" s="239">
+      <c r="R24" s="236">
+        <v>0</v>
+      </c>
+      <c r="S24" s="236">
+        <v>0</v>
+      </c>
+      <c r="T24" s="236">
+        <v>0</v>
+      </c>
+      <c r="U24" s="236">
+        <v>0</v>
+      </c>
+      <c r="V24" s="236">
+        <v>0</v>
+      </c>
+      <c r="W24" s="236">
         <v>0</v>
       </c>
     </row>
@@ -18324,40 +18315,40 @@
       <c r="B25" s="98" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="217"/>
-      <c r="D25" s="217"/>
-      <c r="E25" s="217"/>
-      <c r="F25" s="217"/>
-      <c r="G25" s="217"/>
-      <c r="H25" s="217"/>
-      <c r="I25" s="217"/>
-      <c r="J25" s="243"/>
+      <c r="C25" s="214"/>
+      <c r="D25" s="214"/>
+      <c r="E25" s="214"/>
+      <c r="F25" s="214"/>
+      <c r="G25" s="214"/>
+      <c r="H25" s="214"/>
+      <c r="I25" s="214"/>
+      <c r="J25" s="240"/>
       <c r="M25" s="7" t="s">
         <v>568</v>
       </c>
-      <c r="P25" s="241" t="s">
+      <c r="P25" s="238" t="s">
         <v>379</v>
       </c>
-      <c r="Q25" s="241">
+      <c r="Q25" s="238">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R25" s="241">
-        <v>0</v>
-      </c>
-      <c r="S25" s="241">
-        <v>0</v>
-      </c>
-      <c r="T25" s="241">
-        <v>0</v>
-      </c>
-      <c r="U25" s="241">
-        <v>0</v>
-      </c>
-      <c r="V25" s="241">
-        <v>0</v>
-      </c>
-      <c r="W25" s="241">
+      <c r="R25" s="238">
+        <v>0</v>
+      </c>
+      <c r="S25" s="238">
+        <v>0</v>
+      </c>
+      <c r="T25" s="238">
+        <v>0</v>
+      </c>
+      <c r="U25" s="238">
+        <v>0</v>
+      </c>
+      <c r="V25" s="238">
+        <v>0</v>
+      </c>
+      <c r="W25" s="238">
         <v>0</v>
       </c>
     </row>
@@ -18393,38 +18384,38 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I25),"""",HLOOKUP(REGEXEXTRACT(I25,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I25,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J26" s="242" t="str">
+      <c r="J26" s="239" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J25),"""",HLOOKUP(REGEXEXTRACT(J25,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J25,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="P26" s="239" t="s">
+      <c r="P26" s="236" t="s">
         <v>356</v>
       </c>
-      <c r="Q26" s="239">
+      <c r="Q26" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R26" s="239">
-        <v>0</v>
-      </c>
-      <c r="S26" s="239">
-        <v>0</v>
-      </c>
-      <c r="T26" s="239">
-        <v>0</v>
-      </c>
-      <c r="U26" s="239">
-        <v>0</v>
-      </c>
-      <c r="V26" s="239">
-        <v>0</v>
-      </c>
-      <c r="W26" s="239">
+      <c r="R26" s="236">
+        <v>0</v>
+      </c>
+      <c r="S26" s="236">
+        <v>0</v>
+      </c>
+      <c r="T26" s="236">
+        <v>0</v>
+      </c>
+      <c r="U26" s="236">
+        <v>0</v>
+      </c>
+      <c r="V26" s="236">
+        <v>0</v>
+      </c>
+      <c r="W26" s="236">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:23">
-      <c r="B27" s="218"/>
+      <c r="B27" s="215"/>
       <c r="C27" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C25),"""",HLOOKUP(REGEXEXTRACT(C25,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C25,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
@@ -18459,23 +18450,23 @@
       </c>
     </row>
     <row r="29" spans="2:23">
-      <c r="B29" s="206" t="s">
+      <c r="B29" s="203" t="s">
         <v>305</v>
       </c>
-      <c r="C29" s="191"/>
-      <c r="D29" s="192"/>
-      <c r="E29" s="192"/>
-      <c r="F29" s="192"/>
-      <c r="G29" s="192"/>
-      <c r="H29" s="192"/>
-      <c r="I29" s="192"/>
-      <c r="J29" s="193"/>
+      <c r="C29" s="188"/>
+      <c r="D29" s="189"/>
+      <c r="E29" s="189"/>
+      <c r="F29" s="189"/>
+      <c r="G29" s="189"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="189"/>
+      <c r="J29" s="190"/>
     </row>
     <row r="30" spans="2:23">
       <c r="B30" s="98" t="s">
         <v>550</v>
       </c>
-      <c r="C30" s="232" t="str">
+      <c r="C30" s="229" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C29),"""",HLOOKUP(REGEXEXTRACT(C29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C29,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
@@ -18503,58 +18494,58 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I29),"""",HLOOKUP(REGEXEXTRACT(I29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I29,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J30" s="194" t="str">
+      <c r="J30" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J29),"""",HLOOKUP(REGEXEXTRACT(J29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J29,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" spans="2:23">
-      <c r="B31" s="218"/>
-      <c r="C31" s="240" t="str">
+      <c r="B31" s="215"/>
+      <c r="C31" s="237" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C29),"""",HLOOKUP(REGEXEXTRACT(C29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C29,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="D31" s="195" t="str">
+      <c r="D31" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D29),"""",HLOOKUP(REGEXEXTRACT(D29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D29,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="E31" s="195" t="str">
+      <c r="E31" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E29),"""",HLOOKUP(REGEXEXTRACT(E29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E29,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="F31" s="195" t="str">
+      <c r="F31" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F29),"""",HLOOKUP(REGEXEXTRACT(F29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F29,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="G31" s="195" t="str">
+      <c r="G31" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G29),"""",HLOOKUP(REGEXEXTRACT(G29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G29,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="H31" s="195" t="str">
+      <c r="H31" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H29),"""",HLOOKUP(REGEXEXTRACT(H29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H29,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="I31" s="195" t="str">
+      <c r="I31" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I29),"""",HLOOKUP(REGEXEXTRACT(I29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I29,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J31" s="196" t="str">
+      <c r="J31" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J29),"""",HLOOKUP(REGEXEXTRACT(J29,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J29,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" spans="2:23">
-      <c r="B32" s="206" t="s">
+      <c r="B32" s="203" t="s">
         <v>305</v>
       </c>
-      <c r="C32" s="217"/>
-      <c r="D32" s="217"/>
-      <c r="E32" s="217"/>
-      <c r="F32" s="217"/>
-      <c r="G32" s="217"/>
-      <c r="H32" s="217"/>
-      <c r="I32" s="217"/>
-      <c r="J32" s="243"/>
+      <c r="C32" s="214"/>
+      <c r="D32" s="214"/>
+      <c r="E32" s="214"/>
+      <c r="F32" s="214"/>
+      <c r="G32" s="214"/>
+      <c r="H32" s="214"/>
+      <c r="I32" s="214"/>
+      <c r="J32" s="240"/>
     </row>
     <row r="33" spans="2:10">
       <c r="B33" s="98" t="s">
@@ -18588,13 +18579,13 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I32),"""",HLOOKUP(REGEXEXTRACT(I32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I32,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J33" s="242" t="str">
+      <c r="J33" s="239" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J32),"""",HLOOKUP(REGEXEXTRACT(J32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J32,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" spans="2:10">
-      <c r="B34" s="218"/>
+      <c r="B34" s="215"/>
       <c r="C34" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C32),"""",HLOOKUP(REGEXEXTRACT(C32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C32,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
@@ -18629,17 +18620,17 @@
       </c>
     </row>
     <row r="35" spans="2:10">
-      <c r="B35" s="206" t="s">
+      <c r="B35" s="203" t="s">
         <v>305</v>
       </c>
-      <c r="C35" s="217"/>
-      <c r="D35" s="217"/>
-      <c r="E35" s="217"/>
-      <c r="F35" s="217"/>
-      <c r="G35" s="217"/>
-      <c r="H35" s="217"/>
-      <c r="I35" s="217"/>
-      <c r="J35" s="243"/>
+      <c r="C35" s="214"/>
+      <c r="D35" s="214"/>
+      <c r="E35" s="214"/>
+      <c r="F35" s="214"/>
+      <c r="G35" s="214"/>
+      <c r="H35" s="214"/>
+      <c r="I35" s="214"/>
+      <c r="J35" s="240"/>
     </row>
     <row r="36" spans="2:10">
       <c r="B36" s="98" t="s">
@@ -18673,13 +18664,13 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I35),"""",HLOOKUP(REGEXEXTRACT(I35,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I35,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J36" s="242" t="str">
+      <c r="J36" s="239" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J35),"""",HLOOKUP(REGEXEXTRACT(J35,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J35,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="37" spans="2:10">
-      <c r="B37" s="218"/>
+      <c r="B37" s="215"/>
       <c r="C37" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C35),"""",HLOOKUP(REGEXEXTRACT(C35,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C35,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
@@ -18757,7 +18748,7 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14">
-      <c r="A4" s="251"/>
+      <c r="A4" s="248"/>
       <c r="B4" s="64" t="s">
         <v>134</v>
       </c>
@@ -18773,7 +18764,7 @@
       <c r="F4" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="H4" s="251"/>
+      <c r="H4" s="248"/>
       <c r="I4" s="65" t="s">
         <v>134</v>
       </c>
@@ -18791,7 +18782,7 @@
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="247"/>
+      <c r="A5" s="244"/>
       <c r="B5" s="66" t="s">
         <v>135</v>
       </c>
@@ -18811,7 +18802,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F4),"""",HLOOKUP(REGEXEXTRACT(F4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F4,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H5" s="247"/>
+      <c r="H5" s="244"/>
       <c r="I5" s="67" t="s">
         <v>136</v>
       </c>
@@ -18833,7 +18824,7 @@
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="247"/>
+      <c r="A6" s="244"/>
       <c r="B6" s="68"/>
       <c r="C6" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C4),"""",HLOOKUP(REGEXEXTRACT(C4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -18851,7 +18842,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F4),"""",HLOOKUP(REGEXEXTRACT(F4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H6" s="247"/>
+      <c r="H6" s="244"/>
       <c r="I6" s="69"/>
       <c r="J6" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J4),"""",HLOOKUP(REGEXEXTRACT(J4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -18871,7 +18862,7 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="251"/>
+      <c r="A8" s="248"/>
       <c r="B8" s="70" t="s">
         <v>134</v>
       </c>
@@ -18887,10 +18878,10 @@
       <c r="F8" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="H8" s="252"/>
+      <c r="H8" s="249"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="247"/>
+      <c r="A9" s="244"/>
       <c r="B9" s="71" t="s">
         <v>137</v>
       </c>
@@ -18910,10 +18901,10 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F8),"""",HLOOKUP(REGEXEXTRACT(F8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F8,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Valk")</f>
         <v>Valk</v>
       </c>
-      <c r="H9" s="247"/>
+      <c r="H9" s="244"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="247"/>
+      <c r="A10" s="244"/>
       <c r="B10" s="72"/>
       <c r="C10" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C8),"""",HLOOKUP(REGEXEXTRACT(C8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C8,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -18931,7 +18922,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F8),"""",HLOOKUP(REGEXEXTRACT(F8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F8,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H10" s="247"/>
+      <c r="H10" s="244"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="73"/>
@@ -18950,7 +18941,7 @@
       <c r="N11" s="73"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="251"/>
+      <c r="A12" s="248"/>
       <c r="B12" s="64" t="s">
         <v>138</v>
       </c>
@@ -18966,7 +18957,7 @@
       <c r="F12" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="H12" s="251"/>
+      <c r="H12" s="248"/>
       <c r="I12" s="74" t="s">
         <v>138</v>
       </c>
@@ -18984,7 +18975,7 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="247"/>
+      <c r="A13" s="244"/>
       <c r="B13" s="66" t="s">
         <v>137</v>
       </c>
@@ -19004,7 +18995,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F12),"""",HLOOKUP(REGEXEXTRACT(F12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F12,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H13" s="247"/>
+      <c r="H13" s="244"/>
       <c r="I13" s="75" t="s">
         <v>137</v>
       </c>
@@ -19025,7 +19016,7 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="247"/>
+      <c r="A14" s="244"/>
       <c r="B14" s="68"/>
       <c r="C14" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C12),"""",HLOOKUP(REGEXEXTRACT(C12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19043,7 +19034,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F12),"""",HLOOKUP(REGEXEXTRACT(F12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H14" s="247"/>
+      <c r="H14" s="244"/>
       <c r="I14" s="76"/>
       <c r="J14" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J12),"""",HLOOKUP(REGEXEXTRACT(J12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19060,7 +19051,7 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="251"/>
+      <c r="A16" s="248"/>
       <c r="B16" s="64" t="s">
         <v>138</v>
       </c>
@@ -19076,7 +19067,7 @@
       <c r="F16" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="H16" s="251"/>
+      <c r="H16" s="248"/>
       <c r="I16" s="77" t="s">
         <v>138</v>
       </c>
@@ -19094,7 +19085,7 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="247"/>
+      <c r="A17" s="244"/>
       <c r="B17" s="66" t="s">
         <v>137</v>
       </c>
@@ -19114,7 +19105,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F16),"""",HLOOKUP(REGEXEXTRACT(F16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F16,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H17" s="247"/>
+      <c r="H17" s="244"/>
       <c r="I17" s="78" t="s">
         <v>137</v>
       </c>
@@ -19135,7 +19126,7 @@
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="247"/>
+      <c r="A18" s="244"/>
       <c r="B18" s="68"/>
       <c r="C18" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C16),"""",HLOOKUP(REGEXEXTRACT(C16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C16,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19153,7 +19144,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F16),"""",HLOOKUP(REGEXEXTRACT(F16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F16,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
-      <c r="H18" s="247"/>
+      <c r="H18" s="244"/>
       <c r="I18" s="79"/>
       <c r="J18" s="59"/>
       <c r="K18" s="59">
@@ -19170,7 +19161,7 @@
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="251"/>
+      <c r="A20" s="248"/>
       <c r="B20" s="86" t="s">
         <v>138</v>
       </c>
@@ -19186,7 +19177,7 @@
       <c r="F20" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="H20" s="251"/>
+      <c r="H20" s="248"/>
       <c r="I20" s="77" t="s">
         <v>138</v>
       </c>
@@ -19204,7 +19195,7 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="247"/>
+      <c r="A21" s="244"/>
       <c r="B21" s="87" t="s">
         <v>137</v>
       </c>
@@ -19224,7 +19215,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F20),"""",HLOOKUP(REGEXEXTRACT(F20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F20,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Paladin")</f>
         <v>Paladin</v>
       </c>
-      <c r="H21" s="247"/>
+      <c r="H21" s="244"/>
       <c r="I21" s="78" t="s">
         <v>137</v>
       </c>
@@ -19245,7 +19236,7 @@
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="247"/>
+      <c r="A22" s="244"/>
       <c r="B22" s="88"/>
       <c r="C22" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C20),"""",HLOOKUP(REGEXEXTRACT(C20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C20,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19263,7 +19254,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F20),"""",HLOOKUP(REGEXEXTRACT(F20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F20,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H22" s="247"/>
+      <c r="H22" s="244"/>
       <c r="I22" s="79"/>
       <c r="J22" s="59"/>
       <c r="K22" s="59">
@@ -19280,7 +19271,7 @@
       </c>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="251"/>
+      <c r="A24" s="248"/>
       <c r="B24" s="86" t="s">
         <v>138</v>
       </c>
@@ -19296,7 +19287,7 @@
       <c r="F24" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="H24" s="253"/>
+      <c r="H24" s="250"/>
       <c r="I24" s="89" t="s">
         <v>138</v>
       </c>
@@ -19314,7 +19305,7 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="247"/>
+      <c r="A25" s="244"/>
       <c r="B25" s="87" t="s">
         <v>137</v>
       </c>
@@ -19334,7 +19325,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F24),"""",HLOOKUP(REGEXEXTRACT(F24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F24,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Valk")</f>
         <v>Valk</v>
       </c>
-      <c r="H25" s="249"/>
+      <c r="H25" s="246"/>
       <c r="I25" s="90" t="s">
         <v>137</v>
       </c>
@@ -19356,7 +19347,7 @@
       </c>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="247"/>
+      <c r="A26" s="244"/>
       <c r="B26" s="88"/>
       <c r="C26" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C24),"""",HLOOKUP(REGEXEXTRACT(C24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C24,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19374,7 +19365,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F24),"""",HLOOKUP(REGEXEXTRACT(F24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F24,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H26" s="249"/>
+      <c r="H26" s="246"/>
       <c r="I26" s="91"/>
       <c r="J26" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J24),"""",HLOOKUP(REGEXEXTRACT(J24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J24,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19394,7 +19385,7 @@
       </c>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="251"/>
+      <c r="A28" s="248"/>
       <c r="B28" s="83" t="s">
         <v>138</v>
       </c>
@@ -19410,10 +19401,10 @@
       <c r="F28" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="H28" s="252"/>
+      <c r="H28" s="249"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="247"/>
+      <c r="A29" s="244"/>
       <c r="B29" s="84" t="s">
         <v>137</v>
       </c>
@@ -19433,10 +19424,10 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F28),"""",HLOOKUP(REGEXEXTRACT(F28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F28,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Bard")</f>
         <v>Bard</v>
       </c>
-      <c r="H29" s="247"/>
+      <c r="H29" s="244"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="247"/>
+      <c r="A30" s="244"/>
       <c r="B30" s="85"/>
       <c r="C30" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C28),"""",HLOOKUP(REGEXEXTRACT(C28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C28,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
@@ -19454,16 +19445,10 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F28),"""",HLOOKUP(REGEXEXTRACT(F28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F28,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1700)</f>
         <v>1700</v>
       </c>
-      <c r="H30" s="247"/>
+      <c r="H30" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A24:A26"/>
@@ -19472,6 +19457,12 @@
     <mergeCell ref="H24:H26"/>
     <mergeCell ref="H28:H30"/>
     <mergeCell ref="H16:H18"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="H12:H14"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:A6 H4:H6 A8:A10 H8:H10 A12:A14 H12:H14 A16:A18 H16:H18 A20:A22 H20:H22 A24:A26 H24:H26 A28:A30 H28:H30">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
@@ -19564,7 +19555,7 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14">
-      <c r="A4" s="251"/>
+      <c r="A4" s="248"/>
       <c r="B4" s="64" t="s">
         <v>134</v>
       </c>
@@ -19580,7 +19571,7 @@
       <c r="F4" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="H4" s="251"/>
+      <c r="H4" s="248"/>
       <c r="I4" s="65" t="s">
         <v>134</v>
       </c>
@@ -19598,7 +19589,7 @@
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="247"/>
+      <c r="A5" s="244"/>
       <c r="B5" s="66" t="s">
         <v>135</v>
       </c>
@@ -19618,7 +19609,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F4),"""",HLOOKUP(REGEXEXTRACT(F4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F4,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H5" s="247"/>
+      <c r="H5" s="244"/>
       <c r="I5" s="67" t="s">
         <v>136</v>
       </c>
@@ -19640,7 +19631,7 @@
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="247"/>
+      <c r="A6" s="244"/>
       <c r="B6" s="68"/>
       <c r="C6" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C4),"""",HLOOKUP(REGEXEXTRACT(C4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19658,7 +19649,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F4),"""",HLOOKUP(REGEXEXTRACT(F4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H6" s="247"/>
+      <c r="H6" s="244"/>
       <c r="I6" s="69"/>
       <c r="J6" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J4),"""",HLOOKUP(REGEXEXTRACT(J4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19678,7 +19669,7 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="251"/>
+      <c r="A8" s="248"/>
       <c r="B8" s="64" t="s">
         <v>134</v>
       </c>
@@ -19694,7 +19685,7 @@
       <c r="F8" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="H8" s="251"/>
+      <c r="H8" s="248"/>
       <c r="I8" s="70" t="s">
         <v>134</v>
       </c>
@@ -19712,7 +19703,7 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="247"/>
+      <c r="A9" s="244"/>
       <c r="B9" s="66" t="s">
         <v>137</v>
       </c>
@@ -19732,7 +19723,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F8),"""",HLOOKUP(REGEXEXTRACT(F8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F8,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H9" s="247"/>
+      <c r="H9" s="244"/>
       <c r="I9" s="71" t="s">
         <v>137</v>
       </c>
@@ -19754,7 +19745,7 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="247"/>
+      <c r="A10" s="244"/>
       <c r="B10" s="68"/>
       <c r="C10" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C8),"""",HLOOKUP(REGEXEXTRACT(C8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C8,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19772,7 +19763,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F8),"""",HLOOKUP(REGEXEXTRACT(F8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F8,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
-      <c r="H10" s="247"/>
+      <c r="H10" s="244"/>
       <c r="I10" s="72"/>
       <c r="J10" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J8),"""",HLOOKUP(REGEXEXTRACT(J8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J8,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19808,7 +19799,7 @@
       <c r="N11" s="73"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="251"/>
+      <c r="A12" s="248"/>
       <c r="B12" s="64" t="s">
         <v>138</v>
       </c>
@@ -19824,7 +19815,7 @@
       <c r="F12" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="H12" s="251"/>
+      <c r="H12" s="248"/>
       <c r="I12" s="65" t="s">
         <v>138</v>
       </c>
@@ -19842,7 +19833,7 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="247"/>
+      <c r="A13" s="244"/>
       <c r="B13" s="66" t="s">
         <v>137</v>
       </c>
@@ -19862,7 +19853,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F12),"""",HLOOKUP(REGEXEXTRACT(F12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F12,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H13" s="247"/>
+      <c r="H13" s="244"/>
       <c r="I13" s="67" t="s">
         <v>137</v>
       </c>
@@ -19884,7 +19875,7 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="247"/>
+      <c r="A14" s="244"/>
       <c r="B14" s="68"/>
       <c r="C14" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C12),"""",HLOOKUP(REGEXEXTRACT(C12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19902,7 +19893,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F12),"""",HLOOKUP(REGEXEXTRACT(F12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H14" s="247"/>
+      <c r="H14" s="244"/>
       <c r="I14" s="69"/>
       <c r="J14" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J12),"""",HLOOKUP(REGEXEXTRACT(J12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -19922,7 +19913,7 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="253"/>
+      <c r="A16" s="250"/>
       <c r="B16" s="92" t="s">
         <v>138</v>
       </c>
@@ -19938,7 +19929,7 @@
       <c r="F16" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="H16" s="251"/>
+      <c r="H16" s="248"/>
       <c r="I16" s="77" t="s">
         <v>138</v>
       </c>
@@ -19956,7 +19947,7 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="249"/>
+      <c r="A17" s="246"/>
       <c r="B17" s="93" t="s">
         <v>137</v>
       </c>
@@ -19975,7 +19966,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F16),"""",HLOOKUP(REGEXEXTRACT(F16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F16,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Bard")</f>
         <v>Bard</v>
       </c>
-      <c r="H17" s="247"/>
+      <c r="H17" s="244"/>
       <c r="I17" s="78" t="s">
         <v>137</v>
       </c>
@@ -19996,7 +19987,7 @@
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="249"/>
+      <c r="A18" s="246"/>
       <c r="B18" s="94"/>
       <c r="C18" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C16),"""",HLOOKUP(REGEXEXTRACT(C16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C16,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -20011,7 +20002,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F16),"""",HLOOKUP(REGEXEXTRACT(F16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F16,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H18" s="247"/>
+      <c r="H18" s="244"/>
       <c r="I18" s="79"/>
       <c r="J18" s="59"/>
       <c r="K18" s="59">
@@ -20028,7 +20019,7 @@
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="251"/>
+      <c r="A20" s="248"/>
       <c r="B20" s="95" t="s">
         <v>138</v>
       </c>
@@ -20044,7 +20035,7 @@
       <c r="F20" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="H20" s="251"/>
+      <c r="H20" s="248"/>
       <c r="I20" s="77" t="s">
         <v>138</v>
       </c>
@@ -20062,7 +20053,7 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="247"/>
+      <c r="A21" s="244"/>
       <c r="B21" s="96" t="s">
         <v>137</v>
       </c>
@@ -20082,7 +20073,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F20),"""",HLOOKUP(REGEXEXTRACT(F20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F20,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Valk")</f>
         <v>Valk</v>
       </c>
-      <c r="H21" s="247"/>
+      <c r="H21" s="244"/>
       <c r="I21" s="78" t="s">
         <v>137</v>
       </c>
@@ -20103,7 +20094,7 @@
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="247"/>
+      <c r="A22" s="244"/>
       <c r="B22" s="97"/>
       <c r="C22" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C20),"""",HLOOKUP(REGEXEXTRACT(C20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C20,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -20121,7 +20112,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F20),"""",HLOOKUP(REGEXEXTRACT(F20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F20,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H22" s="247"/>
+      <c r="H22" s="244"/>
       <c r="I22" s="79"/>
       <c r="J22" s="59"/>
       <c r="K22" s="59">
@@ -20138,7 +20129,7 @@
       </c>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="251"/>
+      <c r="A24" s="248"/>
       <c r="B24" s="95" t="s">
         <v>138</v>
       </c>
@@ -20154,7 +20145,7 @@
       <c r="F24" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="H24" s="251"/>
+      <c r="H24" s="248"/>
       <c r="I24" s="77" t="s">
         <v>138</v>
       </c>
@@ -20172,7 +20163,7 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="247"/>
+      <c r="A25" s="244"/>
       <c r="B25" s="96" t="s">
         <v>137</v>
       </c>
@@ -20192,7 +20183,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F24),"""",HLOOKUP(REGEXEXTRACT(F24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F24,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Paladin")</f>
         <v>Paladin</v>
       </c>
-      <c r="H25" s="247"/>
+      <c r="H25" s="244"/>
       <c r="I25" s="78" t="s">
         <v>137</v>
       </c>
@@ -20213,7 +20204,7 @@
       </c>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="247"/>
+      <c r="A26" s="244"/>
       <c r="B26" s="97"/>
       <c r="C26" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C24),"""",HLOOKUP(REGEXEXTRACT(C24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C24,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
@@ -20231,7 +20222,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F24),"""",HLOOKUP(REGEXEXTRACT(F24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F24,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H26" s="247"/>
+      <c r="H26" s="244"/>
       <c r="I26" s="79"/>
       <c r="J26" s="59"/>
       <c r="K26" s="59">
@@ -20249,15 +20240,15 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="7"/>
-      <c r="H28" s="252"/>
+      <c r="H28" s="249"/>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="7"/>
-      <c r="H29" s="247"/>
+      <c r="H29" s="244"/>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="7"/>
-      <c r="H30" s="247"/>
+      <c r="H30" s="244"/>
     </row>
     <row r="35" spans="5:5">
       <c r="E35" s="7" t="s">
@@ -20326,7 +20317,7 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14">
-      <c r="A4" s="251" t="s">
+      <c r="A4" s="248" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="64" t="s">
@@ -20344,7 +20335,7 @@
       <c r="F4" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="H4" s="251" t="s">
+      <c r="H4" s="248" t="s">
         <v>0</v>
       </c>
       <c r="I4" s="65" t="s">
@@ -20364,7 +20355,7 @@
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="247"/>
+      <c r="A5" s="244"/>
       <c r="B5" s="66" t="s">
         <v>135</v>
       </c>
@@ -20384,7 +20375,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F4),"""",HLOOKUP(REGEXEXTRACT(F4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F4,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H5" s="247"/>
+      <c r="H5" s="244"/>
       <c r="I5" s="67" t="s">
         <v>136</v>
       </c>
@@ -20406,7 +20397,7 @@
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="247"/>
+      <c r="A6" s="244"/>
       <c r="B6" s="68"/>
       <c r="C6" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C4),"""",HLOOKUP(REGEXEXTRACT(C4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -20424,7 +20415,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F4),"""",HLOOKUP(REGEXEXTRACT(F4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H6" s="247"/>
+      <c r="H6" s="244"/>
       <c r="I6" s="69"/>
       <c r="J6" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J4),"""",HLOOKUP(REGEXEXTRACT(J4,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J4,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -20444,7 +20435,7 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="251" t="s">
+      <c r="A8" s="248" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="64" t="s">
@@ -20462,7 +20453,7 @@
       <c r="F8" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="H8" s="251"/>
+      <c r="H8" s="248"/>
       <c r="I8" s="70" t="s">
         <v>134</v>
       </c>
@@ -20480,7 +20471,7 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="247"/>
+      <c r="A9" s="244"/>
       <c r="B9" s="66" t="s">
         <v>137</v>
       </c>
@@ -20500,7 +20491,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F8),"""",HLOOKUP(REGEXEXTRACT(F8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F8,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H9" s="247"/>
+      <c r="H9" s="244"/>
       <c r="I9" s="71" t="s">
         <v>137</v>
       </c>
@@ -20522,7 +20513,7 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="247"/>
+      <c r="A10" s="244"/>
       <c r="B10" s="68"/>
       <c r="C10" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C8),"""",HLOOKUP(REGEXEXTRACT(C8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C8,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -20540,7 +20531,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F8),"""",HLOOKUP(REGEXEXTRACT(F8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F8,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
-      <c r="H10" s="247"/>
+      <c r="H10" s="244"/>
       <c r="I10" s="72"/>
       <c r="J10" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J8),"""",HLOOKUP(REGEXEXTRACT(J8,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J8,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -20576,7 +20567,7 @@
       <c r="N11" s="73"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="251" t="s">
+      <c r="A12" s="248" t="s">
         <v>0</v>
       </c>
       <c r="B12" s="64" t="s">
@@ -20594,7 +20585,7 @@
       <c r="F12" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="H12" s="251" t="s">
+      <c r="H12" s="248" t="s">
         <v>0</v>
       </c>
       <c r="I12" s="65" t="s">
@@ -20614,7 +20605,7 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="247"/>
+      <c r="A13" s="244"/>
       <c r="B13" s="66" t="s">
         <v>137</v>
       </c>
@@ -20634,7 +20625,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F12),"""",HLOOKUP(REGEXEXTRACT(F12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F12,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Artist")</f>
         <v>Artist</v>
       </c>
-      <c r="H13" s="247"/>
+      <c r="H13" s="244"/>
       <c r="I13" s="67" t="s">
         <v>137</v>
       </c>
@@ -20656,7 +20647,7 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="247"/>
+      <c r="A14" s="244"/>
       <c r="B14" s="68"/>
       <c r="C14" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C12),"""",HLOOKUP(REGEXEXTRACT(C12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -20674,7 +20665,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F12),"""",HLOOKUP(REGEXEXTRACT(F12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H14" s="247"/>
+      <c r="H14" s="244"/>
       <c r="I14" s="69"/>
       <c r="J14" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J12),"""",HLOOKUP(REGEXEXTRACT(J12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J12,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -20694,7 +20685,7 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="254" t="s">
+      <c r="A16" s="251" t="s">
         <v>0</v>
       </c>
       <c r="B16" s="92" t="s">
@@ -20712,7 +20703,7 @@
       <c r="F16" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="H16" s="251" t="s">
+      <c r="H16" s="248" t="s">
         <v>0</v>
       </c>
       <c r="I16" s="77" t="s">
@@ -20732,7 +20723,7 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="255"/>
+      <c r="A17" s="252"/>
       <c r="B17" s="93" t="s">
         <v>137</v>
       </c>
@@ -20751,7 +20742,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F16),"""",HLOOKUP(REGEXEXTRACT(F16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F16,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Bard")</f>
         <v>Bard</v>
       </c>
-      <c r="H17" s="247"/>
+      <c r="H17" s="244"/>
       <c r="I17" s="78" t="s">
         <v>137</v>
       </c>
@@ -20772,7 +20763,7 @@
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="255"/>
+      <c r="A18" s="252"/>
       <c r="B18" s="94"/>
       <c r="C18" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C16),"""",HLOOKUP(REGEXEXTRACT(C16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C16,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -20787,7 +20778,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F16),"""",HLOOKUP(REGEXEXTRACT(F16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F16,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H18" s="247"/>
+      <c r="H18" s="244"/>
       <c r="I18" s="79"/>
       <c r="J18" s="59"/>
       <c r="K18" s="59">
@@ -20804,7 +20795,7 @@
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="251" t="s">
+      <c r="A20" s="248" t="s">
         <v>0</v>
       </c>
       <c r="B20" s="95" t="s">
@@ -20822,7 +20813,7 @@
       <c r="F20" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="H20" s="251" t="s">
+      <c r="H20" s="248" t="s">
         <v>0</v>
       </c>
       <c r="I20" s="77" t="s">
@@ -20842,7 +20833,7 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="247"/>
+      <c r="A21" s="244"/>
       <c r="B21" s="96" t="s">
         <v>137</v>
       </c>
@@ -20862,7 +20853,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F20),"""",HLOOKUP(REGEXEXTRACT(F20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F20,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Paladin")</f>
         <v>Paladin</v>
       </c>
-      <c r="H21" s="247"/>
+      <c r="H21" s="244"/>
       <c r="I21" s="78" t="s">
         <v>137</v>
       </c>
@@ -20883,7 +20874,7 @@
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="247"/>
+      <c r="A22" s="244"/>
       <c r="B22" s="97"/>
       <c r="C22" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C20),"""",HLOOKUP(REGEXEXTRACT(C20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C20,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -20901,7 +20892,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F20),"""",HLOOKUP(REGEXEXTRACT(F20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F20,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H22" s="247"/>
+      <c r="H22" s="244"/>
       <c r="I22" s="79"/>
       <c r="J22" s="59"/>
       <c r="K22" s="59">
@@ -20918,7 +20909,7 @@
       </c>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="251" t="s">
+      <c r="A24" s="248" t="s">
         <v>0</v>
       </c>
       <c r="B24" s="95" t="s">
@@ -20936,7 +20927,7 @@
       <c r="F24" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="H24" s="251" t="s">
+      <c r="H24" s="248" t="s">
         <v>0</v>
       </c>
       <c r="I24" s="77" t="s">
@@ -20956,7 +20947,7 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="247"/>
+      <c r="A25" s="244"/>
       <c r="B25" s="96" t="s">
         <v>137</v>
       </c>
@@ -20976,7 +20967,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F24),"""",HLOOKUP(REGEXEXTRACT(F24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F24,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Paladin")</f>
         <v>Paladin</v>
       </c>
-      <c r="H25" s="247"/>
+      <c r="H25" s="244"/>
       <c r="I25" s="78" t="s">
         <v>137</v>
       </c>
@@ -20997,7 +20988,7 @@
       </c>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="247"/>
+      <c r="A26" s="244"/>
       <c r="B26" s="97"/>
       <c r="C26" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C24),"""",HLOOKUP(REGEXEXTRACT(C24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C24,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -21015,7 +21006,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F24),"""",HLOOKUP(REGEXEXTRACT(F24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F24,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="H26" s="247"/>
+      <c r="H26" s="244"/>
       <c r="I26" s="79"/>
       <c r="J26" s="59"/>
       <c r="K26" s="59">
@@ -21055,18 +21046,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="H20:H22"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="H16:H18"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="H4:H6"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="H8:H10"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="H12:H14"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="H20:H22"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="H16:H18"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:A6 H4:H6 A8:A10 H8:H10 A12:A14 H12:H14 A16:A18 H16:H18 A20:A22 H20:H22 A24:A26 H24:H26 A28:A30 H28:H30">
     <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
@@ -21359,7 +21350,7 @@
       </c>
       <c r="X4" s="73"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" ht="13.5" thickBot="1">
       <c r="A5" s="73"/>
       <c r="B5" s="116"/>
       <c r="K5" s="117"/>
@@ -21373,7 +21364,7 @@
       <c r="W5" s="117"/>
       <c r="X5" s="73"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" ht="13.5" thickTop="1">
       <c r="A6" s="73"/>
       <c r="B6" s="118" t="s">
         <v>138</v>
@@ -21422,7 +21413,7 @@
         <v>126</v>
       </c>
       <c r="R6" s="73"/>
-      <c r="S6" s="121" t="s">
+      <c r="S6" s="107" t="s">
         <v>156</v>
       </c>
       <c r="T6" s="52"/>
@@ -21437,7 +21428,7 @@
       </c>
       <c r="X6" s="73"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" ht="12.75">
       <c r="A7" s="73"/>
       <c r="B7" s="108" t="s">
         <v>160</v>
@@ -21478,7 +21469,7 @@
         <v>Artist</v>
       </c>
       <c r="L7" s="73"/>
-      <c r="M7" s="122" t="s">
+      <c r="M7" s="121" t="s">
         <v>137</v>
       </c>
       <c r="N7" s="55" t="s">
@@ -21497,7 +21488,7 @@
         <v>Valk</v>
       </c>
       <c r="R7" s="73"/>
-      <c r="S7" s="123" t="s">
+      <c r="S7" s="111" t="s">
         <v>137</v>
       </c>
       <c r="T7" s="55" t="str">
@@ -21518,44 +21509,44 @@
       </c>
       <c r="X7" s="73"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" ht="13.5" thickBot="1">
       <c r="A8" s="73"/>
-      <c r="B8" s="124"/>
-      <c r="C8" s="125">
+      <c r="B8" s="122"/>
+      <c r="C8" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C6),"""",HLOOKUP(REGEXEXTRACT(C6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="D8" s="125">
+      <c r="D8" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D6),"""",HLOOKUP(REGEXEXTRACT(D6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="E8" s="125">
+      <c r="E8" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E6),"""",HLOOKUP(REGEXEXTRACT(E6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="F8" s="126">
+      <c r="F8" s="124">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F6),"""",HLOOKUP(REGEXEXTRACT(F6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="G8" s="127"/>
-      <c r="H8" s="125">
+      <c r="G8" s="125"/>
+      <c r="H8" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H6),"""",HLOOKUP(REGEXEXTRACT(H6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="I8" s="125">
+      <c r="I8" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I6),"""",HLOOKUP(REGEXEXTRACT(I6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="J8" s="125">
+      <c r="J8" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J6),"""",HLOOKUP(REGEXEXTRACT(J6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="K8" s="128">
+      <c r="K8" s="126">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(K6),"""",HLOOKUP(REGEXEXTRACT(K6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(K6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
       <c r="L8" s="73"/>
-      <c r="M8" s="129"/>
+      <c r="M8" s="127"/>
       <c r="N8" s="59"/>
       <c r="O8" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(O6),"""",HLOOKUP(REGEXEXTRACT(O6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(O6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
@@ -21570,26 +21561,26 @@
         <v>1750</v>
       </c>
       <c r="R8" s="73"/>
-      <c r="S8" s="130"/>
-      <c r="T8" s="125" t="str">
+      <c r="S8" s="115"/>
+      <c r="T8" s="123" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(T6),"""",HLOOKUP(REGEXEXTRACT(T6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(T6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="U8" s="125">
+      <c r="U8" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(U6),"""",HLOOKUP(REGEXEXTRACT(U6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(U6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="V8" s="125">
+      <c r="V8" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(V6),"""",HLOOKUP(REGEXEXTRACT(V6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(V6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="W8" s="128">
+      <c r="W8" s="126">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(W6),"""",HLOOKUP(REGEXEXTRACT(W6,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(W6,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
       <c r="X8" s="73"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" ht="14.25" thickTop="1" thickBot="1">
       <c r="A9" s="73"/>
       <c r="B9" s="73"/>
       <c r="C9" s="73"/>
@@ -21617,7 +21608,7 @@
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="73"/>
-      <c r="B10" s="131" t="s">
+      <c r="B10" s="128" t="s">
         <v>134</v>
       </c>
       <c r="C10" s="101" t="s">
@@ -21632,7 +21623,7 @@
       <c r="F10" s="103" t="s">
         <v>130</v>
       </c>
-      <c r="G10" s="132" t="s">
+      <c r="G10" s="129" t="s">
         <v>156</v>
       </c>
       <c r="H10" s="101" t="s">
@@ -21648,7 +21639,7 @@
         <v>130</v>
       </c>
       <c r="L10" s="73"/>
-      <c r="M10" s="133" t="s">
+      <c r="M10" s="130" t="s">
         <v>142</v>
       </c>
       <c r="N10" s="51" t="s">
@@ -21662,7 +21653,7 @@
       </c>
       <c r="Q10" s="52"/>
       <c r="R10" s="73"/>
-      <c r="S10" s="134" t="s">
+      <c r="S10" s="131" t="s">
         <v>156</v>
       </c>
       <c r="T10" s="51" t="s">
@@ -21681,7 +21672,7 @@
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="73"/>
-      <c r="B11" s="135" t="s">
+      <c r="B11" s="132" t="s">
         <v>161</v>
       </c>
       <c r="C11" s="55" t="str">
@@ -21699,7 +21690,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F10),"""",HLOOKUP(REGEXEXTRACT(F10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F10,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Bard")</f>
         <v>Bard</v>
       </c>
-      <c r="G11" s="135" t="s">
+      <c r="G11" s="132" t="s">
         <v>161</v>
       </c>
       <c r="H11" s="55" t="str">
@@ -21718,7 +21709,7 @@
         <v>Bard</v>
       </c>
       <c r="L11" s="73"/>
-      <c r="M11" s="136"/>
+      <c r="M11" s="133"/>
       <c r="N11" s="55" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(N10),"""",HLOOKUP(REGEXEXTRACT(N10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(N10,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Aeromancer")</f>
         <v>Aeromancer</v>
@@ -21736,7 +21727,7 @@
         <v/>
       </c>
       <c r="R11" s="73"/>
-      <c r="S11" s="137" t="s">
+      <c r="S11" s="134" t="s">
         <v>137</v>
       </c>
       <c r="T11" s="55" t="str">
@@ -21758,7 +21749,7 @@
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="73"/>
-      <c r="B12" s="138"/>
+      <c r="B12" s="135"/>
       <c r="C12" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C10),"""",HLOOKUP(REGEXEXTRACT(C10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C10,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
@@ -21772,7 +21763,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F10),"""",HLOOKUP(REGEXEXTRACT(F10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F10,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="G12" s="139"/>
+      <c r="G12" s="136"/>
       <c r="H12" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H10),"""",HLOOKUP(REGEXEXTRACT(H10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H10,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
@@ -21789,7 +21780,7 @@
         <v>1750</v>
       </c>
       <c r="L12" s="73"/>
-      <c r="M12" s="140"/>
+      <c r="M12" s="137"/>
       <c r="N12" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(N10),"""",HLOOKUP(REGEXEXTRACT(N10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(N10,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
         <v>1730</v>
@@ -21807,7 +21798,7 @@
         <v/>
       </c>
       <c r="R12" s="73"/>
-      <c r="S12" s="141"/>
+      <c r="S12" s="138"/>
       <c r="T12" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(T10),"""",HLOOKUP(REGEXEXTRACT(T10,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(T10,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
@@ -21845,7 +21836,7 @@
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="73"/>
-      <c r="B14" s="142" t="s">
+      <c r="B14" s="139" t="s">
         <v>138</v>
       </c>
       <c r="C14" s="51" t="s">
@@ -21860,7 +21851,7 @@
       <c r="F14" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="G14" s="143" t="s">
+      <c r="G14" s="140" t="s">
         <v>156</v>
       </c>
       <c r="H14" s="51" t="s">
@@ -21882,7 +21873,7 @@
       <c r="P14" s="73"/>
       <c r="Q14" s="73"/>
       <c r="R14" s="73"/>
-      <c r="S14" s="144" t="s">
+      <c r="S14" s="141" t="s">
         <v>156</v>
       </c>
       <c r="T14" s="51" t="s">
@@ -21901,7 +21892,7 @@
     </row>
     <row r="15" spans="1:24">
       <c r="A15" s="73"/>
-      <c r="B15" s="135" t="s">
+      <c r="B15" s="132" t="s">
         <v>161</v>
       </c>
       <c r="C15" s="55" t="str">
@@ -21919,7 +21910,7 @@
       <c r="F15" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="G15" s="135" t="s">
+      <c r="G15" s="132" t="s">
         <v>161</v>
       </c>
       <c r="H15" s="55" t="str">
@@ -21944,7 +21935,7 @@
       <c r="P15" s="73"/>
       <c r="Q15" s="73"/>
       <c r="R15" s="73"/>
-      <c r="S15" s="145" t="s">
+      <c r="S15" s="142" t="s">
         <v>137</v>
       </c>
       <c r="T15" s="55" t="str">
@@ -21966,34 +21957,34 @@
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="73"/>
-      <c r="B16" s="146"/>
-      <c r="C16" s="125">
+      <c r="B16" s="143"/>
+      <c r="C16" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C14),"""",HLOOKUP(REGEXEXTRACT(C14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C14,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="D16" s="125">
+      <c r="D16" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D14),"""",HLOOKUP(REGEXEXTRACT(D14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D14,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
-      <c r="E16" s="125">
+      <c r="E16" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E14),"""",HLOOKUP(REGEXEXTRACT(E14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E14,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="F16" s="126"/>
-      <c r="G16" s="147"/>
-      <c r="H16" s="125">
+      <c r="F16" s="124"/>
+      <c r="G16" s="144"/>
+      <c r="H16" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H14),"""",HLOOKUP(REGEXEXTRACT(H14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H14,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="I16" s="125">
+      <c r="I16" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I14),"""",HLOOKUP(REGEXEXTRACT(I14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I14,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="J16" s="125">
+      <c r="J16" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J14),"""",HLOOKUP(REGEXEXTRACT(J14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J14,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="K16" s="128">
+      <c r="K16" s="126">
         <v>1750</v>
       </c>
       <c r="L16" s="73"/>
@@ -22003,7 +21994,7 @@
       <c r="P16" s="73"/>
       <c r="Q16" s="73"/>
       <c r="R16" s="73"/>
-      <c r="S16" s="148"/>
+      <c r="S16" s="145"/>
       <c r="T16" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(T14),"""",HLOOKUP(REGEXEXTRACT(T14,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(T14,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
@@ -22049,7 +22040,7 @@
     </row>
     <row r="18" spans="1:24">
       <c r="A18" s="73"/>
-      <c r="B18" s="149" t="s">
+      <c r="B18" s="146" t="s">
         <v>138</v>
       </c>
       <c r="C18" s="101" t="s">
@@ -22064,7 +22055,7 @@
       <c r="F18" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="G18" s="149" t="s">
+      <c r="G18" s="146" t="s">
         <v>156</v>
       </c>
       <c r="H18" s="101" t="s">
@@ -22086,7 +22077,7 @@
       <c r="P18" s="73"/>
       <c r="Q18" s="73"/>
       <c r="R18" s="73"/>
-      <c r="S18" s="150" t="s">
+      <c r="S18" s="147" t="s">
         <v>159</v>
       </c>
       <c r="T18" s="101"/>
@@ -22103,7 +22094,7 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="73"/>
-      <c r="B19" s="151" t="s">
+      <c r="B19" s="148" t="s">
         <v>137</v>
       </c>
       <c r="C19" s="55" t="s">
@@ -22121,7 +22112,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F18),"""",HLOOKUP(REGEXEXTRACT(F18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F18,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Paladin")</f>
         <v>Paladin</v>
       </c>
-      <c r="G19" s="151" t="s">
+      <c r="G19" s="148" t="s">
         <v>137</v>
       </c>
       <c r="H19" s="55" t="s">
@@ -22146,7 +22137,7 @@
       <c r="P19" s="73"/>
       <c r="Q19" s="73"/>
       <c r="R19" s="73"/>
-      <c r="S19" s="152" t="s">
+      <c r="S19" s="149" t="s">
         <v>137</v>
       </c>
       <c r="T19" s="55"/>
@@ -22165,7 +22156,7 @@
     </row>
     <row r="20" spans="1:24">
       <c r="A20" s="73"/>
-      <c r="B20" s="153"/>
+      <c r="B20" s="150"/>
       <c r="C20" s="59"/>
       <c r="D20" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D18),"""",HLOOKUP(REGEXEXTRACT(D18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D18,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -22179,7 +22170,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F18),"""",HLOOKUP(REGEXEXTRACT(F18,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F18,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="G20" s="153"/>
+      <c r="G20" s="150"/>
       <c r="H20" s="59">
         <v>1750</v>
       </c>
@@ -22202,7 +22193,7 @@
       <c r="P20" s="73"/>
       <c r="Q20" s="73"/>
       <c r="R20" s="73"/>
-      <c r="S20" s="154"/>
+      <c r="S20" s="151"/>
       <c r="T20" s="59"/>
       <c r="U20" s="59">
         <v>1730</v>
@@ -22237,7 +22228,7 @@
     </row>
     <row r="22" spans="1:24">
       <c r="A22" s="73"/>
-      <c r="B22" s="155" t="s">
+      <c r="B22" s="152" t="s">
         <v>138</v>
       </c>
       <c r="C22" s="51" t="s">
@@ -22252,7 +22243,7 @@
       <c r="F22" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="G22" s="155" t="s">
+      <c r="G22" s="152" t="s">
         <v>156</v>
       </c>
       <c r="H22" s="51" t="s">
@@ -22274,7 +22265,7 @@
       <c r="P22" s="73"/>
       <c r="Q22" s="73"/>
       <c r="R22" s="73"/>
-      <c r="S22" s="156" t="s">
+      <c r="S22" s="153" t="s">
         <v>159</v>
       </c>
       <c r="T22" s="51"/>
@@ -22291,7 +22282,7 @@
     </row>
     <row r="23" spans="1:24">
       <c r="A23" s="73"/>
-      <c r="B23" s="151" t="s">
+      <c r="B23" s="148" t="s">
         <v>137</v>
       </c>
       <c r="C23" s="55" t="s">
@@ -22309,7 +22300,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F22),"""",HLOOKUP(REGEXEXTRACT(F22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F22,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Paladin")</f>
         <v>Paladin</v>
       </c>
-      <c r="G23" s="151" t="s">
+      <c r="G23" s="148" t="s">
         <v>137</v>
       </c>
       <c r="H23" s="55" t="s">
@@ -22330,11 +22321,11 @@
       <c r="L23" s="73"/>
       <c r="M23" s="73"/>
       <c r="N23" s="73"/>
-      <c r="O23" s="157"/>
-      <c r="P23" s="157"/>
-      <c r="Q23" s="157"/>
+      <c r="O23" s="154"/>
+      <c r="P23" s="154"/>
+      <c r="Q23" s="154"/>
       <c r="R23" s="73"/>
-      <c r="S23" s="152" t="s">
+      <c r="S23" s="149" t="s">
         <v>137</v>
       </c>
       <c r="T23" s="55"/>
@@ -22353,53 +22344,53 @@
     </row>
     <row r="24" spans="1:24">
       <c r="A24" s="73"/>
-      <c r="B24" s="158"/>
-      <c r="C24" s="125"/>
-      <c r="D24" s="125">
+      <c r="B24" s="155"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D22),"""",HLOOKUP(REGEXEXTRACT(D22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D22,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="E24" s="125">
+      <c r="E24" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E22),"""",HLOOKUP(REGEXEXTRACT(E22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E22,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="F24" s="128">
+      <c r="F24" s="126">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F22),"""",HLOOKUP(REGEXEXTRACT(F22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F22,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="G24" s="158"/>
-      <c r="H24" s="125">
-        <v>1750</v>
-      </c>
-      <c r="I24" s="125">
+      <c r="G24" s="155"/>
+      <c r="H24" s="123">
+        <v>1750</v>
+      </c>
+      <c r="I24" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I22),"""",HLOOKUP(REGEXEXTRACT(I22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I22,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="J24" s="125">
+      <c r="J24" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J22),"""",HLOOKUP(REGEXEXTRACT(J22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J22,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="K24" s="128">
+      <c r="K24" s="126">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(K22),"""",HLOOKUP(REGEXEXTRACT(K22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(K22,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
       <c r="L24" s="73"/>
       <c r="M24" s="73"/>
       <c r="N24" s="73"/>
-      <c r="O24" s="157"/>
-      <c r="P24" s="157"/>
-      <c r="Q24" s="157"/>
+      <c r="O24" s="154"/>
+      <c r="P24" s="154"/>
+      <c r="Q24" s="154"/>
       <c r="R24" s="73"/>
-      <c r="S24" s="159"/>
-      <c r="T24" s="125"/>
-      <c r="U24" s="125">
+      <c r="S24" s="156"/>
+      <c r="T24" s="123"/>
+      <c r="U24" s="123">
         <v>1730</v>
       </c>
-      <c r="V24" s="125">
+      <c r="V24" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(V22),"""",HLOOKUP(REGEXEXTRACT(V22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(V22,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
-      <c r="W24" s="128">
+      <c r="W24" s="126">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(W22),"""",HLOOKUP(REGEXEXTRACT(W22,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(W22,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
@@ -22420,9 +22411,9 @@
       <c r="L25" s="73"/>
       <c r="M25" s="73"/>
       <c r="N25" s="73"/>
-      <c r="O25" s="157"/>
-      <c r="P25" s="157"/>
-      <c r="Q25" s="157"/>
+      <c r="O25" s="154"/>
+      <c r="P25" s="154"/>
+      <c r="Q25" s="154"/>
       <c r="R25" s="73"/>
       <c r="S25" s="73"/>
       <c r="T25" s="73"/>
@@ -22433,7 +22424,7 @@
     </row>
     <row r="26" spans="1:24">
       <c r="A26" s="73"/>
-      <c r="B26" s="160" t="s">
+      <c r="B26" s="157" t="s">
         <v>134</v>
       </c>
       <c r="C26" s="101" t="s">
@@ -22448,7 +22439,7 @@
       <c r="F26" s="105" t="s">
         <v>123</v>
       </c>
-      <c r="G26" s="160" t="s">
+      <c r="G26" s="157" t="s">
         <v>156</v>
       </c>
       <c r="H26" s="101" t="s">
@@ -22466,11 +22457,11 @@
       <c r="L26" s="73"/>
       <c r="M26" s="73"/>
       <c r="N26" s="73"/>
-      <c r="O26" s="157"/>
-      <c r="P26" s="157"/>
-      <c r="Q26" s="157"/>
+      <c r="O26" s="154"/>
+      <c r="P26" s="154"/>
+      <c r="Q26" s="154"/>
       <c r="R26" s="73"/>
-      <c r="S26" s="161" t="s">
+      <c r="S26" s="158" t="s">
         <v>159</v>
       </c>
       <c r="T26" s="51"/>
@@ -22487,7 +22478,7 @@
     </row>
     <row r="27" spans="1:24">
       <c r="A27" s="73"/>
-      <c r="B27" s="162" t="s">
+      <c r="B27" s="159" t="s">
         <v>137</v>
       </c>
       <c r="C27" s="55" t="s">
@@ -22505,7 +22496,7 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F26),"""",HLOOKUP(REGEXEXTRACT(F26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F26,""(.*)-.*""),""!C3:V"")),2,FALSE))"),"Paladin")</f>
         <v>Paladin</v>
       </c>
-      <c r="G27" s="162" t="s">
+      <c r="G27" s="159" t="s">
         <v>137</v>
       </c>
       <c r="H27" s="55" t="s">
@@ -22526,11 +22517,11 @@
       <c r="L27" s="73"/>
       <c r="M27" s="73"/>
       <c r="N27" s="73"/>
-      <c r="O27" s="157"/>
-      <c r="P27" s="157"/>
-      <c r="Q27" s="157"/>
+      <c r="O27" s="154"/>
+      <c r="P27" s="154"/>
+      <c r="Q27" s="154"/>
       <c r="R27" s="73"/>
-      <c r="S27" s="163" t="s">
+      <c r="S27" s="160" t="s">
         <v>137</v>
       </c>
       <c r="T27" s="55" t="str">
@@ -22553,7 +22544,7 @@
     </row>
     <row r="28" spans="1:24">
       <c r="A28" s="73"/>
-      <c r="B28" s="164"/>
+      <c r="B28" s="161"/>
       <c r="C28" s="59"/>
       <c r="D28" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D26),"""",HLOOKUP(REGEXEXTRACT(D26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D26,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
@@ -22567,30 +22558,30 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F26),"""",HLOOKUP(REGEXEXTRACT(F26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F26,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="G28" s="165"/>
-      <c r="H28" s="125">
-        <v>1750</v>
-      </c>
-      <c r="I28" s="125">
+      <c r="G28" s="162"/>
+      <c r="H28" s="123">
+        <v>1750</v>
+      </c>
+      <c r="I28" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I26),"""",HLOOKUP(REGEXEXTRACT(I26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I26,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="J28" s="125">
+      <c r="J28" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J26),"""",HLOOKUP(REGEXEXTRACT(J26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J26,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="K28" s="128">
+      <c r="K28" s="126">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(K26),"""",HLOOKUP(REGEXEXTRACT(K26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(K26,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
       <c r="L28" s="73"/>
       <c r="M28" s="73"/>
       <c r="N28" s="73"/>
-      <c r="O28" s="157"/>
-      <c r="P28" s="157"/>
-      <c r="Q28" s="157"/>
+      <c r="O28" s="154"/>
+      <c r="P28" s="154"/>
+      <c r="Q28" s="154"/>
       <c r="R28" s="73"/>
-      <c r="S28" s="166"/>
+      <c r="S28" s="163"/>
       <c r="T28" s="59" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(T26),"""",HLOOKUP(REGEXEXTRACT(T26,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(T26,""(.*)-.*""),""!C3:V"")),3,FALSE))"),"")</f>
         <v/>
@@ -22621,9 +22612,9 @@
       <c r="L29" s="73"/>
       <c r="M29" s="73"/>
       <c r="N29" s="73"/>
-      <c r="O29" s="157"/>
-      <c r="P29" s="157"/>
-      <c r="Q29" s="157"/>
+      <c r="O29" s="154"/>
+      <c r="P29" s="154"/>
+      <c r="Q29" s="154"/>
       <c r="R29" s="73"/>
       <c r="S29" s="73"/>
       <c r="T29" s="73"/>
@@ -22634,7 +22625,7 @@
     </row>
     <row r="30" spans="1:24">
       <c r="A30" s="73"/>
-      <c r="B30" s="167" t="s">
+      <c r="B30" s="164" t="s">
         <v>138</v>
       </c>
       <c r="C30" s="51" t="s">
@@ -22657,9 +22648,9 @@
       <c r="L30" s="73"/>
       <c r="M30" s="73"/>
       <c r="N30" s="73"/>
-      <c r="O30" s="157"/>
-      <c r="P30" s="157"/>
-      <c r="Q30" s="157"/>
+      <c r="O30" s="154"/>
+      <c r="P30" s="154"/>
+      <c r="Q30" s="154"/>
       <c r="R30" s="73"/>
       <c r="S30" s="73"/>
       <c r="T30" s="73"/>
@@ -22670,7 +22661,7 @@
     </row>
     <row r="31" spans="1:24">
       <c r="A31" s="73"/>
-      <c r="B31" s="162" t="s">
+      <c r="B31" s="159" t="s">
         <v>137</v>
       </c>
       <c r="C31" s="55" t="s">
@@ -22709,17 +22700,17 @@
     </row>
     <row r="32" spans="1:24">
       <c r="A32" s="73"/>
-      <c r="B32" s="165"/>
-      <c r="C32" s="125"/>
-      <c r="D32" s="125">
+      <c r="B32" s="162"/>
+      <c r="C32" s="123"/>
+      <c r="D32" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D30),"""",HLOOKUP(REGEXEXTRACT(D30,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D30,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="E32" s="125">
+      <c r="E32" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E30),"""",HLOOKUP(REGEXEXTRACT(E30,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E30,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="F32" s="128">
+      <c r="F32" s="126">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F30),"""",HLOOKUP(REGEXEXTRACT(F30,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F30,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
@@ -22731,15 +22722,15 @@
       <c r="L32" s="73"/>
       <c r="M32" s="73"/>
       <c r="N32" s="73"/>
-      <c r="O32" s="157"/>
-      <c r="P32" s="157"/>
-      <c r="Q32" s="157"/>
-      <c r="R32" s="157"/>
+      <c r="O32" s="154"/>
+      <c r="P32" s="154"/>
+      <c r="Q32" s="154"/>
+      <c r="R32" s="154"/>
       <c r="S32" s="73"/>
       <c r="T32" s="73"/>
-      <c r="U32" s="157"/>
-      <c r="V32" s="157"/>
-      <c r="W32" s="157"/>
+      <c r="U32" s="154"/>
+      <c r="V32" s="154"/>
+      <c r="W32" s="154"/>
       <c r="X32" s="73"/>
     </row>
     <row r="33" spans="1:24">
@@ -22757,20 +22748,20 @@
       <c r="L33" s="73"/>
       <c r="M33" s="73"/>
       <c r="N33" s="73"/>
-      <c r="O33" s="157"/>
-      <c r="P33" s="157"/>
-      <c r="Q33" s="157"/>
-      <c r="R33" s="157"/>
+      <c r="O33" s="154"/>
+      <c r="P33" s="154"/>
+      <c r="Q33" s="154"/>
+      <c r="R33" s="154"/>
       <c r="S33" s="73"/>
       <c r="T33" s="73"/>
-      <c r="U33" s="157"/>
-      <c r="V33" s="157"/>
-      <c r="W33" s="157"/>
+      <c r="U33" s="154"/>
+      <c r="V33" s="154"/>
+      <c r="W33" s="154"/>
       <c r="X33" s="73"/>
     </row>
     <row r="34" spans="1:24">
       <c r="A34" s="73"/>
-      <c r="B34" s="168" t="s">
+      <c r="B34" s="165" t="s">
         <v>134</v>
       </c>
       <c r="C34" s="101" t="s">
@@ -22785,7 +22776,7 @@
       <c r="F34" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="169" t="s">
+      <c r="G34" s="166" t="s">
         <v>156</v>
       </c>
       <c r="H34" s="101" t="s">
@@ -22803,20 +22794,20 @@
       <c r="L34" s="73"/>
       <c r="M34" s="73"/>
       <c r="N34" s="73"/>
-      <c r="O34" s="157"/>
-      <c r="P34" s="157"/>
-      <c r="Q34" s="157"/>
-      <c r="R34" s="157"/>
+      <c r="O34" s="154"/>
+      <c r="P34" s="154"/>
+      <c r="Q34" s="154"/>
+      <c r="R34" s="154"/>
       <c r="S34" s="73"/>
       <c r="T34" s="73"/>
-      <c r="U34" s="157"/>
-      <c r="V34" s="157"/>
-      <c r="W34" s="157"/>
+      <c r="U34" s="154"/>
+      <c r="V34" s="154"/>
+      <c r="W34" s="154"/>
       <c r="X34" s="73"/>
     </row>
     <row r="35" spans="1:24">
       <c r="A35" s="73"/>
-      <c r="B35" s="170" t="s">
+      <c r="B35" s="167" t="s">
         <v>137</v>
       </c>
       <c r="C35" s="55" t="str">
@@ -22857,65 +22848,65 @@
       <c r="L35" s="73"/>
       <c r="M35" s="73"/>
       <c r="N35" s="73"/>
-      <c r="O35" s="157"/>
-      <c r="P35" s="157"/>
-      <c r="Q35" s="157"/>
-      <c r="R35" s="157"/>
+      <c r="O35" s="154"/>
+      <c r="P35" s="154"/>
+      <c r="Q35" s="154"/>
+      <c r="R35" s="154"/>
       <c r="S35" s="73"/>
       <c r="T35" s="73"/>
-      <c r="U35" s="157"/>
-      <c r="V35" s="157"/>
-      <c r="W35" s="157"/>
+      <c r="U35" s="154"/>
+      <c r="V35" s="154"/>
+      <c r="W35" s="154"/>
       <c r="X35" s="73"/>
     </row>
     <row r="36" spans="1:24">
       <c r="A36" s="73"/>
-      <c r="B36" s="171"/>
-      <c r="C36" s="125">
+      <c r="B36" s="168"/>
+      <c r="C36" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C34),"""",HLOOKUP(REGEXEXTRACT(C34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C34,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="D36" s="125">
+      <c r="D36" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D34),"""",HLOOKUP(REGEXEXTRACT(D34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D34,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="E36" s="125">
+      <c r="E36" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E34),"""",HLOOKUP(REGEXEXTRACT(E34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E34,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="F36" s="126">
+      <c r="F36" s="124">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F34),"""",HLOOKUP(REGEXEXTRACT(F34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F34,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="G36" s="172"/>
-      <c r="H36" s="125">
+      <c r="G36" s="169"/>
+      <c r="H36" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H34),"""",HLOOKUP(REGEXEXTRACT(H34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H34,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="I36" s="125">
+      <c r="I36" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I34),"""",HLOOKUP(REGEXEXTRACT(I34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I34,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="J36" s="125">
+      <c r="J36" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J34),"""",HLOOKUP(REGEXEXTRACT(J34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J34,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="K36" s="128">
+      <c r="K36" s="126">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(K34),"""",HLOOKUP(REGEXEXTRACT(K34,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(K34,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
       <c r="L36" s="73"/>
       <c r="M36" s="73"/>
       <c r="N36" s="73"/>
-      <c r="O36" s="157"/>
-      <c r="P36" s="157"/>
-      <c r="Q36" s="157"/>
-      <c r="R36" s="157"/>
+      <c r="O36" s="154"/>
+      <c r="P36" s="154"/>
+      <c r="Q36" s="154"/>
+      <c r="R36" s="154"/>
       <c r="S36" s="73"/>
       <c r="T36" s="73"/>
-      <c r="U36" s="157"/>
-      <c r="V36" s="157"/>
-      <c r="W36" s="157"/>
+      <c r="U36" s="154"/>
+      <c r="V36" s="154"/>
+      <c r="W36" s="154"/>
       <c r="X36" s="73"/>
     </row>
     <row r="37" spans="1:24">
@@ -22933,20 +22924,20 @@
       <c r="L37" s="73"/>
       <c r="M37" s="73"/>
       <c r="N37" s="73"/>
-      <c r="O37" s="157"/>
-      <c r="P37" s="157"/>
-      <c r="Q37" s="157"/>
-      <c r="R37" s="157"/>
+      <c r="O37" s="154"/>
+      <c r="P37" s="154"/>
+      <c r="Q37" s="154"/>
+      <c r="R37" s="154"/>
       <c r="S37" s="73"/>
       <c r="T37" s="73"/>
-      <c r="U37" s="157"/>
-      <c r="V37" s="157"/>
-      <c r="W37" s="157"/>
+      <c r="U37" s="154"/>
+      <c r="V37" s="154"/>
+      <c r="W37" s="154"/>
       <c r="X37" s="73"/>
     </row>
     <row r="38" spans="1:24">
       <c r="A38" s="73"/>
-      <c r="B38" s="173" t="s">
+      <c r="B38" s="170" t="s">
         <v>134</v>
       </c>
       <c r="C38" s="101" t="s">
@@ -22969,10 +22960,10 @@
       <c r="L38" s="73"/>
       <c r="M38" s="73"/>
       <c r="N38" s="73"/>
-      <c r="O38" s="157"/>
-      <c r="P38" s="157"/>
-      <c r="Q38" s="157"/>
-      <c r="R38" s="157"/>
+      <c r="O38" s="154"/>
+      <c r="P38" s="154"/>
+      <c r="Q38" s="154"/>
+      <c r="R38" s="154"/>
       <c r="S38" s="73"/>
       <c r="T38" s="73"/>
       <c r="U38" s="73"/>
@@ -22982,7 +22973,7 @@
     </row>
     <row r="39" spans="1:24">
       <c r="A39" s="73"/>
-      <c r="B39" s="174" t="s">
+      <c r="B39" s="171" t="s">
         <v>137</v>
       </c>
       <c r="C39" s="55" t="str">
@@ -23009,10 +23000,10 @@
       <c r="L39" s="73"/>
       <c r="M39" s="73"/>
       <c r="N39" s="73"/>
-      <c r="O39" s="157"/>
-      <c r="P39" s="157"/>
-      <c r="Q39" s="157"/>
-      <c r="R39" s="157"/>
+      <c r="O39" s="154"/>
+      <c r="P39" s="154"/>
+      <c r="Q39" s="154"/>
+      <c r="R39" s="154"/>
       <c r="S39" s="73"/>
       <c r="T39" s="73"/>
       <c r="U39" s="73"/>
@@ -23022,7 +23013,7 @@
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="73"/>
-      <c r="B40" s="175"/>
+      <c r="B40" s="172"/>
       <c r="C40" s="59">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C38),"""",HLOOKUP(REGEXEXTRACT(C38,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C38,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
@@ -23047,10 +23038,10 @@
       <c r="L40" s="73"/>
       <c r="M40" s="73"/>
       <c r="N40" s="73"/>
-      <c r="O40" s="157"/>
-      <c r="P40" s="157"/>
-      <c r="Q40" s="157"/>
-      <c r="R40" s="157"/>
+      <c r="O40" s="154"/>
+      <c r="P40" s="154"/>
+      <c r="Q40" s="154"/>
+      <c r="R40" s="154"/>
       <c r="S40" s="73"/>
       <c r="T40" s="73"/>
       <c r="U40" s="73"/>
@@ -23069,10 +23060,10 @@
       <c r="L41" s="73"/>
       <c r="M41" s="73"/>
       <c r="N41" s="73"/>
-      <c r="O41" s="157"/>
-      <c r="P41" s="157"/>
-      <c r="Q41" s="157"/>
-      <c r="R41" s="157"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="154"/>
+      <c r="R41" s="154"/>
       <c r="S41" s="73"/>
       <c r="T41" s="73"/>
       <c r="U41" s="73"/>
@@ -23082,7 +23073,7 @@
     </row>
     <row r="42" spans="1:24">
       <c r="A42" s="73"/>
-      <c r="B42" s="176" t="s">
+      <c r="B42" s="173" t="s">
         <v>138</v>
       </c>
       <c r="C42" s="52" t="s">
@@ -23105,10 +23096,10 @@
       <c r="L42" s="73"/>
       <c r="M42" s="73"/>
       <c r="N42" s="73"/>
-      <c r="O42" s="157"/>
-      <c r="P42" s="157"/>
-      <c r="Q42" s="157"/>
-      <c r="R42" s="157"/>
+      <c r="O42" s="154"/>
+      <c r="P42" s="154"/>
+      <c r="Q42" s="154"/>
+      <c r="R42" s="154"/>
       <c r="S42" s="73"/>
       <c r="T42" s="73"/>
       <c r="U42" s="73"/>
@@ -23118,7 +23109,7 @@
     </row>
     <row r="43" spans="1:24">
       <c r="A43" s="73"/>
-      <c r="B43" s="177" t="s">
+      <c r="B43" s="174" t="s">
         <v>137</v>
       </c>
       <c r="C43" s="55" t="str">
@@ -23145,10 +23136,10 @@
       <c r="L43" s="73"/>
       <c r="M43" s="73"/>
       <c r="N43" s="73"/>
-      <c r="O43" s="157"/>
-      <c r="P43" s="157"/>
-      <c r="Q43" s="157"/>
-      <c r="R43" s="157"/>
+      <c r="O43" s="154"/>
+      <c r="P43" s="154"/>
+      <c r="Q43" s="154"/>
+      <c r="R43" s="154"/>
       <c r="S43" s="73"/>
       <c r="T43" s="73"/>
       <c r="U43" s="73"/>
@@ -23158,20 +23149,20 @@
     </row>
     <row r="44" spans="1:24">
       <c r="A44" s="73"/>
-      <c r="B44" s="178"/>
-      <c r="C44" s="125">
+      <c r="B44" s="175"/>
+      <c r="C44" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C42),"""",HLOOKUP(REGEXEXTRACT(C42,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C42,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="D44" s="125">
+      <c r="D44" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D42),"""",HLOOKUP(REGEXEXTRACT(D42,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D42,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="E44" s="125">
+      <c r="E44" s="123">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E42),"""",HLOOKUP(REGEXEXTRACT(E42,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E42,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="F44" s="126">
+      <c r="F44" s="124">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F42),"""",HLOOKUP(REGEXEXTRACT(F42,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F42,""(.*)-.*""),""!C3:V"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
@@ -23183,10 +23174,10 @@
       <c r="L44" s="73"/>
       <c r="M44" s="73"/>
       <c r="N44" s="73"/>
-      <c r="O44" s="157"/>
-      <c r="P44" s="157"/>
-      <c r="Q44" s="157"/>
-      <c r="R44" s="157"/>
+      <c r="O44" s="154"/>
+      <c r="P44" s="154"/>
+      <c r="Q44" s="154"/>
+      <c r="R44" s="154"/>
       <c r="S44" s="73"/>
       <c r="T44" s="73"/>
       <c r="U44" s="73"/>
@@ -23376,7 +23367,7 @@
       <c r="W51" s="73"/>
       <c r="X51" s="73"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" ht="12.75">
       <c r="A52" s="73"/>
       <c r="B52" s="73"/>
       <c r="C52" s="73"/>
@@ -23400,7 +23391,7 @@
       <c r="U52" s="73"/>
       <c r="V52" s="73"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" ht="12.75">
       <c r="A53" s="73"/>
       <c r="B53" s="73"/>
       <c r="C53" s="73"/>
@@ -23466,356 +23457,356 @@
       </c>
     </row>
     <row r="10" spans="4:17">
-      <c r="D10" s="179" t="s">
+      <c r="D10" s="176" t="s">
         <v>171</v>
       </c>
-      <c r="E10" s="180"/>
-      <c r="F10" s="181" t="s">
+      <c r="E10" s="177"/>
+      <c r="F10" s="178" t="s">
         <v>172</v>
       </c>
-      <c r="G10" s="182"/>
-      <c r="I10" s="179" t="s">
+      <c r="G10" s="179"/>
+      <c r="I10" s="176" t="s">
         <v>171</v>
       </c>
-      <c r="J10" s="180"/>
-      <c r="K10" s="181" t="s">
+      <c r="J10" s="177"/>
+      <c r="K10" s="178" t="s">
         <v>172</v>
       </c>
-      <c r="L10" s="182"/>
-      <c r="N10" s="179" t="s">
+      <c r="L10" s="179"/>
+      <c r="N10" s="176" t="s">
         <v>171</v>
       </c>
-      <c r="O10" s="180"/>
-      <c r="P10" s="181" t="s">
+      <c r="O10" s="177"/>
+      <c r="P10" s="178" t="s">
         <v>172</v>
       </c>
-      <c r="Q10" s="182"/>
+      <c r="Q10" s="179"/>
     </row>
     <row r="11" spans="4:17">
-      <c r="D11" s="183">
+      <c r="D11" s="180">
         <v>1</v>
       </c>
-      <c r="E11" s="184" t="s">
+      <c r="E11" s="181" t="s">
         <v>173</v>
       </c>
-      <c r="F11" s="184">
+      <c r="F11" s="181">
         <v>1</v>
       </c>
-      <c r="G11" s="184" t="s">
+      <c r="G11" s="181" t="s">
         <v>174</v>
       </c>
-      <c r="I11" s="183">
+      <c r="I11" s="180">
         <v>1</v>
       </c>
-      <c r="J11" s="184" t="s">
+      <c r="J11" s="181" t="s">
         <v>175</v>
       </c>
-      <c r="K11" s="184">
+      <c r="K11" s="181">
         <v>1</v>
       </c>
-      <c r="L11" s="184" t="s">
+      <c r="L11" s="181" t="s">
         <v>176</v>
       </c>
-      <c r="N11" s="183">
+      <c r="N11" s="180">
         <v>1</v>
       </c>
-      <c r="O11" s="184" t="s">
+      <c r="O11" s="181" t="s">
         <v>177</v>
       </c>
-      <c r="P11" s="184">
+      <c r="P11" s="181">
         <v>1</v>
       </c>
-      <c r="Q11" s="184" t="s">
+      <c r="Q11" s="181" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="12" spans="4:17">
-      <c r="D12" s="183">
+      <c r="D12" s="180">
         <v>2</v>
       </c>
-      <c r="E12" s="184" t="s">
+      <c r="E12" s="181" t="s">
         <v>179</v>
       </c>
-      <c r="F12" s="184">
+      <c r="F12" s="181">
         <v>2</v>
       </c>
-      <c r="G12" s="184" t="s">
+      <c r="G12" s="181" t="s">
         <v>180</v>
       </c>
-      <c r="I12" s="183">
+      <c r="I12" s="180">
         <v>2</v>
       </c>
-      <c r="J12" s="184" t="s">
+      <c r="J12" s="181" t="s">
         <v>181</v>
       </c>
-      <c r="K12" s="184">
+      <c r="K12" s="181">
         <v>2</v>
       </c>
-      <c r="L12" s="184" t="s">
+      <c r="L12" s="181" t="s">
         <v>182</v>
       </c>
-      <c r="N12" s="183">
+      <c r="N12" s="180">
         <v>2</v>
       </c>
-      <c r="O12" s="184" t="s">
+      <c r="O12" s="181" t="s">
         <v>183</v>
       </c>
-      <c r="P12" s="184">
+      <c r="P12" s="181">
         <v>2</v>
       </c>
-      <c r="Q12" s="184" t="s">
+      <c r="Q12" s="181" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="13" spans="4:17">
-      <c r="D13" s="183">
+      <c r="D13" s="180">
         <v>3</v>
       </c>
-      <c r="E13" s="184" t="s">
+      <c r="E13" s="181" t="s">
         <v>185</v>
       </c>
-      <c r="F13" s="184">
+      <c r="F13" s="181">
         <v>3</v>
       </c>
-      <c r="G13" s="184" t="s">
+      <c r="G13" s="181" t="s">
         <v>186</v>
       </c>
-      <c r="I13" s="183">
+      <c r="I13" s="180">
         <v>3</v>
       </c>
-      <c r="J13" s="184" t="s">
+      <c r="J13" s="181" t="s">
         <v>187</v>
       </c>
-      <c r="K13" s="184">
+      <c r="K13" s="181">
         <v>3</v>
       </c>
-      <c r="L13" s="184" t="s">
+      <c r="L13" s="181" t="s">
         <v>188</v>
       </c>
-      <c r="N13" s="183">
+      <c r="N13" s="180">
         <v>3</v>
       </c>
-      <c r="O13" s="184" t="s">
+      <c r="O13" s="181" t="s">
         <v>189</v>
       </c>
-      <c r="P13" s="184">
+      <c r="P13" s="181">
         <v>3</v>
       </c>
-      <c r="Q13" s="184" t="s">
+      <c r="Q13" s="181" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="14" spans="4:17">
-      <c r="D14" s="183">
+      <c r="D14" s="180">
         <v>4</v>
       </c>
-      <c r="E14" s="184" t="s">
+      <c r="E14" s="181" t="s">
         <v>191</v>
       </c>
-      <c r="F14" s="184">
+      <c r="F14" s="181">
         <v>4</v>
       </c>
-      <c r="G14" s="184" t="s">
+      <c r="G14" s="181" t="s">
         <v>192</v>
       </c>
-      <c r="I14" s="183">
+      <c r="I14" s="180">
         <v>4</v>
       </c>
-      <c r="J14" s="184" t="s">
+      <c r="J14" s="181" t="s">
         <v>193</v>
       </c>
-      <c r="K14" s="184">
+      <c r="K14" s="181">
         <v>4</v>
       </c>
-      <c r="L14" s="184" t="s">
+      <c r="L14" s="181" t="s">
         <v>194</v>
       </c>
-      <c r="N14" s="183">
+      <c r="N14" s="180">
         <v>4</v>
       </c>
-      <c r="O14" s="184" t="s">
+      <c r="O14" s="181" t="s">
         <v>195</v>
       </c>
-      <c r="P14" s="184">
+      <c r="P14" s="181">
         <v>4</v>
       </c>
-      <c r="Q14" s="184" t="s">
+      <c r="Q14" s="181" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="15" spans="4:17">
-      <c r="D15" s="185" t="s">
+      <c r="D15" s="182" t="s">
         <v>197</v>
       </c>
-      <c r="E15" s="186"/>
-      <c r="F15" s="187" t="s">
+      <c r="E15" s="183"/>
+      <c r="F15" s="184" t="s">
         <v>198</v>
       </c>
-      <c r="G15" s="188"/>
-      <c r="I15" s="185" t="s">
+      <c r="G15" s="185"/>
+      <c r="I15" s="182" t="s">
         <v>197</v>
       </c>
-      <c r="J15" s="186"/>
-      <c r="K15" s="187" t="s">
+      <c r="J15" s="183"/>
+      <c r="K15" s="184" t="s">
         <v>198</v>
       </c>
-      <c r="L15" s="188"/>
-      <c r="N15" s="185" t="s">
+      <c r="L15" s="185"/>
+      <c r="N15" s="182" t="s">
         <v>197</v>
       </c>
-      <c r="O15" s="186"/>
-      <c r="P15" s="187" t="s">
+      <c r="O15" s="183"/>
+      <c r="P15" s="184" t="s">
         <v>198</v>
       </c>
-      <c r="Q15" s="188"/>
+      <c r="Q15" s="185"/>
     </row>
     <row r="16" spans="4:17">
-      <c r="D16" s="183">
+      <c r="D16" s="180">
         <v>1</v>
       </c>
-      <c r="E16" s="184" t="s">
+      <c r="E16" s="181" t="s">
         <v>199</v>
       </c>
-      <c r="F16" s="183">
+      <c r="F16" s="180">
         <v>1</v>
       </c>
-      <c r="G16" s="184" t="s">
+      <c r="G16" s="181" t="s">
         <v>200</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="180">
         <v>1</v>
       </c>
-      <c r="J16" s="184" t="s">
+      <c r="J16" s="181" t="s">
         <v>201</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="180">
         <v>1</v>
       </c>
-      <c r="L16" s="184" t="s">
+      <c r="L16" s="181" t="s">
         <v>202</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="180">
         <v>1</v>
       </c>
-      <c r="O16" s="184" t="s">
+      <c r="O16" s="181" t="s">
         <v>201</v>
       </c>
-      <c r="P16" s="183">
+      <c r="P16" s="180">
         <v>1</v>
       </c>
-      <c r="Q16" s="184" t="s">
+      <c r="Q16" s="181" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="17" spans="4:17">
-      <c r="D17" s="183">
+      <c r="D17" s="180">
         <v>2</v>
       </c>
-      <c r="E17" s="189" t="s">
+      <c r="E17" s="186" t="s">
         <v>204</v>
       </c>
-      <c r="F17" s="183">
+      <c r="F17" s="180">
         <v>2</v>
       </c>
-      <c r="G17" s="184" t="s">
+      <c r="G17" s="181" t="s">
         <v>205</v>
       </c>
-      <c r="I17" s="183">
+      <c r="I17" s="180">
         <v>2</v>
       </c>
-      <c r="J17" s="189" t="s">
+      <c r="J17" s="186" t="s">
         <v>206</v>
       </c>
-      <c r="K17" s="183">
+      <c r="K17" s="180">
         <v>2</v>
       </c>
-      <c r="L17" s="184" t="s">
+      <c r="L17" s="181" t="s">
         <v>207</v>
       </c>
-      <c r="N17" s="183">
+      <c r="N17" s="180">
         <v>2</v>
       </c>
-      <c r="O17" s="189" t="s">
+      <c r="O17" s="186" t="s">
         <v>208</v>
       </c>
-      <c r="P17" s="183">
+      <c r="P17" s="180">
         <v>2</v>
       </c>
-      <c r="Q17" s="184" t="s">
+      <c r="Q17" s="181" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="18" spans="4:17">
-      <c r="D18" s="183">
+      <c r="D18" s="180">
         <v>3</v>
       </c>
-      <c r="E18" s="184" t="s">
+      <c r="E18" s="181" t="s">
         <v>210</v>
       </c>
-      <c r="F18" s="183">
+      <c r="F18" s="180">
         <v>3</v>
       </c>
-      <c r="G18" s="184" t="s">
+      <c r="G18" s="181" t="s">
         <v>211</v>
       </c>
-      <c r="I18" s="183">
+      <c r="I18" s="180">
         <v>3</v>
       </c>
-      <c r="J18" s="184" t="s">
+      <c r="J18" s="181" t="s">
         <v>212</v>
       </c>
-      <c r="K18" s="183">
+      <c r="K18" s="180">
         <v>3</v>
       </c>
-      <c r="L18" s="184"/>
-      <c r="N18" s="183">
+      <c r="L18" s="181"/>
+      <c r="N18" s="180">
         <v>3</v>
       </c>
-      <c r="O18" s="184" t="s">
+      <c r="O18" s="181" t="s">
         <v>213</v>
       </c>
-      <c r="P18" s="183">
+      <c r="P18" s="180">
         <v>3</v>
       </c>
-      <c r="Q18" s="184" t="s">
+      <c r="Q18" s="181" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="19" spans="4:17">
-      <c r="D19" s="183">
+      <c r="D19" s="180">
         <v>4</v>
       </c>
-      <c r="E19" s="184" t="s">
+      <c r="E19" s="181" t="s">
         <v>215</v>
       </c>
-      <c r="F19" s="183">
+      <c r="F19" s="180">
         <v>4</v>
       </c>
-      <c r="G19" s="184" t="s">
+      <c r="G19" s="181" t="s">
         <v>216</v>
       </c>
-      <c r="I19" s="183">
+      <c r="I19" s="180">
         <v>4</v>
       </c>
-      <c r="J19" s="184" t="s">
+      <c r="J19" s="181" t="s">
         <v>217</v>
       </c>
-      <c r="K19" s="183">
+      <c r="K19" s="180">
         <v>4</v>
       </c>
-      <c r="L19" s="184" t="s">
+      <c r="L19" s="181" t="s">
         <v>218</v>
       </c>
-      <c r="N19" s="183">
+      <c r="N19" s="180">
         <v>4</v>
       </c>
-      <c r="O19" s="184" t="s">
+      <c r="O19" s="181" t="s">
         <v>219</v>
       </c>
-      <c r="P19" s="183">
+      <c r="P19" s="180">
         <v>4</v>
       </c>
-      <c r="Q19" s="184" t="s">
+      <c r="Q19" s="181" t="s">
         <v>220</v>
       </c>
     </row>
@@ -24007,120 +23998,120 @@
       </c>
     </row>
     <row r="71" spans="10:13">
-      <c r="J71" s="179" t="s">
+      <c r="J71" s="176" t="s">
         <v>171</v>
       </c>
-      <c r="K71" s="180"/>
-      <c r="L71" s="181" t="s">
+      <c r="K71" s="177"/>
+      <c r="L71" s="178" t="s">
         <v>172</v>
       </c>
-      <c r="M71" s="182"/>
+      <c r="M71" s="179"/>
     </row>
     <row r="72" spans="10:13">
-      <c r="J72" s="183">
+      <c r="J72" s="180">
         <v>1</v>
       </c>
-      <c r="K72" s="184" t="s">
+      <c r="K72" s="181" t="s">
         <v>240</v>
       </c>
-      <c r="L72" s="184">
+      <c r="L72" s="181">
         <v>1</v>
       </c>
-      <c r="M72" s="184"/>
+      <c r="M72" s="181"/>
     </row>
     <row r="73" spans="10:13">
-      <c r="J73" s="183">
+      <c r="J73" s="180">
         <v>2</v>
       </c>
-      <c r="K73" s="184" t="s">
+      <c r="K73" s="181" t="s">
         <v>241</v>
       </c>
-      <c r="L73" s="184">
+      <c r="L73" s="181">
         <v>2</v>
       </c>
-      <c r="M73" s="184"/>
+      <c r="M73" s="181"/>
     </row>
     <row r="74" spans="10:13">
-      <c r="J74" s="183">
+      <c r="J74" s="180">
         <v>3</v>
       </c>
-      <c r="K74" s="184" t="s">
+      <c r="K74" s="181" t="s">
         <v>242</v>
       </c>
-      <c r="L74" s="184">
+      <c r="L74" s="181">
         <v>3</v>
       </c>
-      <c r="M74" s="184"/>
+      <c r="M74" s="181"/>
     </row>
     <row r="75" spans="10:13">
-      <c r="J75" s="183">
+      <c r="J75" s="180">
         <v>4</v>
       </c>
-      <c r="K75" s="184" t="s">
+      <c r="K75" s="181" t="s">
         <v>243</v>
       </c>
-      <c r="L75" s="184">
+      <c r="L75" s="181">
         <v>4</v>
       </c>
-      <c r="M75" s="184" t="s">
+      <c r="M75" s="181" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="76" spans="10:13">
-      <c r="J76" s="185" t="s">
+      <c r="J76" s="182" t="s">
         <v>197</v>
       </c>
-      <c r="K76" s="186"/>
-      <c r="L76" s="187" t="s">
+      <c r="K76" s="183"/>
+      <c r="L76" s="184" t="s">
         <v>198</v>
       </c>
-      <c r="M76" s="188"/>
+      <c r="M76" s="185"/>
     </row>
     <row r="77" spans="10:13">
-      <c r="J77" s="183">
+      <c r="J77" s="180">
         <v>1</v>
       </c>
-      <c r="K77" s="184" t="s">
+      <c r="K77" s="181" t="s">
         <v>244</v>
       </c>
-      <c r="L77" s="183">
+      <c r="L77" s="180">
         <v>1</v>
       </c>
-      <c r="M77" s="184"/>
+      <c r="M77" s="181"/>
     </row>
     <row r="78" spans="10:13">
-      <c r="J78" s="183">
+      <c r="J78" s="180">
         <v>2</v>
       </c>
-      <c r="K78" s="189" t="s">
+      <c r="K78" s="186" t="s">
         <v>245</v>
       </c>
-      <c r="L78" s="183">
+      <c r="L78" s="180">
         <v>2</v>
       </c>
-      <c r="M78" s="184"/>
+      <c r="M78" s="181"/>
     </row>
     <row r="79" spans="10:13">
-      <c r="J79" s="183">
+      <c r="J79" s="180">
         <v>3</v>
       </c>
-      <c r="K79" s="184"/>
-      <c r="L79" s="183">
+      <c r="K79" s="181"/>
+      <c r="L79" s="180">
         <v>3</v>
       </c>
-      <c r="M79" s="184"/>
+      <c r="M79" s="181"/>
     </row>
     <row r="80" spans="10:13">
-      <c r="J80" s="183">
+      <c r="J80" s="180">
         <v>4</v>
       </c>
-      <c r="K80" s="184" t="s">
+      <c r="K80" s="181" t="s">
         <v>246</v>
       </c>
-      <c r="L80" s="183">
+      <c r="L80" s="180">
         <v>4</v>
       </c>
-      <c r="M80" s="184" t="s">
+      <c r="M80" s="181" t="s">
         <v>247</v>
       </c>
     </row>
@@ -24155,7 +24146,7 @@
       <c r="D2" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="F2" s="190" t="s">
+      <c r="F2" s="187" t="s">
         <v>252</v>
       </c>
     </row>
@@ -24273,25 +24264,25 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="12.75">
-      <c r="A12" s="246"/>
+      <c r="A12" s="243"/>
       <c r="B12" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="C12" s="191" t="s">
+      <c r="C12" s="188" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="192"/>
-      <c r="E12" s="192"/>
-      <c r="F12" s="192"/>
-      <c r="G12" s="192" t="s">
+      <c r="D12" s="189"/>
+      <c r="E12" s="189"/>
+      <c r="F12" s="189"/>
+      <c r="G12" s="189" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="192"/>
-      <c r="I12" s="192"/>
-      <c r="J12" s="193"/>
+      <c r="H12" s="189"/>
+      <c r="I12" s="189"/>
+      <c r="J12" s="190"/>
     </row>
     <row r="13" spans="1:12" ht="12.75">
-      <c r="A13" s="247"/>
+      <c r="A13" s="244"/>
       <c r="B13" s="54" t="s">
         <v>261</v>
       </c>
@@ -24323,13 +24314,13 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I12),"""",HLOOKUP(REGEXEXTRACT(I12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I12,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J13" s="194" t="str">
+      <c r="J13" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J12),"""",HLOOKUP(REGEXEXTRACT(J12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J12,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:12" ht="12.75">
-      <c r="A14" s="247"/>
+      <c r="A14" s="244"/>
       <c r="B14" s="58" t="s">
         <v>262</v>
       </c>
@@ -24341,11 +24332,11 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D12),"""",HLOOKUP(REGEXEXTRACT(D12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D12,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="E14" s="195" t="str">
+      <c r="E14" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E12),"""",HLOOKUP(REGEXEXTRACT(E12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E12,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="F14" s="195" t="str">
+      <c r="F14" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F12),"""",HLOOKUP(REGEXEXTRACT(F12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F12,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
@@ -24353,37 +24344,37 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G12),"""",HLOOKUP(REGEXEXTRACT(G12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G12,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="H14" s="195" t="str">
+      <c r="H14" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H12),"""",HLOOKUP(REGEXEXTRACT(H12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H12,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="I14" s="195" t="str">
+      <c r="I14" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I12),"""",HLOOKUP(REGEXEXTRACT(I12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I12,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J14" s="196" t="str">
+      <c r="J14" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J12),"""",HLOOKUP(REGEXEXTRACT(J12,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J12,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:12" ht="12.75">
-      <c r="A16" s="246"/>
+      <c r="A16" s="243"/>
       <c r="B16" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="C16" s="191"/>
-      <c r="D16" s="192" t="s">
+      <c r="C16" s="188"/>
+      <c r="D16" s="189" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="192"/>
-      <c r="F16" s="192"/>
-      <c r="G16" s="192"/>
-      <c r="H16" s="192"/>
-      <c r="I16" s="192"/>
-      <c r="J16" s="193"/>
+      <c r="E16" s="189"/>
+      <c r="F16" s="189"/>
+      <c r="G16" s="189"/>
+      <c r="H16" s="189"/>
+      <c r="I16" s="189"/>
+      <c r="J16" s="190"/>
     </row>
     <row r="17" spans="1:10" ht="12.75">
-      <c r="A17" s="247"/>
+      <c r="A17" s="244"/>
       <c r="B17" s="54" t="s">
         <v>261</v>
       </c>
@@ -24415,13 +24406,13 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I16),"""",HLOOKUP(REGEXEXTRACT(I16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I16,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J17" s="194" t="str">
+      <c r="J17" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J16),"""",HLOOKUP(REGEXEXTRACT(J16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J16,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:10" ht="12.75">
-      <c r="A18" s="247"/>
+      <c r="A18" s="244"/>
       <c r="B18" s="58" t="s">
         <v>262</v>
       </c>
@@ -24433,11 +24424,11 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D16),"""",HLOOKUP(REGEXEXTRACT(D16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D16,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="E18" s="195" t="str">
+      <c r="E18" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E16),"""",HLOOKUP(REGEXEXTRACT(E16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E16,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="F18" s="195" t="str">
+      <c r="F18" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F16),"""",HLOOKUP(REGEXEXTRACT(F16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F16,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
@@ -24445,39 +24436,39 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G16),"""",HLOOKUP(REGEXEXTRACT(G16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G16,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="H18" s="195" t="str">
+      <c r="H18" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H16),"""",HLOOKUP(REGEXEXTRACT(H16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H16,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="I18" s="195" t="str">
+      <c r="I18" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I16),"""",HLOOKUP(REGEXEXTRACT(I16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I16,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J18" s="196" t="str">
+      <c r="J18" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J16),"""",HLOOKUP(REGEXEXTRACT(J16,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J16,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:10" ht="12.75">
-      <c r="A20" s="246"/>
+      <c r="A20" s="243"/>
       <c r="B20" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="C20" s="191" t="s">
+      <c r="C20" s="188" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="192"/>
-      <c r="E20" s="192"/>
-      <c r="F20" s="192"/>
-      <c r="G20" s="192" t="s">
+      <c r="D20" s="189"/>
+      <c r="E20" s="189"/>
+      <c r="F20" s="189"/>
+      <c r="G20" s="189" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="192"/>
-      <c r="I20" s="192"/>
-      <c r="J20" s="193"/>
+      <c r="H20" s="189"/>
+      <c r="I20" s="189"/>
+      <c r="J20" s="190"/>
     </row>
     <row r="21" spans="1:10" ht="12.75">
-      <c r="A21" s="247"/>
+      <c r="A21" s="244"/>
       <c r="B21" s="54" t="s">
         <v>261</v>
       </c>
@@ -24509,13 +24500,13 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I20),"""",HLOOKUP(REGEXEXTRACT(I20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I20,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J21" s="194" t="str">
+      <c r="J21" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J20),"""",HLOOKUP(REGEXEXTRACT(J20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J20,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:10" ht="12.75">
-      <c r="A22" s="247"/>
+      <c r="A22" s="244"/>
       <c r="B22" s="58" t="s">
         <v>263</v>
       </c>
@@ -24527,11 +24518,11 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D20),"""",HLOOKUP(REGEXEXTRACT(D20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D20,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="E22" s="195" t="str">
+      <c r="E22" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E20),"""",HLOOKUP(REGEXEXTRACT(E20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E20,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="F22" s="195" t="str">
+      <c r="F22" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F20),"""",HLOOKUP(REGEXEXTRACT(F20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F20,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
@@ -24539,47 +24530,47 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G20),"""",HLOOKUP(REGEXEXTRACT(G20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G20,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="H22" s="195" t="str">
+      <c r="H22" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H20),"""",HLOOKUP(REGEXEXTRACT(H20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H20,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="I22" s="195" t="str">
+      <c r="I22" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I20),"""",HLOOKUP(REGEXEXTRACT(I20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I20,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J22" s="196" t="str">
+      <c r="J22" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J20),"""",HLOOKUP(REGEXEXTRACT(J20,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J20,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:10" ht="12.75">
-      <c r="A24" s="246"/>
+      <c r="A24" s="243"/>
       <c r="B24" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="C24" s="191" t="s">
+      <c r="C24" s="188" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="192" t="s">
+      <c r="D24" s="189" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="192" t="s">
+      <c r="E24" s="189" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="192" t="s">
+      <c r="F24" s="189" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="192" t="s">
+      <c r="G24" s="189" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="192" t="s">
+      <c r="H24" s="189" t="s">
         <v>28</v>
       </c>
-      <c r="I24" s="192"/>
-      <c r="J24" s="193"/>
+      <c r="I24" s="189"/>
+      <c r="J24" s="190"/>
     </row>
     <row r="25" spans="1:10" ht="12.75">
-      <c r="A25" s="247"/>
+      <c r="A25" s="244"/>
       <c r="B25" s="54" t="s">
         <v>261</v>
       </c>
@@ -24611,13 +24602,13 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I24),"""",HLOOKUP(REGEXEXTRACT(I24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I24,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J25" s="194" t="str">
+      <c r="J25" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J24),"""",HLOOKUP(REGEXEXTRACT(J24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J24,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:10" ht="12.75">
-      <c r="A26" s="247"/>
+      <c r="A26" s="244"/>
       <c r="B26" s="58" t="s">
         <v>264</v>
       </c>
@@ -24629,11 +24620,11 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D24),"""",HLOOKUP(REGEXEXTRACT(D24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D24,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1730)</f>
         <v>1730</v>
       </c>
-      <c r="E26" s="195">
+      <c r="E26" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E24),"""",HLOOKUP(REGEXEXTRACT(E24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E24,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="F26" s="195" t="str">
+      <c r="F26" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F24),"""",HLOOKUP(REGEXEXTRACT(F24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F24,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
@@ -24641,46 +24632,46 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G24),"""",HLOOKUP(REGEXEXTRACT(G24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G24,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="H26" s="195" t="str">
+      <c r="H26" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H24),"""",HLOOKUP(REGEXEXTRACT(H24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H24,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="I26" s="195" t="str">
+      <c r="I26" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I24),"""",HLOOKUP(REGEXEXTRACT(I24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I24,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J26" s="196" t="str">
+      <c r="J26" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J24),"""",HLOOKUP(REGEXEXTRACT(J24,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J24,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:10" ht="12.75">
-      <c r="A28" s="246"/>
-      <c r="B28" s="197" t="s">
+      <c r="A28" s="243"/>
+      <c r="B28" s="194" t="s">
         <v>260</v>
       </c>
-      <c r="C28" s="191" t="s">
+      <c r="C28" s="188" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="192" t="s">
+      <c r="D28" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="192" t="s">
+      <c r="E28" s="189" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="192" t="s">
+      <c r="F28" s="189" t="s">
         <v>36</v>
       </c>
-      <c r="G28" s="192" t="s">
+      <c r="G28" s="189" t="s">
         <v>5</v>
       </c>
-      <c r="H28" s="192"/>
-      <c r="I28" s="192"/>
-      <c r="J28" s="193"/>
+      <c r="H28" s="189"/>
+      <c r="I28" s="189"/>
+      <c r="J28" s="190"/>
     </row>
     <row r="29" spans="1:10" ht="12.75">
-      <c r="A29" s="247"/>
-      <c r="B29" s="198" t="s">
+      <c r="A29" s="244"/>
+      <c r="B29" s="195" t="s">
         <v>265</v>
       </c>
       <c r="C29" s="8" t="str">
@@ -24711,14 +24702,14 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I28),"""",HLOOKUP(REGEXEXTRACT(I28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I28,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J29" s="194" t="str">
+      <c r="J29" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J28),"""",HLOOKUP(REGEXEXTRACT(J28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J28,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:10" ht="12.75">
-      <c r="A30" s="247"/>
-      <c r="B30" s="199" t="s">
+      <c r="A30" s="244"/>
+      <c r="B30" s="196" t="s">
         <v>266</v>
       </c>
       <c r="C30" s="10">
@@ -24729,11 +24720,11 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D28),"""",HLOOKUP(REGEXEXTRACT(D28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D28,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="E30" s="195">
+      <c r="E30" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E28),"""",HLOOKUP(REGEXEXTRACT(E28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E28,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="F30" s="195" t="str">
+      <c r="F30" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F28),"""",HLOOKUP(REGEXEXTRACT(F28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F28,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
@@ -24741,44 +24732,44 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G28),"""",HLOOKUP(REGEXEXTRACT(G28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G28,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="H30" s="195" t="str">
+      <c r="H30" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H28),"""",HLOOKUP(REGEXEXTRACT(H28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H28,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="I30" s="195" t="str">
+      <c r="I30" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I28),"""",HLOOKUP(REGEXEXTRACT(I28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I28,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J30" s="196" t="str">
+      <c r="J30" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J28),"""",HLOOKUP(REGEXEXTRACT(J28,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J28,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:10" ht="12.75">
-      <c r="A32" s="246"/>
-      <c r="B32" s="197" t="s">
+      <c r="A32" s="243"/>
+      <c r="B32" s="194" t="s">
         <v>260</v>
       </c>
-      <c r="C32" s="191" t="s">
+      <c r="C32" s="188" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="192" t="s">
+      <c r="D32" s="189" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="192" t="s">
+      <c r="E32" s="189" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="192"/>
-      <c r="G32" s="192" t="s">
+      <c r="F32" s="189"/>
+      <c r="G32" s="189" t="s">
         <v>17</v>
       </c>
-      <c r="H32" s="192"/>
-      <c r="I32" s="192"/>
-      <c r="J32" s="193"/>
+      <c r="H32" s="189"/>
+      <c r="I32" s="189"/>
+      <c r="J32" s="190"/>
     </row>
     <row r="33" spans="1:10" ht="12.75">
-      <c r="A33" s="247"/>
-      <c r="B33" s="198" t="s">
+      <c r="A33" s="244"/>
+      <c r="B33" s="195" t="s">
         <v>265</v>
       </c>
       <c r="C33" s="8" t="str">
@@ -24809,14 +24800,14 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I32),"""",HLOOKUP(REGEXEXTRACT(I32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I32,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J33" s="194" t="str">
+      <c r="J33" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J32),"""",HLOOKUP(REGEXEXTRACT(J32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J32,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:10" ht="12.75">
-      <c r="A34" s="247"/>
-      <c r="B34" s="199" t="s">
+      <c r="A34" s="244"/>
+      <c r="B34" s="196" t="s">
         <v>267</v>
       </c>
       <c r="C34" s="10">
@@ -24827,11 +24818,11 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D32),"""",HLOOKUP(REGEXEXTRACT(D32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D32,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="E34" s="195">
+      <c r="E34" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E32),"""",HLOOKUP(REGEXEXTRACT(E32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E32,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="F34" s="195" t="str">
+      <c r="F34" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F32),"""",HLOOKUP(REGEXEXTRACT(F32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F32,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
@@ -24839,46 +24830,46 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G32),"""",HLOOKUP(REGEXEXTRACT(G32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G32,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="H34" s="195" t="str">
+      <c r="H34" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H32),"""",HLOOKUP(REGEXEXTRACT(H32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H32,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="I34" s="195" t="str">
+      <c r="I34" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I32),"""",HLOOKUP(REGEXEXTRACT(I32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I32,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J34" s="196" t="str">
+      <c r="J34" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J32),"""",HLOOKUP(REGEXEXTRACT(J32,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J32,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:10" ht="12.75">
-      <c r="A36" s="246"/>
-      <c r="B36" s="200" t="s">
+      <c r="A36" s="243"/>
+      <c r="B36" s="197" t="s">
         <v>260</v>
       </c>
-      <c r="C36" s="191" t="s">
+      <c r="C36" s="188" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="192" t="s">
+      <c r="D36" s="189" t="s">
         <v>3</v>
       </c>
-      <c r="E36" s="192" t="s">
+      <c r="E36" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="192" t="s">
+      <c r="F36" s="189" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="192" t="s">
+      <c r="G36" s="189" t="s">
         <v>13</v>
       </c>
-      <c r="H36" s="192"/>
-      <c r="I36" s="192"/>
-      <c r="J36" s="193"/>
+      <c r="H36" s="189"/>
+      <c r="I36" s="189"/>
+      <c r="J36" s="190"/>
     </row>
     <row r="37" spans="1:10" ht="12.75">
-      <c r="A37" s="247"/>
-      <c r="B37" s="201" t="s">
+      <c r="A37" s="244"/>
+      <c r="B37" s="198" t="s">
         <v>95</v>
       </c>
       <c r="C37" s="8" t="str">
@@ -24909,14 +24900,14 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I36),"""",HLOOKUP(REGEXEXTRACT(I36,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I36,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J37" s="194" t="str">
+      <c r="J37" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J36),"""",HLOOKUP(REGEXEXTRACT(J36,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J36,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="38" spans="1:10" ht="12.75">
-      <c r="A38" s="247"/>
-      <c r="B38" s="202" t="s">
+      <c r="A38" s="244"/>
+      <c r="B38" s="199" t="s">
         <v>268</v>
       </c>
       <c r="C38" s="10">
@@ -24927,11 +24918,11 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D36),"""",HLOOKUP(REGEXEXTRACT(D36,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D36,""(.*)-.*""),""!C3:P"")),3,FALSE))"),1600)</f>
         <v>1600</v>
       </c>
-      <c r="E38" s="195">
+      <c r="E38" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E36),"""",HLOOKUP(REGEXEXTRACT(E36,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E36,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1600)</f>
         <v>1600</v>
       </c>
-      <c r="F38" s="195" t="str">
+      <c r="F38" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F36),"""",HLOOKUP(REGEXEXTRACT(F36,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F36,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
@@ -24939,46 +24930,46 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G36),"""",HLOOKUP(REGEXEXTRACT(G36,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G36,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="H38" s="195" t="str">
+      <c r="H38" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H36),"""",HLOOKUP(REGEXEXTRACT(H36,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H36,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="I38" s="195" t="str">
+      <c r="I38" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I36),"""",HLOOKUP(REGEXEXTRACT(I36,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I36,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J38" s="196" t="str">
+      <c r="J38" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J36),"""",HLOOKUP(REGEXEXTRACT(J36,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J36,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="40" spans="1:10" ht="12.75">
-      <c r="A40" s="246"/>
-      <c r="B40" s="200" t="s">
+      <c r="A40" s="243"/>
+      <c r="B40" s="197" t="s">
         <v>260</v>
       </c>
-      <c r="C40" s="191" t="s">
+      <c r="C40" s="188" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="192" t="s">
+      <c r="D40" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="192" t="s">
+      <c r="E40" s="189" t="s">
         <v>40</v>
       </c>
-      <c r="F40" s="192" t="s">
+      <c r="F40" s="189" t="s">
         <v>15</v>
       </c>
-      <c r="G40" s="192" t="s">
+      <c r="G40" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="H40" s="192"/>
-      <c r="I40" s="192"/>
-      <c r="J40" s="193"/>
+      <c r="H40" s="189"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="190"/>
     </row>
     <row r="41" spans="1:10" ht="12.75">
-      <c r="A41" s="247"/>
-      <c r="B41" s="201" t="s">
+      <c r="A41" s="244"/>
+      <c r="B41" s="198" t="s">
         <v>95</v>
       </c>
       <c r="C41" s="8" t="str">
@@ -25009,14 +25000,14 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I40),"""",HLOOKUP(REGEXEXTRACT(I40,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I40,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J41" s="194" t="str">
+      <c r="J41" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J40),"""",HLOOKUP(REGEXEXTRACT(J40,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J40,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" spans="1:10" ht="12.75">
-      <c r="A42" s="247"/>
-      <c r="B42" s="202" t="s">
+      <c r="A42" s="244"/>
+      <c r="B42" s="199" t="s">
         <v>268</v>
       </c>
       <c r="C42" s="10">
@@ -25027,11 +25018,11 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D40),"""",HLOOKUP(REGEXEXTRACT(D40,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D40,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
-      <c r="E42" s="195">
+      <c r="E42" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E40),"""",HLOOKUP(REGEXEXTRACT(E40,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E40,""(.*)-.*""),""!C3:I"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="F42" s="195" t="str">
+      <c r="F42" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F40),"""",HLOOKUP(REGEXEXTRACT(F40,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F40,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
@@ -25039,42 +25030,42 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G40),"""",HLOOKUP(REGEXEXTRACT(G40,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G40,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="H42" s="195" t="str">
+      <c r="H42" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H40),"""",HLOOKUP(REGEXEXTRACT(H40,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H40,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="I42" s="195" t="str">
+      <c r="I42" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I40),"""",HLOOKUP(REGEXEXTRACT(I40,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I40,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J42" s="196" t="str">
+      <c r="J42" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J40),"""",HLOOKUP(REGEXEXTRACT(J40,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J40,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="44" spans="1:10" ht="12.75">
-      <c r="A44" s="246"/>
-      <c r="B44" s="203" t="s">
+      <c r="A44" s="243"/>
+      <c r="B44" s="200" t="s">
         <v>269</v>
       </c>
-      <c r="C44" s="191"/>
-      <c r="D44" s="192"/>
-      <c r="E44" s="192" t="s">
+      <c r="C44" s="188"/>
+      <c r="D44" s="189"/>
+      <c r="E44" s="189" t="s">
         <v>19</v>
       </c>
-      <c r="F44" s="192" t="s">
+      <c r="F44" s="189" t="s">
         <v>31</v>
       </c>
-      <c r="G44" s="192"/>
-      <c r="H44" s="192" t="s">
+      <c r="G44" s="189"/>
+      <c r="H44" s="189" t="s">
         <v>270</v>
       </c>
-      <c r="I44" s="192"/>
-      <c r="J44" s="193"/>
+      <c r="I44" s="189"/>
+      <c r="J44" s="190"/>
     </row>
     <row r="45" spans="1:10" ht="12.75">
-      <c r="A45" s="247"/>
-      <c r="B45" s="204" t="s">
+      <c r="A45" s="244"/>
+      <c r="B45" s="201" t="s">
         <v>265</v>
       </c>
       <c r="C45" s="8" t="str">
@@ -25105,14 +25096,14 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I44),"""",HLOOKUP(REGEXEXTRACT(I44,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I44,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J45" s="194" t="str">
+      <c r="J45" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J44),"""",HLOOKUP(REGEXEXTRACT(J44,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J44,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" spans="1:10" ht="12.75">
-      <c r="A46" s="247"/>
-      <c r="B46" s="205" t="s">
+      <c r="A46" s="244"/>
+      <c r="B46" s="202" t="s">
         <v>271</v>
       </c>
       <c r="C46" s="10" t="str">
@@ -25123,11 +25114,11 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D44),"""",HLOOKUP(REGEXEXTRACT(D44,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D44,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="E46" s="195">
+      <c r="E46" s="192">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E44),"""",HLOOKUP(REGEXEXTRACT(E44,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E44,""(.*)-.*""),""!C3:Q"")),3,FALSE))"),1750)</f>
         <v>1750</v>
       </c>
-      <c r="F46" s="195" t="str">
+      <c r="F46" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F44),"""",HLOOKUP(REGEXEXTRACT(F44,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F44,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#N/A")</f>
         <v>#N/A</v>
       </c>
@@ -25135,15 +25126,15 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G44),"""",HLOOKUP(REGEXEXTRACT(G44,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G44,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="H46" s="195" t="str">
+      <c r="H46" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H44),"""",HLOOKUP(REGEXEXTRACT(H44,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H44,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="I46" s="195" t="str">
+      <c r="I46" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I44),"""",HLOOKUP(REGEXEXTRACT(I44,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I44,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J46" s="196" t="str">
+      <c r="J46" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J44),"""",HLOOKUP(REGEXEXTRACT(J44,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J44,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
@@ -25155,22 +25146,22 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="12.75">
-      <c r="A48" s="246"/>
-      <c r="B48" s="203" t="s">
+      <c r="A48" s="243"/>
+      <c r="B48" s="200" t="s">
         <v>269</v>
       </c>
-      <c r="C48" s="191"/>
-      <c r="D48" s="192"/>
-      <c r="E48" s="192"/>
-      <c r="F48" s="192"/>
-      <c r="G48" s="192"/>
-      <c r="H48" s="192"/>
-      <c r="I48" s="192"/>
-      <c r="J48" s="193"/>
+      <c r="C48" s="188"/>
+      <c r="D48" s="189"/>
+      <c r="E48" s="189"/>
+      <c r="F48" s="189"/>
+      <c r="G48" s="189"/>
+      <c r="H48" s="189"/>
+      <c r="I48" s="189"/>
+      <c r="J48" s="190"/>
     </row>
     <row r="49" spans="1:10" ht="12.75">
-      <c r="A49" s="247"/>
-      <c r="B49" s="204" t="s">
+      <c r="A49" s="244"/>
+      <c r="B49" s="201" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="8" t="str">
@@ -25201,14 +25192,14 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I48),"""",HLOOKUP(REGEXEXTRACT(I48,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I48,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J49" s="194" t="str">
+      <c r="J49" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J48),"""",HLOOKUP(REGEXEXTRACT(J48,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J48,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="50" spans="1:10" ht="12.75">
-      <c r="A50" s="247"/>
-      <c r="B50" s="205" t="s">
+      <c r="A50" s="244"/>
+      <c r="B50" s="202" t="s">
         <v>272</v>
       </c>
       <c r="C50" s="10" t="str">
@@ -25219,11 +25210,11 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D48),"""",HLOOKUP(REGEXEXTRACT(D48,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D48,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="E50" s="195" t="str">
+      <c r="E50" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E48),"""",HLOOKUP(REGEXEXTRACT(E48,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E48,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="F50" s="195" t="str">
+      <c r="F50" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F48),"""",HLOOKUP(REGEXEXTRACT(F48,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F48,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
@@ -25231,39 +25222,39 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G48),"""",HLOOKUP(REGEXEXTRACT(G48,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G48,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="H50" s="195" t="str">
+      <c r="H50" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H48),"""",HLOOKUP(REGEXEXTRACT(H48,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H48,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="I50" s="195" t="str">
+      <c r="I50" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I48),"""",HLOOKUP(REGEXEXTRACT(I48,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I48,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J50" s="196" t="str">
+      <c r="J50" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J48),"""",HLOOKUP(REGEXEXTRACT(J48,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J48,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="52" spans="1:10" ht="12.75">
-      <c r="A52" s="246"/>
-      <c r="B52" s="206" t="s">
+      <c r="A52" s="243"/>
+      <c r="B52" s="203" t="s">
         <v>273</v>
       </c>
-      <c r="C52" s="191" t="s">
+      <c r="C52" s="188" t="s">
         <v>59</v>
       </c>
-      <c r="D52" s="192" t="s">
+      <c r="D52" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="E52" s="192"/>
-      <c r="F52" s="192"/>
-      <c r="G52" s="192"/>
-      <c r="H52" s="192"/>
-      <c r="I52" s="192"/>
-      <c r="J52" s="193"/>
+      <c r="E52" s="189"/>
+      <c r="F52" s="189"/>
+      <c r="G52" s="189"/>
+      <c r="H52" s="189"/>
+      <c r="I52" s="189"/>
+      <c r="J52" s="190"/>
     </row>
     <row r="53" spans="1:10" ht="12.75">
-      <c r="A53" s="247"/>
+      <c r="A53" s="244"/>
       <c r="B53" s="98"/>
       <c r="C53" s="8" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C52),"""",HLOOKUP(REGEXEXTRACT(C52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C52,""(.*)-.*""),""!C3:P"")),2,FALSE))"),"#REF!")</f>
@@ -25293,13 +25284,13 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I52),"""",HLOOKUP(REGEXEXTRACT(I52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I52,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J53" s="194" t="str">
+      <c r="J53" s="191" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J52),"""",HLOOKUP(REGEXEXTRACT(J52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J52,""(.*)-.*""),""!C3:I"")),2,FALSE))"),"")</f>
         <v/>
       </c>
     </row>
     <row r="54" spans="1:10" ht="12.75">
-      <c r="A54" s="247"/>
+      <c r="A54" s="244"/>
       <c r="B54" s="99"/>
       <c r="C54" s="10" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(C52),"""",HLOOKUP(REGEXEXTRACT(C52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(C52,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
@@ -25309,11 +25300,11 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(D52),"""",HLOOKUP(REGEXEXTRACT(D52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(D52,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"#REF!")</f>
         <v>#REF!</v>
       </c>
-      <c r="E54" s="195" t="str">
+      <c r="E54" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(E52),"""",HLOOKUP(REGEXEXTRACT(E52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(E52,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="F54" s="195" t="str">
+      <c r="F54" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(F52),"""",HLOOKUP(REGEXEXTRACT(F52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(F52,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
@@ -25321,15 +25312,15 @@
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(G52),"""",HLOOKUP(REGEXEXTRACT(G52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(G52,""(.*)-.*""),""!C3:P"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="H54" s="195" t="str">
+      <c r="H54" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(H52),"""",HLOOKUP(REGEXEXTRACT(H52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(H52,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="I54" s="195" t="str">
+      <c r="I54" s="192" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(I52),"""",HLOOKUP(REGEXEXTRACT(I52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(I52,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
-      <c r="J54" s="196" t="str">
+      <c r="J54" s="193" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("IF(ISBLANK(J52),"""",HLOOKUP(REGEXEXTRACT(J52,"".*-(.*)""),INDIRECT(CONCATENATE(REGEXEXTRACT(J52,""(.*)-.*""),""!C3:I"")),3,FALSE))"),"")</f>
         <v/>
       </c>
@@ -25361,22 +25352,22 @@
       <c r="A61" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B61" s="207" t="s">
+      <c r="B61" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="C61" s="207" t="s">
+      <c r="C61" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="D61" s="208" t="s">
+      <c r="D61" s="205" t="s">
         <v>274</v>
       </c>
-      <c r="E61" s="207" t="s">
+      <c r="E61" s="204" t="s">
         <v>275</v>
       </c>
-      <c r="F61" s="208" t="s">
+      <c r="F61" s="205" t="s">
         <v>275</v>
       </c>
-      <c r="G61" s="208" t="s">
+      <c r="G61" s="205" t="s">
         <v>276</v>
       </c>
     </row>
@@ -25384,22 +25375,22 @@
       <c r="A62" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B62" s="207" t="s">
+      <c r="B62" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="C62" s="207" t="s">
+      <c r="C62" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="D62" s="208" t="s">
+      <c r="D62" s="205" t="s">
         <v>274</v>
       </c>
-      <c r="E62" s="207" t="s">
+      <c r="E62" s="204" t="s">
         <v>275</v>
       </c>
-      <c r="F62" s="208" t="s">
+      <c r="F62" s="205" t="s">
         <v>275</v>
       </c>
-      <c r="G62" s="208" t="s">
+      <c r="G62" s="205" t="s">
         <v>276</v>
       </c>
     </row>
@@ -25407,22 +25398,22 @@
       <c r="A63" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B63" s="207" t="s">
+      <c r="B63" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="C63" s="207" t="s">
+      <c r="C63" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="D63" s="208" t="s">
+      <c r="D63" s="205" t="s">
         <v>274</v>
       </c>
-      <c r="E63" s="207" t="s">
+      <c r="E63" s="204" t="s">
         <v>275</v>
       </c>
-      <c r="F63" s="208" t="s">
+      <c r="F63" s="205" t="s">
         <v>275</v>
       </c>
-      <c r="G63" s="209" t="s">
+      <c r="G63" s="206" t="s">
         <v>277</v>
       </c>
     </row>
@@ -25430,22 +25421,22 @@
       <c r="A64" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B64" s="207" t="s">
+      <c r="B64" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="C64" s="207" t="s">
+      <c r="C64" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="D64" s="208" t="s">
+      <c r="D64" s="205" t="s">
         <v>274</v>
       </c>
-      <c r="E64" s="208" t="s">
+      <c r="E64" s="205" t="s">
         <v>275</v>
       </c>
-      <c r="F64" s="207" t="s">
+      <c r="F64" s="204" t="s">
         <v>275</v>
       </c>
-      <c r="G64" s="207" t="s">
+      <c r="G64" s="204" t="s">
         <v>274</v>
       </c>
     </row>
@@ -25453,22 +25444,22 @@
       <c r="A65" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B65" s="207" t="s">
+      <c r="B65" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="C65" s="207" t="s">
+      <c r="C65" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="D65" s="207" t="s">
+      <c r="D65" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="E65" s="208" t="s">
+      <c r="E65" s="205" t="s">
         <v>275</v>
       </c>
-      <c r="F65" s="207" t="s">
+      <c r="F65" s="204" t="s">
         <v>275</v>
       </c>
-      <c r="G65" s="207" t="s">
+      <c r="G65" s="204" t="s">
         <v>274</v>
       </c>
     </row>
@@ -25476,22 +25467,22 @@
       <c r="A66" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B66" s="207" t="s">
+      <c r="B66" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="C66" s="207" t="s">
+      <c r="C66" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="D66" s="207" t="s">
+      <c r="D66" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="E66" s="207" t="s">
+      <c r="E66" s="204" t="s">
         <v>275</v>
       </c>
-      <c r="F66" s="208" t="s">
+      <c r="F66" s="205" t="s">
         <v>275</v>
       </c>
-      <c r="G66" s="209" t="s">
+      <c r="G66" s="206" t="s">
         <v>277</v>
       </c>
     </row>
@@ -25499,22 +25490,22 @@
       <c r="A67" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B67" s="207" t="s">
+      <c r="B67" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="C67" s="207" t="s">
+      <c r="C67" s="204" t="s">
         <v>274</v>
       </c>
-      <c r="D67" s="209" t="s">
+      <c r="D67" s="206" t="s">
         <v>278</v>
       </c>
-      <c r="E67" s="207" t="s">
+      <c r="E67" s="204" t="s">
         <v>275</v>
       </c>
-      <c r="F67" s="208" t="s">
+      <c r="F67" s="205" t="s">
         <v>275</v>
       </c>
-      <c r="G67" s="209" t="s">
+      <c r="G67" s="206" t="s">
         <v>277</v>
       </c>
     </row>
@@ -25569,7 +25560,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="207" t="s">
         <v>279</v>
       </c>
     </row>
@@ -25588,7 +25579,7 @@
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="210" t="s">
+      <c r="A4" s="207" t="s">
         <v>282</v>
       </c>
       <c r="G4" s="7"/>
@@ -25632,7 +25623,7 @@
       <c r="J8" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="K8" s="211" t="e">
+      <c r="K8" s="208" t="e">
         <f ca="1">IF(G8=H19,I20,H20)</f>
         <v>#NAME?</v>
       </c>
@@ -25661,13 +25652,13 @@
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="B11" s="212" t="s">
+      <c r="B11" s="209" t="s">
         <v>254</v>
       </c>
-      <c r="C11" s="212" t="s">
+      <c r="C11" s="209" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="212" t="s">
+      <c r="D11" s="209" t="s">
         <v>80</v>
       </c>
       <c r="G11" s="7" t="s">
@@ -25704,13 +25695,13 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="B13" s="213">
+      <c r="B13" s="210">
         <v>110348</v>
       </c>
-      <c r="C13" s="213">
+      <c r="C13" s="210">
         <v>103400</v>
       </c>
-      <c r="D13" s="213">
+      <c r="D13" s="210">
         <v>113710</v>
       </c>
       <c r="G13" s="7" t="e">
@@ -25733,144 +25724,144 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="B14" s="213"/>
-      <c r="C14" s="213"/>
-      <c r="D14" s="213"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="210"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="B15" s="213"/>
-      <c r="C15" s="213"/>
-      <c r="D15" s="213"/>
+      <c r="B15" s="210"/>
+      <c r="C15" s="210"/>
+      <c r="D15" s="210"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="B16" s="213"/>
-      <c r="C16" s="213"/>
-      <c r="D16" s="213"/>
-      <c r="F16" s="210"/>
+      <c r="B16" s="210"/>
+      <c r="C16" s="210"/>
+      <c r="D16" s="210"/>
+      <c r="F16" s="207"/>
       <c r="G16" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="H16" s="211">
+      <c r="H16" s="208">
         <f>SUM(B40:D40)</f>
         <v>448355.75</v>
       </c>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="213"/>
-      <c r="C17" s="213"/>
-      <c r="D17" s="213"/>
+      <c r="B17" s="210"/>
+      <c r="C17" s="210"/>
+      <c r="D17" s="210"/>
       <c r="G17" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="H17" s="211">
+      <c r="H17" s="208">
         <f>H16/3</f>
         <v>149451.91666666666</v>
       </c>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="213"/>
-      <c r="C18" s="213"/>
-      <c r="D18" s="213"/>
+      <c r="B18" s="210"/>
+      <c r="C18" s="210"/>
+      <c r="D18" s="210"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="213"/>
-      <c r="C19" s="213"/>
-      <c r="D19" s="213"/>
-      <c r="H19" s="212" t="e">
+      <c r="B19" s="210"/>
+      <c r="C19" s="210"/>
+      <c r="D19" s="210"/>
+      <c r="H19" s="209" t="e">
         <f t="shared" ref="H19:J19" ca="1" si="1">_xludf.CONCAT(B12,B11)</f>
         <v>#NAME?</v>
       </c>
-      <c r="I19" s="212" t="e">
+      <c r="I19" s="209" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#NAME?</v>
       </c>
-      <c r="J19" s="212" t="e">
+      <c r="J19" s="209" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#NAME?</v>
       </c>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="213"/>
-      <c r="C20" s="213"/>
-      <c r="D20" s="213"/>
+      <c r="B20" s="210"/>
+      <c r="C20" s="210"/>
+      <c r="D20" s="210"/>
       <c r="G20" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="H20" s="211">
+      <c r="H20" s="208">
         <f t="shared" ref="H20:J20" si="2">$H$17-B40</f>
         <v>-1378.8833333333314</v>
       </c>
-      <c r="I20" s="211">
+      <c r="I20" s="208">
         <f t="shared" si="2"/>
         <v>259.61666666666861</v>
       </c>
-      <c r="J20" s="211">
+      <c r="J20" s="208">
         <f t="shared" si="2"/>
         <v>1119.2666666666628</v>
       </c>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="213"/>
-      <c r="C21" s="213"/>
-      <c r="D21" s="213"/>
+      <c r="B21" s="210"/>
+      <c r="C21" s="210"/>
+      <c r="D21" s="210"/>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="213"/>
-      <c r="C22" s="213"/>
-      <c r="D22" s="213"/>
+      <c r="B22" s="210"/>
+      <c r="C22" s="210"/>
+      <c r="D22" s="210"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="213"/>
-      <c r="C23" s="213"/>
-      <c r="D23" s="213"/>
+      <c r="B23" s="210"/>
+      <c r="C23" s="210"/>
+      <c r="D23" s="210"/>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="213"/>
-      <c r="C24" s="213"/>
-      <c r="D24" s="213"/>
+      <c r="B24" s="210"/>
+      <c r="C24" s="210"/>
+      <c r="D24" s="210"/>
       <c r="J24" s="7"/>
     </row>
     <row r="25" spans="2:10">
-      <c r="B25" s="213"/>
-      <c r="C25" s="213"/>
-      <c r="D25" s="213"/>
+      <c r="B25" s="210"/>
+      <c r="C25" s="210"/>
+      <c r="D25" s="210"/>
       <c r="J25" s="7"/>
     </row>
     <row r="26" spans="2:10">
-      <c r="B26" s="213"/>
-      <c r="C26" s="213"/>
-      <c r="D26" s="213"/>
+      <c r="B26" s="210"/>
+      <c r="C26" s="210"/>
+      <c r="D26" s="210"/>
       <c r="J26" s="7"/>
     </row>
     <row r="27" spans="2:10">
-      <c r="B27" s="213"/>
-      <c r="C27" s="213"/>
-      <c r="D27" s="213"/>
+      <c r="B27" s="210"/>
+      <c r="C27" s="210"/>
+      <c r="D27" s="210"/>
       <c r="J27" s="7"/>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="213"/>
-      <c r="C28" s="213"/>
-      <c r="D28" s="213"/>
+      <c r="B28" s="210"/>
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
       <c r="F28" s="7"/>
       <c r="J28" s="7"/>
     </row>
     <row r="29" spans="2:10">
-      <c r="B29" s="213"/>
-      <c r="C29" s="213"/>
-      <c r="D29" s="213"/>
+      <c r="B29" s="210"/>
+      <c r="C29" s="210"/>
+      <c r="D29" s="210"/>
       <c r="J29" s="7"/>
     </row>
     <row r="30" spans="2:10">
-      <c r="B30" s="213"/>
-      <c r="C30" s="213"/>
-      <c r="D30" s="213"/>
+      <c r="B30" s="210"/>
+      <c r="C30" s="210"/>
+      <c r="D30" s="210"/>
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="2:10">
-      <c r="B31" s="213"/>
-      <c r="C31" s="213"/>
-      <c r="D31" s="213"/>
+      <c r="B31" s="210"/>
+      <c r="C31" s="210"/>
+      <c r="D31" s="210"/>
       <c r="J31" s="7"/>
     </row>
     <row r="32" spans="2:10">
@@ -25886,13 +25877,13 @@
       <c r="J32" s="7"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="B33" s="214">
+      <c r="B33" s="211">
         <v>510</v>
       </c>
-      <c r="C33" s="214">
+      <c r="C33" s="211">
         <v>450</v>
       </c>
-      <c r="D33" s="214">
+      <c r="D33" s="211">
         <v>400</v>
       </c>
       <c r="J33" s="7"/>
@@ -25910,13 +25901,13 @@
       <c r="J34" s="7"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="B35" s="214">
+      <c r="B35" s="211">
         <v>50</v>
       </c>
-      <c r="C35" s="214">
+      <c r="C35" s="211">
         <v>200</v>
       </c>
-      <c r="D35" s="214">
+      <c r="D35" s="211">
         <v>749</v>
       </c>
       <c r="J35" s="7"/>
@@ -25933,13 +25924,13 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="B37" s="215">
+      <c r="B37" s="212">
         <v>100</v>
       </c>
-      <c r="C37" s="215">
+      <c r="C37" s="212">
         <v>100</v>
       </c>
-      <c r="D37" s="215">
+      <c r="D37" s="212">
         <v>150</v>
       </c>
     </row>
@@ -25964,15 +25955,15 @@
       <c r="A39" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="B39" s="216">
+      <c r="B39" s="213">
         <f t="shared" ref="B39:D39" si="4">SUM(IF(ISNUMBER(B32),B32,0),IF(ISNUMBER(B34),B34,0),IF(ISNUMBER(B36),B36,0)) *0.95 - SUM(IF(ISNUMBER(B33),B33,0),IF(ISNUMBER(B35),B35,0),IF(ISNUMBER(B37),B37,0))</f>
         <v>46000.2</v>
       </c>
-      <c r="C39" s="216">
+      <c r="C39" s="213">
         <f t="shared" si="4"/>
         <v>50962.299999999996</v>
       </c>
-      <c r="D39" s="216">
+      <c r="D39" s="213">
         <f t="shared" si="4"/>
         <v>40308.15</v>
       </c>
@@ -25981,15 +25972,15 @@
       <c r="A40" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B40" s="211">
+      <c r="B40" s="208">
         <f t="shared" ref="B40:D40" si="5">B38*0.95+B39</f>
         <v>150830.79999999999</v>
       </c>
-      <c r="C40" s="211">
+      <c r="C40" s="208">
         <f t="shared" si="5"/>
         <v>149192.29999999999</v>
       </c>
-      <c r="D40" s="211">
+      <c r="D40" s="208">
         <f t="shared" si="5"/>
         <v>148332.65</v>
       </c>
@@ -25999,7 +25990,7 @@
         <f t="shared" ref="A42:D42" ca="1" si="6">IF($H$3=1,G8,G12)</f>
         <v>#NAME?</v>
       </c>
-      <c r="B42" s="210" t="str">
+      <c r="B42" s="207" t="str">
         <f t="shared" si="6"/>
         <v>lists gem for</v>
       </c>
@@ -26007,11 +25998,11 @@
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
       </c>
-      <c r="D42" s="210" t="str">
+      <c r="D42" s="207" t="str">
         <f t="shared" si="6"/>
         <v>at price</v>
       </c>
-      <c r="E42" s="211" t="e">
+      <c r="E42" s="208" t="e">
         <f t="shared" ref="E42:E43" ca="1" si="7">ABS(IF($H$3=1,K8,K12))</f>
         <v>#NAME?</v>
       </c>
@@ -26021,7 +26012,7 @@
         <f t="shared" ref="A43:D43" ca="1" si="8">IF($H$3=1,G9,G13)</f>
         <v>#NAME?</v>
       </c>
-      <c r="B43" s="210" t="str">
+      <c r="B43" s="207" t="str">
         <f t="shared" si="8"/>
         <v>lists gem for</v>
       </c>
@@ -26029,11 +26020,11 @@
         <f t="shared" ca="1" si="8"/>
         <v>#NAME?</v>
       </c>
-      <c r="D43" s="210" t="str">
+      <c r="D43" s="207" t="str">
         <f t="shared" si="8"/>
         <v>at price</v>
       </c>
-      <c r="E43" s="211" t="e">
+      <c r="E43" s="208" t="e">
         <f t="shared" ca="1" si="7"/>
         <v>#NAME?</v>
       </c>
